--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ДЗТ\pmi_dzt\dtz2_modes\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{683E3844-2838-4F52-8D3E-D4D1F9A89C0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E013718B-5EC1-466A-83C0-22F4EE63CD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="995" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="79">
   <si>
     <t>№</t>
   </si>
@@ -57,109 +57,52 @@
     <t>Ед. изм.</t>
   </si>
   <si>
+    <t>ДЗТ / Д2Г: Пуск ф.C</t>
+  </si>
+  <si>
     <t>Хорошее [0]</t>
   </si>
   <si>
     <t>System</t>
   </si>
   <si>
-    <t>Слот M3.Реле1. Статус</t>
-  </si>
-  <si>
     <t>0</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Ввод</t>
+    <t>ДЗТ / Д2Г: Пуск</t>
   </si>
   <si>
-    <t>1</t>
+    <t>Слот M4.Реле1. Статус</t>
   </si>
   <si>
-    <t>Статус светодиода "Готовность"</t>
+    <t>ПС / ПС: Пуск (имп)</t>
   </si>
   <si>
-    <t>Виртуальный ключ-3_Опер. вывод</t>
+    <t>ПС / ПС: Пуск</t>
   </si>
   <si>
-    <t>Виртуальный ключ-4_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ДТО</t>
-  </si>
-  <si>
-    <t>ДВ: ДТО на сигн</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ3. Статус</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ4. Статус</t>
+    <t>Слот M3.Реле1. Статус</t>
   </si>
   <si>
     <t>Слот M3.Реле2. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле5. Статус</t>
+    <t>ДЗТ / КЦТнеб: Неисправность</t>
   </si>
   <si>
-    <t>Слот M3.Реле8. Статус</t>
+    <t>КЦТ / КЦТст1: Пуск обрыв</t>
   </si>
   <si>
-    <t>Слот M4.Реле3. Статус</t>
+    <t>КЦТ / КЦТст1: Срабатывание обрыв</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Оперативный вывод</t>
+    <t>КЦТ / КЦТст1: Пуск асимметрия</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: ИО IA</t>
+    <t>КЦТ / КЦТст1: Сраб. асимметрия</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: ИО IB</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТО: ИО IC</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-2_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ДЗТ</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ2. Статус</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-1_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: Вывод терминала</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ1. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле8. Статус</t>
-  </si>
-  <si>
-    <t>ПС / ПС: Пуск</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле6. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле7. Статус</t>
+    <t>КЦТ / КЦТ общ: Срабатывание</t>
   </si>
   <si>
     <t>ЛО Т / ЛО: Срабатывание</t>
@@ -168,34 +111,34 @@
     <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
   </si>
   <si>
-    <t>Слот M3.Реле6. Статус</t>
+    <t>1</t>
   </si>
   <si>
     <t>Слот M3.Реле7. Статус</t>
   </si>
   <si>
-    <t>Слот M4.Реле4. Статус</t>
+    <t>Слот M3.Реле8. Статус</t>
   </si>
   <si>
-    <t>Слот M4.Реле5. Статус</t>
+    <t>ДЗТ / ДТЗт: ИО IC</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Пуск ф.B</t>
+    <t>ДЗТ / ДТЗт: Пуск ф.C</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Пуск</t>
+    <t>ДЗТ / ДТЗт: Пуск</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Сраб. ф.B сигн</t>
+    <t>ДЗТ / ДТЗт: Сраб. ф.C сигн</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Срабатывание сигн</t>
+    <t>ДЗТ / ДТЗт: Срабатывание сигн</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Срабатывание ф.B</t>
+    <t>ДЗТ / ДТЗт: Срабатывание ф.C</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Срабатывание</t>
+    <t>ДЗТ / ДТЗт: Срабатывание</t>
   </si>
   <si>
     <t>ДЗТ / Общие: Срабатывание</t>
@@ -207,34 +150,118 @@
     <t>Слот M3.Реле4. Статус</t>
   </si>
   <si>
-    <t>Слот M4.Реле1. Статус</t>
+    <t>ДВ: ОВ КЦТст2</t>
   </si>
   <si>
-    <t>Слот M4.Реле2. Статус</t>
+    <t>КЦТ / КЦТст2: Ввод</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Пуск ф.A</t>
+    <t>КЦТ / КЦТст2: Оперативный вывод</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Пуск ф.C</t>
+    <t>КЦТ / КЦТст2: Пуск обрыв</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Сраб. ф.A сигн</t>
+    <t>КЦТ / КЦТст2: Срабатывание обрыв</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Сраб. ф.C сигн</t>
+    <t>КЦТ / КЦТст2: Пуск асимметрия</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Срабатывание ф.A</t>
+    <t>КЦТ / КЦТст2: Сраб. асимметрия</t>
   </si>
   <si>
-    <t>ДЗТ / ДТО: Срабатывание ф.C</t>
+    <t>Виртуальный ключ-10_Опер. вывод</t>
   </si>
   <si>
-    <t>ПС / ПС: Пуск (имп)</t>
+    <t>Слот M8. ДВ3. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / Д2Г: Пуск ф.B</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: ИО IB</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Пуск ф.B</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Сраб. ф.B сигн</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Срабатывание ф.B</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле5. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле6. Статус</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ КЦТст3</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Ввод</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Пуск обрыв</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Срабатывание обрыв</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Пуск асимметрия</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст3: Сраб. асимметрия</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-11_Опер. вывод</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ4. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / Д2Г: Пуск ф.A</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст1: Ввод</t>
+  </si>
+  <si>
+    <t>КЦТ / КЦТст1: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-9_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ КЦТст1</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ2. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: ИО IA</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Пуск ф.A</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Ввод</t>
   </si>
   <si>
     <t>Наличие внешнего питания (общий)</t>
+  </si>
+  <si>
+    <t>Статус светодиода "Готовность"</t>
   </si>
 </sst>
 </file>
@@ -636,17 +663,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J329"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
     <col min="3" max="3" width="24.28515625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="159" style="3" customWidth="1"/>
+    <col min="4" max="4" width="159.5703125" style="3" customWidth="1"/>
     <col min="5" max="5" width="7" style="3" customWidth="1"/>
     <col min="6" max="6" width="12.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="16.85546875" style="3" customWidth="1"/>
     <col min="8" max="8" width="13.28515625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="10.140625" style="3" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" style="3" customWidth="1"/>
     <col min="10" max="10" width="8" style="3" customWidth="1"/>
   </cols>
   <sheetData>
@@ -684,804 +711,804 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>19804</v>
+        <v>1</v>
       </c>
       <c r="C2" s="2">
-        <v>45806.908700832908</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>19805</v>
+        <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>45806.908710044656</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>19806</v>
+        <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>45806.908710044656</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>19807</v>
+        <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>45806.908710044656</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>19808</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>45806.908710101176</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>19809</v>
+        <v>6</v>
       </c>
       <c r="C7" s="2">
-        <v>45806.908703794128</v>
+        <v>45807.954818137878</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>19810</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2">
-        <v>45806.908703794128</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>19811</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2">
-        <v>45806.908712881705</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>19812</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2">
-        <v>45806.908712881705</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>19813</v>
+        <v>10</v>
       </c>
       <c r="C11" s="2">
-        <v>45806.908712881705</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>19814</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2">
-        <v>45806.908712949516</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>19815</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2">
-        <v>45806.909778114721</v>
+        <v>45807.954827067064</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>19816</v>
+        <v>13</v>
       </c>
       <c r="C14" s="2">
-        <v>45806.909778114721</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>19817</v>
+        <v>14</v>
       </c>
       <c r="C15" s="2">
-        <v>45806.909778114721</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>19818</v>
+        <v>15</v>
       </c>
       <c r="C16" s="2">
-        <v>45806.90977818254</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>58</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>19819</v>
+        <v>16</v>
       </c>
       <c r="C17" s="2">
-        <v>45806.90977818254</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>19820</v>
+        <v>17</v>
       </c>
       <c r="C18" s="2">
-        <v>45806.909778239053</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>19821</v>
+        <v>18</v>
       </c>
       <c r="C19" s="2">
-        <v>45806.909778239053</v>
+        <v>45807.954827123584</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19822</v>
+        <v>19</v>
       </c>
       <c r="C20" s="2">
-        <v>45806.909778239053</v>
+        <v>45807.955718858517</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>66</v>
+        <v>41</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>19823</v>
+        <v>20</v>
       </c>
       <c r="C21" s="2">
-        <v>45806.909778239053</v>
+        <v>45807.955718858517</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>19824</v>
+        <v>21</v>
       </c>
       <c r="C22" s="2">
-        <v>45806.909778239053</v>
+        <v>45807.955718858517</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>19825</v>
+        <v>22</v>
       </c>
       <c r="C23" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955718858517</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>19826</v>
+        <v>23</v>
       </c>
       <c r="C24" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>19827</v>
+        <v>24</v>
       </c>
       <c r="C25" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>68</v>
+        <v>43</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>19828</v>
+        <v>25</v>
       </c>
       <c r="C26" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>19829</v>
+        <v>26</v>
       </c>
       <c r="C27" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>59</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>19830</v>
+        <v>27</v>
       </c>
       <c r="C28" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>19831</v>
+        <v>28</v>
       </c>
       <c r="C29" s="2">
-        <v>45806.909778295572</v>
+        <v>45807.955724656938</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>19832</v>
+        <v>29</v>
       </c>
       <c r="C30" s="2">
-        <v>45806.909778352085</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>19833</v>
+        <v>30</v>
       </c>
       <c r="C31" s="2">
-        <v>45806.909778352085</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>19834</v>
+        <v>31</v>
       </c>
       <c r="C32" s="2">
-        <v>45806.909778352085</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>19835</v>
+        <v>32</v>
       </c>
       <c r="C33" s="2">
-        <v>45806.909778408604</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
+        <v>23</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>19836</v>
+        <v>33</v>
       </c>
       <c r="C34" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>19837</v>
+        <v>34</v>
       </c>
       <c r="C35" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756609932</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>19838</v>
+        <v>35</v>
       </c>
       <c r="C36" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>13</v>
@@ -1489,22 +1516,22 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>19839</v>
+        <v>36</v>
       </c>
       <c r="C37" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>13</v>
@@ -1512,22 +1539,22 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>19840</v>
+        <v>37</v>
       </c>
       <c r="C38" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>13</v>
@@ -1535,22 +1562,22 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>19841</v>
+        <v>38</v>
       </c>
       <c r="C39" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>13</v>
@@ -1558,22 +1585,22 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>19842</v>
+        <v>39</v>
       </c>
       <c r="C40" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
         <v>13</v>
@@ -1581,22 +1608,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>19843</v>
+        <v>40</v>
       </c>
       <c r="C41" s="2">
-        <v>45806.909850000455</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
         <v>13</v>
@@ -1604,114 +1631,114 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>19844</v>
+        <v>41</v>
       </c>
       <c r="C42" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>45</v>
+        <v>16</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>19845</v>
+        <v>42</v>
       </c>
       <c r="C43" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>19846</v>
+        <v>43</v>
       </c>
       <c r="C44" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>19847</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756677751</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>59</v>
+        <v>19</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>19848</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756734271</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
         <v>13</v>
@@ -1719,22 +1746,22 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>19849</v>
+        <v>46</v>
       </c>
       <c r="C47" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756734271</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>13</v>
@@ -1742,22 +1769,22 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>19850</v>
+        <v>47</v>
       </c>
       <c r="C48" s="2">
-        <v>45806.909850068281</v>
+        <v>45807.955756734271</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>13</v>
@@ -1765,22 +1792,22 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>19851</v>
+        <v>48</v>
       </c>
       <c r="C49" s="2">
-        <v>45806.909850124786</v>
+        <v>45807.955756734271</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I49" s="3" t="s">
         <v>13</v>
@@ -1788,45 +1815,45 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>19852</v>
+        <v>49</v>
       </c>
       <c r="C50" s="2">
-        <v>45806.909850124786</v>
+        <v>45807.955756734271</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>19853</v>
+        <v>50</v>
       </c>
       <c r="C51" s="2">
-        <v>45806.909850124786</v>
+        <v>45807.95575679079</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
         <v>13</v>
@@ -1834,505 +1861,505 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>19854</v>
+        <v>51</v>
       </c>
       <c r="C52" s="2">
-        <v>45806.909850181306</v>
+        <v>45807.9558284054</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H52" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>19855</v>
+        <v>52</v>
       </c>
       <c r="C53" s="2">
-        <v>45806.909850181306</v>
+        <v>45807.9558284054</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>19856</v>
+        <v>53</v>
       </c>
       <c r="C54" s="2">
-        <v>45806.909850181306</v>
+        <v>45807.9558284054</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>52</v>
+        <v>33</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H54" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>19857</v>
+        <v>54</v>
       </c>
       <c r="C55" s="2">
-        <v>45806.909850181306</v>
+        <v>45807.9558284054</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H55" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>19858</v>
+        <v>55</v>
       </c>
       <c r="C56" s="2">
-        <v>45806.909850237818</v>
+        <v>45807.9558284054</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>19859</v>
+        <v>56</v>
       </c>
       <c r="C57" s="2">
-        <v>45806.909850237818</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H57" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>19860</v>
+        <v>57</v>
       </c>
       <c r="C58" s="2">
-        <v>45806.909850294331</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H58" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>19861</v>
+        <v>58</v>
       </c>
       <c r="C59" s="2">
-        <v>45806.909850294331</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>19862</v>
+        <v>59</v>
       </c>
       <c r="C60" s="2">
-        <v>45806.909850294331</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>19863</v>
+        <v>60</v>
       </c>
       <c r="C61" s="2">
-        <v>45806.909850294331</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>19864</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
-        <v>45806.909850294331</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>19865</v>
+        <v>62</v>
       </c>
       <c r="C63" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>19866</v>
+        <v>63</v>
       </c>
       <c r="C64" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>19867</v>
+        <v>64</v>
       </c>
       <c r="C65" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>68</v>
+        <v>25</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>19868</v>
+        <v>65</v>
       </c>
       <c r="C66" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828461905</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>19869</v>
+        <v>66</v>
       </c>
       <c r="C67" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>19870</v>
+        <v>67</v>
       </c>
       <c r="C68" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>19871</v>
+        <v>68</v>
       </c>
       <c r="C69" s="2">
-        <v>45806.90985035085</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>19872</v>
+        <v>69</v>
       </c>
       <c r="C70" s="2">
-        <v>45806.909850407363</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>19873</v>
+        <v>70</v>
       </c>
       <c r="C71" s="2">
-        <v>45806.909850407363</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>19874</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
-        <v>45806.909850407363</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>19875</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
-        <v>45806.909850463882</v>
+        <v>45807.955828518425</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>68</v>
+        <v>29</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
         <v>13</v>
@@ -2340,22 +2367,22 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>19876</v>
+        <v>73</v>
       </c>
       <c r="C74" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.955828574937</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I74" s="3" t="s">
         <v>13</v>
@@ -2363,114 +2390,114 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>19877</v>
+        <v>74</v>
       </c>
       <c r="C75" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.955828574937</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>51</v>
+        <v>15</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>19878</v>
+        <v>75</v>
       </c>
       <c r="C76" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.955900370398</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>19879</v>
+        <v>76</v>
       </c>
       <c r="C77" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.955900370398</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>53</v>
+        <v>14</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>19880</v>
+        <v>77</v>
       </c>
       <c r="C78" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.95590042691</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>19881</v>
+        <v>78</v>
       </c>
       <c r="C79" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.95590042691</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I79" s="3" t="s">
         <v>13</v>
@@ -2478,22 +2505,22 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>19882</v>
+        <v>79</v>
       </c>
       <c r="C80" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.95590042691</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I80" s="3" t="s">
         <v>13</v>
@@ -2501,68 +2528,68 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>19883</v>
+        <v>80</v>
       </c>
       <c r="C81" s="2">
-        <v>45806.909922010673</v>
+        <v>45807.955900483423</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H81" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>19884</v>
+        <v>81</v>
       </c>
       <c r="C82" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955900483423</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H82" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>19885</v>
+        <v>82</v>
       </c>
       <c r="C83" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955900483423</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H83" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I83" s="3" t="s">
         <v>13</v>
@@ -2570,22 +2597,22 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>19886</v>
+        <v>83</v>
       </c>
       <c r="C84" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955900539942</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H84" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I84" s="3" t="s">
         <v>13</v>
@@ -2593,45 +2620,45 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>19887</v>
+        <v>84</v>
       </c>
       <c r="C85" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955900539942</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H85" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>19888</v>
+        <v>85</v>
       </c>
       <c r="C86" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955901410271</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H86" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I86" s="3" t="s">
         <v>13</v>
@@ -2639,22 +2666,22 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>19889</v>
+        <v>86</v>
       </c>
       <c r="C87" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.955901410271</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="F87" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H87" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I87" s="3" t="s">
         <v>13</v>
@@ -2662,91 +2689,91 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>19890</v>
+        <v>87</v>
       </c>
       <c r="C88" s="2">
-        <v>45806.909922067185</v>
+        <v>45807.95597209804</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>50</v>
       </c>
       <c r="F88" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>19891</v>
+        <v>88</v>
       </c>
       <c r="C89" s="2">
-        <v>45806.909922123705</v>
+        <v>45807.95597209804</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F89" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>19892</v>
+        <v>89</v>
       </c>
       <c r="C90" s="2">
-        <v>45806.909922123705</v>
+        <v>45807.955972154552</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F90" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H90" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>19893</v>
+        <v>90</v>
       </c>
       <c r="C91" s="2">
-        <v>45806.909922123705</v>
+        <v>45807.955972154552</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F91" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H91" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
         <v>13</v>
@@ -2754,22 +2781,22 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>19894</v>
+        <v>91</v>
       </c>
       <c r="C92" s="2">
-        <v>45806.90992218021</v>
+        <v>45807.955972154552</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="F92" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H92" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I92" s="3" t="s">
         <v>13</v>
@@ -2777,873 +2804,873 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>19895</v>
+        <v>92</v>
       </c>
       <c r="C93" s="2">
-        <v>45806.909922236729</v>
+        <v>45807.955972211064</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F93" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>19896</v>
+        <v>93</v>
       </c>
       <c r="C94" s="2">
-        <v>45806.909922236729</v>
+        <v>45807.955972211064</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="F94" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>19897</v>
+        <v>94</v>
       </c>
       <c r="C95" s="2">
-        <v>45806.909922236729</v>
+        <v>45807.955972211064</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>52</v>
+        <v>18</v>
       </c>
       <c r="F95" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G95" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>19898</v>
+        <v>95</v>
       </c>
       <c r="C96" s="2">
-        <v>45806.909922293242</v>
+        <v>45807.955972267438</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="F96" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>19899</v>
+        <v>96</v>
       </c>
       <c r="C97" s="2">
-        <v>45806.909922293242</v>
+        <v>45807.955972267438</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F97" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G97" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>19900</v>
+        <v>97</v>
       </c>
       <c r="C98" s="2">
-        <v>45806.909922349761</v>
+        <v>45807.955972436983</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="F98" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G98" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H98" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>19901</v>
+        <v>98</v>
       </c>
       <c r="C99" s="2">
-        <v>45806.909922349761</v>
+        <v>45807.955972436983</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>54</v>
+        <v>14</v>
       </c>
       <c r="F99" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G99" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H99" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>19902</v>
+        <v>99</v>
       </c>
       <c r="C100" s="2">
-        <v>45806.909922349761</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F100" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H100" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>19903</v>
+        <v>100</v>
       </c>
       <c r="C101" s="2">
-        <v>45806.909922349761</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="F101" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H101" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>19904</v>
+        <v>101</v>
       </c>
       <c r="C102" s="2">
-        <v>45806.909922349761</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="F102" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>19905</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="F103" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H103" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>19906</v>
+        <v>103</v>
       </c>
       <c r="C104" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F104" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H104" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>19907</v>
+        <v>104</v>
       </c>
       <c r="C105" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F105" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H105" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>19908</v>
+        <v>105</v>
       </c>
       <c r="C106" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="F106" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>19909</v>
+        <v>106</v>
       </c>
       <c r="C107" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="F107" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>19910</v>
+        <v>107</v>
       </c>
       <c r="C108" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="F108" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>19911</v>
+        <v>108</v>
       </c>
       <c r="C109" s="2">
-        <v>45806.909922406281</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="F109" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H109" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>19912</v>
+        <v>109</v>
       </c>
       <c r="C110" s="2">
-        <v>45806.909922462786</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="F110" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G110" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H110" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>19913</v>
+        <v>110</v>
       </c>
       <c r="C111" s="2">
-        <v>45806.909922462786</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F111" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I111" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>19914</v>
+        <v>111</v>
       </c>
       <c r="C112" s="2">
-        <v>45806.909922462786</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="F112" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H112" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>19915</v>
+        <v>112</v>
       </c>
       <c r="C113" s="2">
-        <v>45806.909922530613</v>
+        <v>45807.956031268099</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F113" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>19916</v>
+        <v>113</v>
       </c>
       <c r="C114" s="2">
-        <v>45806.909994179128</v>
+        <v>45807.956031324611</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F114" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>19917</v>
+        <v>114</v>
       </c>
       <c r="C115" s="2">
-        <v>45806.909994179128</v>
+        <v>45807.956031324611</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="F115" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>19918</v>
+        <v>115</v>
       </c>
       <c r="C116" s="2">
-        <v>45806.909994235641</v>
+        <v>45807.956031324611</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F116" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>19919</v>
+        <v>116</v>
       </c>
       <c r="C117" s="2">
-        <v>45806.909994235641</v>
+        <v>45807.956031324611</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="F117" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>19920</v>
+        <v>117</v>
       </c>
       <c r="C118" s="2">
-        <v>45806.909994235641</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="F118" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>19921</v>
+        <v>118</v>
       </c>
       <c r="C119" s="2">
-        <v>45806.909994235641</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F119" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>19922</v>
+        <v>119</v>
       </c>
       <c r="C120" s="2">
-        <v>45806.90999429216</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="F120" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>19923</v>
+        <v>120</v>
       </c>
       <c r="C121" s="2">
-        <v>45806.90999429216</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="F121" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>19924</v>
+        <v>121</v>
       </c>
       <c r="C122" s="2">
-        <v>45806.90999429216</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F122" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>19925</v>
+        <v>122</v>
       </c>
       <c r="C123" s="2">
-        <v>45806.90999429216</v>
+        <v>45807.956031381131</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F123" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>19926</v>
+        <v>123</v>
       </c>
       <c r="C124" s="2">
-        <v>45806.909994348673</v>
+        <v>45807.95603143765</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="F124" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G124" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>19927</v>
+        <v>124</v>
       </c>
       <c r="C125" s="2">
-        <v>45806.909994348673</v>
+        <v>45807.95603143765</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="F125" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G125" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>19928</v>
+        <v>125</v>
       </c>
       <c r="C126" s="2">
-        <v>45806.909994348673</v>
+        <v>45807.95603143765</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="F126" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G126" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>19929</v>
+        <v>126</v>
       </c>
       <c r="C127" s="2">
-        <v>45806.909994416492</v>
+        <v>45807.95603143765</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="F127" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G127" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>19930</v>
+        <v>127</v>
       </c>
       <c r="C128" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.95603143765</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F128" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G128" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>19931</v>
+        <v>128</v>
       </c>
       <c r="C129" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956031494155</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
       <c r="F129" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G129" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>19932</v>
+        <v>129</v>
       </c>
       <c r="C130" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956031550675</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="F130" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G130" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I130" s="3" t="s">
         <v>13</v>
@@ -3651,22 +3678,22 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>19933</v>
+        <v>130</v>
       </c>
       <c r="C131" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956103696517</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F131" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G131" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I131" s="3" t="s">
         <v>13</v>
@@ -3674,22 +3701,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>19934</v>
+        <v>131</v>
       </c>
       <c r="C132" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956103696517</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="F132" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G132" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I132" s="3" t="s">
         <v>13</v>
@@ -3697,22 +3724,22 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>19935</v>
+        <v>132</v>
       </c>
       <c r="C133" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="F133" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G133" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I133" s="3" t="s">
         <v>13</v>
@@ -3720,68 +3747,68 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>19936</v>
+        <v>133</v>
       </c>
       <c r="C134" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G134" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>19937</v>
+        <v>134</v>
       </c>
       <c r="C135" s="2">
-        <v>45806.910053225009</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="F135" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G135" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>19938</v>
+        <v>135</v>
       </c>
       <c r="C136" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="F136" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G136" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I136" s="3" t="s">
         <v>13</v>
@@ -3789,22 +3816,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>19939</v>
+        <v>136</v>
       </c>
       <c r="C137" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="F137" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G137" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I137" s="3" t="s">
         <v>13</v>
@@ -3812,22 +3839,22 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>19940</v>
+        <v>137</v>
       </c>
       <c r="C138" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="F138" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G138" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>13</v>
@@ -3835,22 +3862,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>19941</v>
+        <v>138</v>
       </c>
       <c r="C139" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="F139" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G139" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I139" s="3" t="s">
         <v>13</v>
@@ -3858,45 +3885,45 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>19942</v>
+        <v>139</v>
       </c>
       <c r="C140" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F140" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G140" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>19943</v>
+        <v>140</v>
       </c>
       <c r="C141" s="2">
-        <v>45806.910053281521</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F141" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G141" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I141" s="3" t="s">
         <v>13</v>
@@ -3904,45 +3931,45 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>19944</v>
+        <v>141</v>
       </c>
       <c r="C142" s="2">
-        <v>45806.910053338041</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="F142" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G142" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>19945</v>
+        <v>142</v>
       </c>
       <c r="C143" s="2">
-        <v>45806.910053338041</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="F143" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G143" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I143" s="3" t="s">
         <v>13</v>
@@ -3950,137 +3977,137 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>19946</v>
+        <v>143</v>
       </c>
       <c r="C144" s="2">
-        <v>45806.910125811664</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F144" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G144" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>19947</v>
+        <v>144</v>
       </c>
       <c r="C145" s="2">
-        <v>45806.910125811664</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F145" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G145" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>19948</v>
+        <v>145</v>
       </c>
       <c r="C146" s="2">
-        <v>45806.910125811664</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F146" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G146" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>19949</v>
+        <v>146</v>
       </c>
       <c r="C147" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G147" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>19950</v>
+        <v>147</v>
       </c>
       <c r="C148" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F148" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G148" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>19951</v>
+        <v>148</v>
       </c>
       <c r="C149" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109483632</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="F149" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G149" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I149" s="3" t="s">
         <v>13</v>
@@ -4088,22 +4115,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>19952</v>
+        <v>149</v>
       </c>
       <c r="C150" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="F150" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G150" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I150" s="3" t="s">
         <v>13</v>
@@ -4111,22 +4138,22 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>19953</v>
+        <v>150</v>
       </c>
       <c r="C151" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="F151" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G151" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H151" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I151" s="3" t="s">
         <v>13</v>
@@ -4134,91 +4161,91 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>19954</v>
+        <v>151</v>
       </c>
       <c r="C152" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>52</v>
+        <v>16</v>
       </c>
       <c r="F152" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G152" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H152" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>19955</v>
+        <v>152</v>
       </c>
       <c r="C153" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="F153" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G153" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H153" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>19956</v>
+        <v>153</v>
       </c>
       <c r="C154" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>53</v>
+        <v>19</v>
       </c>
       <c r="F154" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G154" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H154" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>19957</v>
+        <v>154</v>
       </c>
       <c r="C155" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="F155" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G155" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H155" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I155" s="3" t="s">
         <v>13</v>
@@ -4226,22 +4253,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>19958</v>
+        <v>155</v>
       </c>
       <c r="C156" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109540151</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>54</v>
+        <v>30</v>
       </c>
       <c r="F156" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G156" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H156" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I156" s="3" t="s">
         <v>13</v>
@@ -4249,22 +4276,22 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>19959</v>
+        <v>156</v>
       </c>
       <c r="C157" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956109596664</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F157" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G157" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H157" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I157" s="3" t="s">
         <v>13</v>
@@ -4272,91 +4299,91 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>19960</v>
+        <v>157</v>
       </c>
       <c r="C158" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956117350346</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="F158" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G158" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H158" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>19961</v>
+        <v>158</v>
       </c>
       <c r="C159" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956117350346</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="F159" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G159" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H159" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>19962</v>
+        <v>159</v>
       </c>
       <c r="C160" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F160" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G160" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H160" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>19963</v>
+        <v>160</v>
       </c>
       <c r="C161" s="2">
-        <v>45806.910125868184</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F161" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G161" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H161" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I161" s="3" t="s">
         <v>13</v>
@@ -4364,22 +4391,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>19964</v>
+        <v>161</v>
       </c>
       <c r="C162" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F162" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G162" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H162" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I162" s="3" t="s">
         <v>13</v>
@@ -4387,45 +4414,45 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>19965</v>
+        <v>162</v>
       </c>
       <c r="C163" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D163" s="3" t="s">
         <v>23</v>
       </c>
       <c r="F163" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G163" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H163" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>19966</v>
+        <v>163</v>
       </c>
       <c r="C164" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F164" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G164" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H164" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I164" s="3" t="s">
         <v>13</v>
@@ -4433,229 +4460,229 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>19967</v>
+        <v>164</v>
       </c>
       <c r="C165" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F165" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G165" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H165" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>19968</v>
+        <v>165</v>
       </c>
       <c r="C166" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="F166" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G166" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H166" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>19969</v>
+        <v>166</v>
       </c>
       <c r="C167" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F167" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G167" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H167" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>19970</v>
+        <v>167</v>
       </c>
       <c r="C168" s="2">
-        <v>45806.910125924704</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="F168" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G168" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H168" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>19971</v>
+        <v>168</v>
       </c>
       <c r="C169" s="2">
-        <v>45806.910198556427</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="F169" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G169" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H169" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>19972</v>
+        <v>169</v>
       </c>
       <c r="C170" s="2">
-        <v>45806.910198556427</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>40</v>
+        <v>61</v>
       </c>
       <c r="F170" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G170" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H170" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>19973</v>
+        <v>170</v>
       </c>
       <c r="C171" s="2">
-        <v>45806.910198850303</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="F171" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G171" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H171" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>19974</v>
+        <v>171</v>
       </c>
       <c r="C172" s="2">
-        <v>45806.910198850303</v>
+        <v>45807.956117418158</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G172" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H172" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>19975</v>
+        <v>172</v>
       </c>
       <c r="C173" s="2">
-        <v>45806.910198850303</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="F173" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G173" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H173" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>19976</v>
+        <v>173</v>
       </c>
       <c r="C174" s="2">
-        <v>45806.910204343534</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F174" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G174" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H174" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I174" s="3" t="s">
         <v>13</v>
@@ -4663,114 +4690,114 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>19977</v>
+        <v>174</v>
       </c>
       <c r="C175" s="2">
-        <v>45806.910204400054</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F175" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G175" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H175" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>19978</v>
+        <v>175</v>
       </c>
       <c r="C176" s="2">
-        <v>45806.910204400054</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="F176" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G176" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H176" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>19979</v>
+        <v>176</v>
       </c>
       <c r="C177" s="2">
-        <v>45806.910204400054</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F177" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G177" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H177" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>19980</v>
+        <v>177</v>
       </c>
       <c r="C178" s="2">
-        <v>45806.910204400054</v>
+        <v>45807.956117474678</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="F178" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G178" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H178" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>19981</v>
+        <v>178</v>
       </c>
       <c r="C179" s="2">
-        <v>45806.910270736182</v>
+        <v>45807.956117531183</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>32</v>
+        <v>66</v>
       </c>
       <c r="F179" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G179" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H179" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I179" s="3" t="s">
         <v>13</v>
@@ -4778,22 +4805,22 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>19982</v>
+        <v>179</v>
       </c>
       <c r="C180" s="2">
-        <v>45806.910270736182</v>
+        <v>45807.956117870279</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F180" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G180" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H180" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I180" s="3" t="s">
         <v>13</v>
@@ -4801,114 +4828,114 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>19983</v>
+        <v>180</v>
       </c>
       <c r="C181" s="2">
-        <v>45806.910271086577</v>
+        <v>45807.956117870279</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F181" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G181" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H181" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I181" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>19984</v>
+        <v>181</v>
       </c>
       <c r="C182" s="2">
-        <v>45806.910271086577</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F182" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G182" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H182" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>19985</v>
+        <v>182</v>
       </c>
       <c r="C183" s="2">
-        <v>45806.910271086577</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F183" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G183" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H183" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>19986</v>
+        <v>183</v>
       </c>
       <c r="C184" s="2">
-        <v>45806.910276523296</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F184" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G184" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H184" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>19987</v>
+        <v>184</v>
       </c>
       <c r="C185" s="2">
-        <v>45806.910425867267</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="F185" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G185" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H185" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I185" s="3" t="s">
         <v>13</v>
@@ -4916,22 +4943,22 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>19988</v>
+        <v>185</v>
       </c>
       <c r="C186" s="2">
-        <v>45806.910425867267</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="F186" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G186" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H186" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I186" s="3" t="s">
         <v>13</v>
@@ -4939,22 +4966,22 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>19989</v>
+        <v>186</v>
       </c>
       <c r="C187" s="2">
-        <v>45806.910425867267</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="F187" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G187" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H187" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I187" s="3" t="s">
         <v>13</v>
@@ -4962,22 +4989,22 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>19990</v>
+        <v>187</v>
       </c>
       <c r="C188" s="2">
-        <v>45806.910425867267</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="F188" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G188" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H188" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I188" s="3" t="s">
         <v>13</v>
@@ -4985,68 +5012,68 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>19991</v>
+        <v>188</v>
       </c>
       <c r="C189" s="2">
-        <v>45806.910425923787</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="F189" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G189" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H189" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>19992</v>
+        <v>189</v>
       </c>
       <c r="C190" s="2">
-        <v>45806.910425923787</v>
+        <v>45807.956176407519</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F190" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G190" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H190" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>19993</v>
+        <v>190</v>
       </c>
       <c r="C191" s="2">
-        <v>45806.910425923787</v>
+        <v>45807.956176464038</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F191" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G191" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H191" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I191" s="3" t="s">
         <v>13</v>
@@ -5054,22 +5081,22 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>19994</v>
+        <v>191</v>
       </c>
       <c r="C192" s="2">
-        <v>45806.910425923787</v>
+        <v>45807.956176464038</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G192" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H192" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I192" s="3" t="s">
         <v>13</v>
@@ -5077,91 +5104,91 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>19995</v>
+        <v>192</v>
       </c>
       <c r="C193" s="2">
-        <v>45806.910465223555</v>
+        <v>45807.956261506406</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="F193" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G193" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H193" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>19996</v>
+        <v>193</v>
       </c>
       <c r="C194" s="2">
-        <v>45806.910465223555</v>
+        <v>45807.956261506406</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F194" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G194" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>19997</v>
+        <v>194</v>
       </c>
       <c r="C195" s="2">
-        <v>45806.910465223555</v>
+        <v>45807.956261562918</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F195" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G195" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H195" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>19998</v>
+        <v>195</v>
       </c>
       <c r="C196" s="2">
-        <v>45806.910465223555</v>
+        <v>45807.956261687104</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F196" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G196" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H196" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I196" s="3" t="s">
         <v>13</v>
@@ -5169,22 +5196,22 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>19999</v>
+        <v>196</v>
       </c>
       <c r="C197" s="2">
-        <v>45806.910471010669</v>
+        <v>45807.956262489613</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="F197" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G197" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H197" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I197" s="3" t="s">
         <v>13</v>
@@ -5192,30 +5219,3043 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>20000</v>
+        <v>197</v>
       </c>
       <c r="C198" s="2">
-        <v>45806.910471010669</v>
+        <v>45807.956262489613</v>
       </c>
       <c r="D198" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="C199" s="2">
+        <v>45807.956320506928</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="C200" s="2">
+        <v>45807.956320506928</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="C201" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="C202" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="C203" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="C204" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="C205" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="C206" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="C207" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="C208" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="C209" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="C210" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="C211" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="C212" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="C213" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="C214" s="2">
+        <v>45807.956320789497</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="C215" s="2">
+        <v>45807.956320846009</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="C216" s="2">
+        <v>45807.956320846009</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="C217" s="2">
+        <v>45807.956320846009</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="C218" s="2">
+        <v>45807.956320846009</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="C219" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="C220" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="C221" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="C222" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="C223" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="C224" s="2">
+        <v>45807.956320913821</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="C225" s="2">
+        <v>45807.956320970341</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="C226" s="2">
+        <v>45807.956320970341</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="C227" s="2">
+        <v>45807.956320970341</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="C228" s="2">
+        <v>45807.956320970341</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="C229" s="2">
+        <v>45807.956320970341</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="C230" s="2">
+        <v>45807.956321026861</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="C231" s="2">
+        <v>45807.956321083373</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="C232" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="C233" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="C234" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="C235" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="C236" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="C237" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="C238" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="C239" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="C240" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="C241" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="C242" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="C243" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="C244" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="C245" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="C246" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="C247" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="C248" s="2">
+        <v>45807.956326294036</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="C249" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="C250" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="C251" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="C252" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="C253" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="C254" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="C255" s="2">
+        <v>45807.956326350548</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="C256" s="2">
+        <v>45807.956326407068</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="C257" s="2">
+        <v>45807.956407063888</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>257</v>
+      </c>
+      <c r="C258" s="2">
+        <v>45807.956407063888</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>258</v>
+      </c>
+      <c r="C259" s="2">
+        <v>45807.95640717692</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>259</v>
+      </c>
+      <c r="C260" s="2">
+        <v>45807.956407233425</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>260</v>
+      </c>
+      <c r="C261" s="2">
+        <v>45807.956407459489</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>261</v>
+      </c>
+      <c r="C262" s="2">
+        <v>45807.956407459489</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>262</v>
+      </c>
+      <c r="C263" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>263</v>
+      </c>
+      <c r="C264" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>264</v>
+      </c>
+      <c r="C265" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>265</v>
+      </c>
+      <c r="C266" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>266</v>
+      </c>
+      <c r="C267" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>267</v>
+      </c>
+      <c r="C268" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>268</v>
+      </c>
+      <c r="C269" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>269</v>
+      </c>
+      <c r="C270" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>270</v>
+      </c>
+      <c r="C271" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>271</v>
+      </c>
+      <c r="C272" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>272</v>
+      </c>
+      <c r="C273" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>273</v>
+      </c>
+      <c r="C274" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>274</v>
+      </c>
+      <c r="C275" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>275</v>
+      </c>
+      <c r="C276" s="2">
+        <v>45807.956466166281</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>276</v>
+      </c>
+      <c r="C277" s="2">
+        <v>45807.956466222793</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H277" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>277</v>
+      </c>
+      <c r="C278" s="2">
+        <v>45807.956466222793</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H278" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>278</v>
+      </c>
+      <c r="C279" s="2">
+        <v>45807.956466222793</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>279</v>
+      </c>
+      <c r="C280" s="2">
+        <v>45807.956466222793</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H280" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>280</v>
+      </c>
+      <c r="C281" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>281</v>
+      </c>
+      <c r="C282" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>282</v>
+      </c>
+      <c r="C283" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H283" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>283</v>
+      </c>
+      <c r="C284" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>284</v>
+      </c>
+      <c r="C285" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I285" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>285</v>
+      </c>
+      <c r="C286" s="2">
+        <v>45807.956466279305</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H286" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I286" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>286</v>
+      </c>
+      <c r="C287" s="2">
+        <v>45807.956466347132</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H287" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>287</v>
+      </c>
+      <c r="C288" s="2">
+        <v>45807.956466347132</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H288" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I288" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>288</v>
+      </c>
+      <c r="C289" s="2">
+        <v>45807.956466347132</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>289</v>
+      </c>
+      <c r="C290" s="2">
+        <v>45807.956466347132</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H290" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I290" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>290</v>
+      </c>
+      <c r="C291" s="2">
+        <v>45807.956466347132</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H291" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>291</v>
+      </c>
+      <c r="C292" s="2">
+        <v>45807.956466403637</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H292" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>292</v>
+      </c>
+      <c r="C293" s="2">
+        <v>45807.956466460157</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H293" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>293</v>
+      </c>
+      <c r="C294" s="2">
+        <v>45807.956540154359</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>294</v>
+      </c>
+      <c r="C295" s="2">
+        <v>45807.956540154359</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H295" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>295</v>
+      </c>
+      <c r="C296" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>296</v>
+      </c>
+      <c r="C297" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>297</v>
+      </c>
+      <c r="C298" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H298" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>298</v>
+      </c>
+      <c r="C299" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H299" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>299</v>
+      </c>
+      <c r="C300" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H300" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>300</v>
+      </c>
+      <c r="C301" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H301" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>301</v>
+      </c>
+      <c r="C302" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H302" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>302</v>
+      </c>
+      <c r="C303" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>303</v>
+      </c>
+      <c r="C304" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>304</v>
+      </c>
+      <c r="C305" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H305" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>305</v>
+      </c>
+      <c r="C306" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H306" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>306</v>
+      </c>
+      <c r="C307" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H307" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>307</v>
+      </c>
+      <c r="C308" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H308" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>308</v>
+      </c>
+      <c r="C309" s="2">
+        <v>45807.956540267391</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G309" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H309" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>309</v>
+      </c>
+      <c r="C310" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H310" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>310</v>
+      </c>
+      <c r="C311" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H311" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>311</v>
+      </c>
+      <c r="C312" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H312" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I312" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>312</v>
+      </c>
+      <c r="C313" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H313" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>313</v>
+      </c>
+      <c r="C314" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H314" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>314</v>
+      </c>
+      <c r="C315" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>315</v>
+      </c>
+      <c r="C316" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H316" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>316</v>
+      </c>
+      <c r="C317" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H317" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>317</v>
+      </c>
+      <c r="C318" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H318" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I318" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>318</v>
+      </c>
+      <c r="C319" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D319" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F198" s="3" t="s">
+      <c r="F319" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G319" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H319" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>319</v>
+      </c>
+      <c r="C320" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H320" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I320" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>320</v>
+      </c>
+      <c r="C321" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H321" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>321</v>
+      </c>
+      <c r="C322" s="2">
+        <v>45807.956540335203</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H322" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I322" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A323" s="1">
+        <v>322</v>
+      </c>
+      <c r="C323" s="2">
+        <v>45807.956540391722</v>
+      </c>
+      <c r="D323" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F323" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G323" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H323" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I323" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A324" s="1">
+        <v>323</v>
+      </c>
+      <c r="C324" s="2">
+        <v>45807.956540391722</v>
+      </c>
+      <c r="D324" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F324" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G324" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H324" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I324" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A325" s="1">
+        <v>324</v>
+      </c>
+      <c r="C325" s="2">
+        <v>45807.956540391722</v>
+      </c>
+      <c r="D325" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F325" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G325" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H325" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I325" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A326" s="1">
+        <v>325</v>
+      </c>
+      <c r="C326" s="2">
+        <v>45807.956540391722</v>
+      </c>
+      <c r="D326" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F326" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G326" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H326" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I326" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A327" s="1">
+        <v>326</v>
+      </c>
+      <c r="C327" s="2">
+        <v>45807.956540448242</v>
+      </c>
+      <c r="D327" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F327" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G327" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H327" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I327" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A328" s="1">
+        <v>327</v>
+      </c>
+      <c r="C328" s="2">
+        <v>45807.956543115732</v>
+      </c>
+      <c r="D328" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G198" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="H198" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="I198" s="3" t="s">
+      <c r="F328" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G328" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H328" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I328" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A329" s="1">
+        <v>328</v>
+      </c>
+      <c r="C329" s="2">
+        <v>45807.956543115732</v>
+      </c>
+      <c r="D329" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F329" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G329" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H329" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I329" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J198">
-    <sortCondition ref="A1:A198"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J329">
+    <sortCondition ref="A2:A329"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ДЗТ\pmi_dzt\dtz2_modes\Журнал событий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ДЗТ\pmi_dzt\dtz3_modes\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E013718B-5EC1-466A-83C0-22F4EE63CD2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C566CE-664D-4FA7-B9DF-5AFB54F4F396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1650" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1440" uniqueCount="67">
   <si>
     <t>№</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Ед. изм.</t>
   </si>
   <si>
-    <t>ДЗТ / Д2Г: Пуск ф.C</t>
+    <t>Виртуальный ключ-7_Опер. вывод</t>
   </si>
   <si>
     <t>Хорошее [0]</t>
@@ -69,40 +69,103 @@
     <t>0</t>
   </si>
   <si>
-    <t>ДЗТ / Д2Г: Пуск</t>
+    <t>ДВ: ОВ КЦТнеб</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ2. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Ввод</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-2_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ ДЗТ</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ1. Статус</t>
+  </si>
+  <si>
+    <t>Слот M4.Реле2. Статус</t>
+  </si>
+  <si>
+    <t>ПС / ПС: Пуск</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле3. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле7. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле8. Статус</t>
   </si>
   <si>
     <t>Слот M4.Реле1. Статус</t>
   </si>
   <si>
+    <t>ДЗТ / КЦТнеб: Ввод</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Срабатывание ф.C</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Срабатывание</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Неисправность</t>
+  </si>
+  <si>
     <t>ПС / ПС: Пуск (имп)</t>
   </si>
   <si>
-    <t>ПС / ПС: Пуск</t>
+    <t>Слот M3.Реле6. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Срабатывание ф.B</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле5. Статус</t>
+  </si>
+  <si>
+    <t>ДЗТ / КЦТнеб: Срабатывание ф.A</t>
   </si>
   <si>
     <t>Слот M3.Реле1. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле2. Статус</t>
+    <t>ДЗТ / Д2Г: Пуск ф.A</t>
   </si>
   <si>
-    <t>ДЗТ / КЦТнеб: Неисправность</t>
+    <t>ДЗТ / Д2Г: Пуск ф.B</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст1: Пуск обрыв</t>
+    <t>ДЗТ / Д2Г: Пуск ф.C</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст1: Срабатывание обрыв</t>
+    <t>ДЗТ / Д2Г: Пуск</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст1: Пуск асимметрия</t>
+    <t>ДЗТ / ДТЗт: ИО IA</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст1: Сраб. асимметрия</t>
+    <t>ДЗТ / ДТЗт: ИО IB</t>
   </si>
   <si>
-    <t>КЦТ / КЦТ общ: Срабатывание</t>
+    <t>ДЗТ / ДТЗт: ИО IC</t>
   </si>
   <si>
     <t>ЛО Т / ЛО: Срабатывание</t>
@@ -111,16 +174,10 @@
     <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
   </si>
   <si>
-    <t>1</t>
+    <t>ДЗТ / ДТЗт: Пуск ф.A</t>
   </si>
   <si>
-    <t>Слот M3.Реле7. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле8. Статус</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: ИО IC</t>
+    <t>ДЗТ / ДТЗт: Пуск ф.B</t>
   </si>
   <si>
     <t>ДЗТ / ДТЗт: Пуск ф.C</t>
@@ -129,10 +186,22 @@
     <t>ДЗТ / ДТЗт: Пуск</t>
   </si>
   <si>
+    <t>ДЗТ / ДТЗт: Сраб. ф.A сигн</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Сраб. ф.B сигн</t>
+  </si>
+  <si>
     <t>ДЗТ / ДТЗт: Сраб. ф.C сигн</t>
   </si>
   <si>
     <t>ДЗТ / ДТЗт: Срабатывание сигн</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Срабатывание ф.A</t>
+  </si>
+  <si>
+    <t>ДЗТ / ДТЗт: Срабатывание ф.B</t>
   </si>
   <si>
     <t>ДЗТ / ДТЗт: Срабатывание ф.C</t>
@@ -144,124 +213,19 @@
     <t>ДЗТ / Общие: Срабатывание</t>
   </si>
   <si>
-    <t>Слот M3.Реле3. Статус</t>
+    <t>Слот M3.Реле2. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле4. Статус</t>
+    <t>ДЗТ / Д5Г: Пуск ф.B</t>
   </si>
   <si>
-    <t>ДВ: ОВ КЦТст2</t>
+    <t>ДЗТ / Д5Г: Пуск</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст2: Ввод</t>
+    <t>ДЗТ / Д5Г: Пуск ф.C</t>
   </si>
   <si>
-    <t>КЦТ / КЦТст2: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст2: Пуск обрыв</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст2: Срабатывание обрыв</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст2: Пуск асимметрия</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст2: Сраб. асимметрия</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-10_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ3. Статус</t>
-  </si>
-  <si>
-    <t>ДЗТ / Д2Г: Пуск ф.B</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: ИО IB</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: Пуск ф.B</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: Сраб. ф.B сигн</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: Срабатывание ф.B</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле5. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле6. Статус</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ КЦТст3</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Ввод</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Пуск обрыв</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Срабатывание обрыв</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Пуск асимметрия</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст3: Сраб. асимметрия</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-11_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ4. Статус</t>
-  </si>
-  <si>
-    <t>ДЗТ / Д2Г: Пуск ф.A</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст1: Ввод</t>
-  </si>
-  <si>
-    <t>КЦТ / КЦТст1: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-9_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ КЦТст1</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ2. Статус</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: ИО IA</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: Пуск ф.A</t>
-  </si>
-  <si>
-    <t>ДЗТ / ДТЗт: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Ввод</t>
-  </si>
-  <si>
-    <t>Наличие внешнего питания (общий)</t>
-  </si>
-  <si>
-    <t>Статус светодиода "Готовность"</t>
+    <t>ДЗТ / Д5Г: Пуск ф.A</t>
   </si>
 </sst>
 </file>
@@ -663,7 +627,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J329"/>
+  <dimension ref="A1:J287"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -711,13 +675,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>1</v>
+        <v>1360</v>
       </c>
       <c r="C2" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -729,18 +693,18 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>2</v>
+        <v>1361</v>
       </c>
       <c r="C3" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -752,18 +716,18 @@
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>3</v>
+        <v>1362</v>
       </c>
       <c r="C4" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -775,18 +739,18 @@
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4</v>
+        <v>1363</v>
       </c>
       <c r="C5" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -798,18 +762,18 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>5</v>
+        <v>1364</v>
       </c>
       <c r="C6" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -821,18 +785,18 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>1365</v>
       </c>
       <c r="C7" s="2">
-        <v>45807.954818137878</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -844,18 +808,18 @@
         <v>12</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>1366</v>
       </c>
       <c r="C8" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -867,18 +831,18 @@
         <v>12</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>1367</v>
       </c>
       <c r="C9" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -890,18 +854,18 @@
         <v>12</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>1368</v>
       </c>
       <c r="C10" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -913,18 +877,18 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>1369</v>
       </c>
       <c r="C11" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -936,18 +900,18 @@
         <v>12</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>1370</v>
       </c>
       <c r="C12" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837472498</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -959,18 +923,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>1371</v>
       </c>
       <c r="C13" s="2">
-        <v>45807.954827067064</v>
+        <v>45808.043837529018</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>76</v>
+        <v>39</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -982,18 +946,18 @@
         <v>12</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>1372</v>
       </c>
       <c r="C14" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043837529018</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -1005,18 +969,18 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>1373</v>
       </c>
       <c r="C15" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043890324363</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -1028,18 +992,18 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>1374</v>
       </c>
       <c r="C16" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043890324363</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -1051,18 +1015,18 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>1375</v>
       </c>
       <c r="C17" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043890324363</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -1074,18 +1038,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>1376</v>
       </c>
       <c r="C18" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043890380883</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -1097,18 +1061,18 @@
         <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>1377</v>
       </c>
       <c r="C19" s="2">
-        <v>45807.954827123584</v>
+        <v>45808.043890380883</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1120,18 +1084,18 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>1378</v>
       </c>
       <c r="C20" s="2">
-        <v>45807.955718858517</v>
+        <v>45808.043890380883</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1143,18 +1107,18 @@
         <v>12</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>1379</v>
       </c>
       <c r="C21" s="2">
-        <v>45807.955718858517</v>
+        <v>45808.043890437388</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1171,13 +1135,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>1380</v>
       </c>
       <c r="C22" s="2">
-        <v>45807.955718858517</v>
+        <v>45808.043890437388</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -1194,13 +1158,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>1381</v>
       </c>
       <c r="C23" s="2">
-        <v>45807.955718858517</v>
+        <v>45808.043890437388</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1217,13 +1181,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>1382</v>
       </c>
       <c r="C24" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043890493907</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -1235,18 +1199,18 @@
         <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>24</v>
+        <v>1383</v>
       </c>
       <c r="C25" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043890674759</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1263,13 +1227,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>25</v>
+        <v>1384</v>
       </c>
       <c r="C26" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043890900815</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1281,18 +1245,18 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>26</v>
+        <v>1385</v>
       </c>
       <c r="C27" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043891138179</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1309,13 +1273,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>27</v>
+        <v>1386</v>
       </c>
       <c r="C28" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043891138179</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1332,13 +1296,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>28</v>
+        <v>1387</v>
       </c>
       <c r="C29" s="2">
-        <v>45807.955724656938</v>
+        <v>45808.043891194691</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1355,13 +1319,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>29</v>
+        <v>1388</v>
       </c>
       <c r="C30" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.04389147726</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1373,18 +1337,18 @@
         <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>30</v>
+        <v>1389</v>
       </c>
       <c r="C31" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.043891545087</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1396,18 +1360,18 @@
         <v>12</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>31</v>
+        <v>1390</v>
       </c>
       <c r="C32" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.043891545087</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1419,18 +1383,18 @@
         <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>32</v>
+        <v>1391</v>
       </c>
       <c r="C33" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.043891601592</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1442,18 +1406,18 @@
         <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>33</v>
+        <v>1392</v>
       </c>
       <c r="C34" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.044671721378</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1465,18 +1429,18 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>34</v>
+        <v>1393</v>
       </c>
       <c r="C35" s="2">
-        <v>45807.955756609932</v>
+        <v>45808.044671721378</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1488,18 +1452,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>35</v>
+        <v>1394</v>
       </c>
       <c r="C36" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671721378</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1511,18 +1475,18 @@
         <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>36</v>
+        <v>1395</v>
       </c>
       <c r="C37" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671721378</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1534,18 +1498,18 @@
         <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>37</v>
+        <v>1396</v>
       </c>
       <c r="C38" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671721378</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>22</v>
+        <v>43</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1557,18 +1521,18 @@
         <v>12</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>38</v>
+        <v>1397</v>
       </c>
       <c r="C39" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.04467177789</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1580,18 +1544,18 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>39</v>
+        <v>1398</v>
       </c>
       <c r="C40" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.04467177789</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1603,18 +1567,18 @@
         <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>40</v>
+        <v>1399</v>
       </c>
       <c r="C41" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.04467177789</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1626,18 +1590,18 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>41</v>
+        <v>1400</v>
       </c>
       <c r="C42" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1649,18 +1613,18 @@
         <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>42</v>
+        <v>1401</v>
       </c>
       <c r="C43" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1672,18 +1636,18 @@
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>43</v>
+        <v>1402</v>
       </c>
       <c r="C44" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1695,18 +1659,18 @@
         <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>44</v>
+        <v>1403</v>
       </c>
       <c r="C45" s="2">
-        <v>45807.955756677751</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>19</v>
+        <v>52</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1718,18 +1682,18 @@
         <v>12</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>45</v>
+        <v>1404</v>
       </c>
       <c r="C46" s="2">
-        <v>45807.955756734271</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1746,13 +1710,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>46</v>
+        <v>1405</v>
       </c>
       <c r="C47" s="2">
-        <v>45807.955756734271</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1769,13 +1733,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>47</v>
+        <v>1406</v>
       </c>
       <c r="C48" s="2">
-        <v>45807.955756734271</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1792,13 +1756,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>48</v>
+        <v>1407</v>
       </c>
       <c r="C49" s="2">
-        <v>45807.955756734271</v>
+        <v>45808.044671902222</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1815,13 +1779,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>49</v>
+        <v>1408</v>
       </c>
       <c r="C50" s="2">
-        <v>45807.955756734271</v>
+        <v>45808.044671958742</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1833,18 +1797,18 @@
         <v>12</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>50</v>
+        <v>1409</v>
       </c>
       <c r="C51" s="2">
-        <v>45807.95575679079</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>15</v>
+        <v>53</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1856,18 +1820,18 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>51</v>
+        <v>1410</v>
       </c>
       <c r="C52" s="2">
-        <v>45807.9558284054</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -1879,18 +1843,18 @@
         <v>12</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>52</v>
+        <v>1411</v>
       </c>
       <c r="C53" s="2">
-        <v>45807.9558284054</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1902,18 +1866,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>53</v>
+        <v>1412</v>
       </c>
       <c r="C54" s="2">
-        <v>45807.9558284054</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1925,18 +1889,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>54</v>
+        <v>1413</v>
       </c>
       <c r="C55" s="2">
-        <v>45807.9558284054</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1948,18 +1912,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>55</v>
+        <v>1414</v>
       </c>
       <c r="C56" s="2">
-        <v>45807.9558284054</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1971,18 +1935,18 @@
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>56</v>
+        <v>1415</v>
       </c>
       <c r="C57" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1994,18 +1958,18 @@
         <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>57</v>
+        <v>1416</v>
       </c>
       <c r="C58" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -2017,18 +1981,18 @@
         <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>58</v>
+        <v>1417</v>
       </c>
       <c r="C59" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672015247</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -2040,18 +2004,18 @@
         <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>59</v>
+        <v>1418</v>
       </c>
       <c r="C60" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672071766</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -2063,18 +2027,18 @@
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>60</v>
+        <v>1419</v>
       </c>
       <c r="C61" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672071766</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -2086,18 +2050,18 @@
         <v>12</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>61</v>
+        <v>1420</v>
       </c>
       <c r="C62" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672071766</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -2109,18 +2073,18 @@
         <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>62</v>
+        <v>1421</v>
       </c>
       <c r="C63" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672071766</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -2132,15 +2096,15 @@
         <v>12</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>63</v>
+        <v>1422</v>
       </c>
       <c r="C64" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672128279</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>24</v>
@@ -2155,18 +2119,18 @@
         <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>64</v>
+        <v>1423</v>
       </c>
       <c r="C65" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044672184798</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -2178,18 +2142,18 @@
         <v>12</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>65</v>
+        <v>1424</v>
       </c>
       <c r="C66" s="2">
-        <v>45807.955828461905</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -2201,18 +2165,18 @@
         <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>66</v>
+        <v>1425</v>
       </c>
       <c r="C67" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -2229,13 +2193,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>67</v>
+        <v>1426</v>
       </c>
       <c r="C68" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -2252,13 +2216,13 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>68</v>
+        <v>1427</v>
       </c>
       <c r="C69" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -2270,18 +2234,18 @@
         <v>12</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>69</v>
+        <v>1428</v>
       </c>
       <c r="C70" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -2293,18 +2257,18 @@
         <v>12</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>70</v>
+        <v>1429</v>
       </c>
       <c r="C71" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -2316,18 +2280,18 @@
         <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>71</v>
+        <v>1430</v>
       </c>
       <c r="C72" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>19</v>
+        <v>55</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -2339,18 +2303,18 @@
         <v>12</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>72</v>
+        <v>1431</v>
       </c>
       <c r="C73" s="2">
-        <v>45807.955828518425</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -2367,13 +2331,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>73</v>
+        <v>1432</v>
       </c>
       <c r="C74" s="2">
-        <v>45807.955828574937</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -2390,13 +2354,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>74</v>
+        <v>1433</v>
       </c>
       <c r="C75" s="2">
-        <v>45807.955828574937</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -2408,18 +2372,18 @@
         <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>75</v>
+        <v>1434</v>
       </c>
       <c r="C76" s="2">
-        <v>45807.955900370398</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -2431,18 +2395,18 @@
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>76</v>
+        <v>1435</v>
       </c>
       <c r="C77" s="2">
-        <v>45807.955900370398</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>14</v>
+        <v>60</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -2454,18 +2418,18 @@
         <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>77</v>
+        <v>1436</v>
       </c>
       <c r="C78" s="2">
-        <v>45807.95590042691</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -2477,18 +2441,18 @@
         <v>12</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>78</v>
+        <v>1437</v>
       </c>
       <c r="C79" s="2">
-        <v>45807.95590042691</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -2500,18 +2464,18 @@
         <v>12</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>79</v>
+        <v>1438</v>
       </c>
       <c r="C80" s="2">
-        <v>45807.95590042691</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>11</v>
@@ -2523,18 +2487,18 @@
         <v>12</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>80</v>
+        <v>1439</v>
       </c>
       <c r="C81" s="2">
-        <v>45807.955900483423</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>11</v>
@@ -2546,18 +2510,18 @@
         <v>12</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>81</v>
+        <v>1440</v>
       </c>
       <c r="C82" s="2">
-        <v>45807.955900483423</v>
+        <v>45808.044742996899</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>22</v>
+        <v>61</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>11</v>
@@ -2569,18 +2533,18 @@
         <v>12</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>82</v>
+        <v>1441</v>
       </c>
       <c r="C83" s="2">
-        <v>45807.955900483423</v>
+        <v>45808.044743053419</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -2597,13 +2561,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>83</v>
+        <v>1442</v>
       </c>
       <c r="C84" s="2">
-        <v>45807.955900539942</v>
+        <v>45808.044743053419</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>11</v>
@@ -2620,13 +2584,13 @@
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>84</v>
+        <v>1443</v>
       </c>
       <c r="C85" s="2">
-        <v>45807.955900539942</v>
+        <v>45808.044743053419</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -2638,18 +2602,18 @@
         <v>12</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>85</v>
+        <v>1444</v>
       </c>
       <c r="C86" s="2">
-        <v>45807.955901410271</v>
+        <v>45808.044743109924</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>11</v>
@@ -2666,13 +2630,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>86</v>
+        <v>1445</v>
       </c>
       <c r="C87" s="2">
-        <v>45807.955901410271</v>
+        <v>45808.044743166443</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>11</v>
@@ -2689,13 +2653,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>87</v>
+        <v>1446</v>
       </c>
       <c r="C88" s="2">
-        <v>45807.95597209804</v>
+        <v>45808.044819064722</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -2707,18 +2671,18 @@
         <v>12</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>88</v>
+        <v>1447</v>
       </c>
       <c r="C89" s="2">
-        <v>45807.95597209804</v>
+        <v>45808.044819064722</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -2730,18 +2694,18 @@
         <v>12</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>89</v>
+        <v>1448</v>
       </c>
       <c r="C90" s="2">
-        <v>45807.955972154552</v>
+        <v>45808.044819064722</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>10</v>
+        <v>65</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -2753,18 +2717,18 @@
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>90</v>
+        <v>1449</v>
       </c>
       <c r="C91" s="2">
-        <v>45807.955972154552</v>
+        <v>45808.044819064722</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -2776,18 +2740,18 @@
         <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>91</v>
+        <v>1450</v>
       </c>
       <c r="C92" s="2">
-        <v>45807.955972154552</v>
+        <v>45808.044819121242</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>22</v>
+        <v>62</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -2799,18 +2763,18 @@
         <v>12</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>92</v>
+        <v>1451</v>
       </c>
       <c r="C93" s="2">
-        <v>45807.955972211064</v>
+        <v>45808.045015044081</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>11</v>
@@ -2822,18 +2786,18 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>93</v>
+        <v>1452</v>
       </c>
       <c r="C94" s="2">
-        <v>45807.955972211064</v>
+        <v>45808.045015044081</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>11</v>
@@ -2845,18 +2809,18 @@
         <v>12</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>94</v>
+        <v>1453</v>
       </c>
       <c r="C95" s="2">
-        <v>45807.955972211064</v>
+        <v>45808.045015044081</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>18</v>
+        <v>51</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>11</v>
@@ -2868,18 +2832,18 @@
         <v>12</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>95</v>
+        <v>1454</v>
       </c>
       <c r="C96" s="2">
-        <v>45807.955972267438</v>
+        <v>45808.045015044081</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -2891,18 +2855,18 @@
         <v>12</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>96</v>
+        <v>1455</v>
       </c>
       <c r="C97" s="2">
-        <v>45807.955972267438</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>11</v>
@@ -2914,18 +2878,18 @@
         <v>12</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>97</v>
+        <v>1456</v>
       </c>
       <c r="C98" s="2">
-        <v>45807.955972436983</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>11</v>
@@ -2937,18 +2901,18 @@
         <v>12</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>98</v>
+        <v>1457</v>
       </c>
       <c r="C99" s="2">
-        <v>45807.955972436983</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>11</v>
@@ -2960,18 +2924,18 @@
         <v>12</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>99</v>
+        <v>1458</v>
       </c>
       <c r="C100" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>11</v>
@@ -2983,18 +2947,18 @@
         <v>12</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>100</v>
+        <v>1459</v>
       </c>
       <c r="C101" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>11</v>
@@ -3006,18 +2970,18 @@
         <v>12</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>101</v>
+        <v>1460</v>
       </c>
       <c r="C102" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -3029,18 +2993,18 @@
         <v>12</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>102</v>
+        <v>1461</v>
       </c>
       <c r="C103" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>11</v>
@@ -3052,18 +3016,18 @@
         <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>103</v>
+        <v>1462</v>
       </c>
       <c r="C104" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -3075,18 +3039,18 @@
         <v>12</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>104</v>
+        <v>1463</v>
       </c>
       <c r="C105" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015157113</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>11</v>
@@ -3098,18 +3062,18 @@
         <v>12</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>105</v>
+        <v>1464</v>
       </c>
       <c r="C106" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015213618</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>11</v>
@@ -3121,18 +3085,18 @@
         <v>12</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>106</v>
+        <v>1465</v>
       </c>
       <c r="C107" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015213618</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>11</v>
@@ -3144,18 +3108,18 @@
         <v>12</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>107</v>
+        <v>1466</v>
       </c>
       <c r="C108" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015213618</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>11</v>
@@ -3167,18 +3131,18 @@
         <v>12</v>
       </c>
       <c r="I108" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>108</v>
+        <v>1467</v>
       </c>
       <c r="C109" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015213618</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>11</v>
@@ -3190,15 +3154,15 @@
         <v>12</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>109</v>
+        <v>1468</v>
       </c>
       <c r="C110" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015270138</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>24</v>
@@ -3213,18 +3177,18 @@
         <v>12</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>110</v>
+        <v>1469</v>
       </c>
       <c r="C111" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045015326657</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>11</v>
@@ -3241,13 +3205,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>111</v>
+        <v>1470</v>
       </c>
       <c r="C112" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -3259,18 +3223,18 @@
         <v>12</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>112</v>
+        <v>1471</v>
       </c>
       <c r="C113" s="2">
-        <v>45807.956031268099</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>11</v>
@@ -3282,18 +3246,18 @@
         <v>12</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>113</v>
+        <v>1472</v>
       </c>
       <c r="C114" s="2">
-        <v>45807.956031324611</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>11</v>
@@ -3310,13 +3274,13 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>114</v>
+        <v>1473</v>
       </c>
       <c r="C115" s="2">
-        <v>45807.956031324611</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>11</v>
@@ -3333,13 +3297,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>115</v>
+        <v>1474</v>
       </c>
       <c r="C116" s="2">
-        <v>45807.956031324611</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>11</v>
@@ -3356,13 +3320,13 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>116</v>
+        <v>1475</v>
       </c>
       <c r="C117" s="2">
-        <v>45807.956031324611</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>11</v>
@@ -3374,18 +3338,18 @@
         <v>12</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>117</v>
+        <v>1476</v>
       </c>
       <c r="C118" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>11</v>
@@ -3397,18 +3361,18 @@
         <v>12</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>118</v>
+        <v>1477</v>
       </c>
       <c r="C119" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>11</v>
@@ -3420,18 +3384,18 @@
         <v>12</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>119</v>
+        <v>1478</v>
       </c>
       <c r="C120" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>11</v>
@@ -3443,18 +3407,18 @@
         <v>12</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>120</v>
+        <v>1479</v>
       </c>
       <c r="C121" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>11</v>
@@ -3466,18 +3430,18 @@
         <v>12</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>121</v>
+        <v>1480</v>
       </c>
       <c r="C122" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>38</v>
+        <v>59</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -3489,18 +3453,18 @@
         <v>12</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>122</v>
+        <v>1481</v>
       </c>
       <c r="C123" s="2">
-        <v>45807.956031381131</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -3517,13 +3481,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>123</v>
+        <v>1482</v>
       </c>
       <c r="C124" s="2">
-        <v>45807.95603143765</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>11</v>
@@ -3535,18 +3499,18 @@
         <v>12</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>124</v>
+        <v>1483</v>
       </c>
       <c r="C125" s="2">
-        <v>45807.95603143765</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>11</v>
@@ -3558,18 +3522,18 @@
         <v>12</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>125</v>
+        <v>1484</v>
       </c>
       <c r="C126" s="2">
-        <v>45807.95603143765</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>11</v>
@@ -3581,18 +3545,18 @@
         <v>12</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>126</v>
+        <v>1485</v>
       </c>
       <c r="C127" s="2">
-        <v>45807.95603143765</v>
+        <v>45808.045260801038</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>11</v>
@@ -3604,18 +3568,18 @@
         <v>12</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>127</v>
+        <v>1486</v>
       </c>
       <c r="C128" s="2">
-        <v>45807.95603143765</v>
+        <v>45808.045260857558</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>11</v>
@@ -3627,18 +3591,18 @@
         <v>12</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>128</v>
+        <v>1487</v>
       </c>
       <c r="C129" s="2">
-        <v>45807.956031494155</v>
+        <v>45808.04584906689</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>11</v>
@@ -3650,18 +3614,18 @@
         <v>12</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>129</v>
+        <v>1488</v>
       </c>
       <c r="C130" s="2">
-        <v>45807.956031550675</v>
+        <v>45808.045849123409</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>11</v>
@@ -3673,18 +3637,18 @@
         <v>12</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>130</v>
+        <v>1489</v>
       </c>
       <c r="C131" s="2">
-        <v>45807.956103696517</v>
+        <v>45808.045860640967</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>70</v>
+        <v>38</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>11</v>
@@ -3696,18 +3660,18 @@
         <v>12</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>131</v>
+        <v>1490</v>
       </c>
       <c r="C132" s="2">
-        <v>45807.956103696517</v>
+        <v>45808.045860640967</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>11</v>
@@ -3719,15 +3683,15 @@
         <v>12</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>132</v>
+        <v>1491</v>
       </c>
       <c r="C133" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860640967</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>31</v>
@@ -3742,15 +3706,15 @@
         <v>12</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>133</v>
+        <v>1492</v>
       </c>
       <c r="C134" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860640967</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>32</v>
@@ -3765,15 +3729,15 @@
         <v>12</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>134</v>
+        <v>1493</v>
       </c>
       <c r="C135" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860640967</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>33</v>
@@ -3788,15 +3752,15 @@
         <v>12</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>135</v>
+        <v>1494</v>
       </c>
       <c r="C136" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>34</v>
@@ -3811,18 +3775,18 @@
         <v>12</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>136</v>
+        <v>1495</v>
       </c>
       <c r="C137" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>11</v>
@@ -3834,18 +3798,18 @@
         <v>12</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>137</v>
+        <v>1496</v>
       </c>
       <c r="C138" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>11</v>
@@ -3857,18 +3821,18 @@
         <v>12</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>138</v>
+        <v>1497</v>
       </c>
       <c r="C139" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>11</v>
@@ -3880,18 +3844,18 @@
         <v>12</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>139</v>
+        <v>1498</v>
       </c>
       <c r="C140" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>11</v>
@@ -3903,18 +3867,18 @@
         <v>12</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>140</v>
+        <v>1499</v>
       </c>
       <c r="C141" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>11</v>
@@ -3926,18 +3890,18 @@
         <v>12</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>141</v>
+        <v>1500</v>
       </c>
       <c r="C142" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860697479</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>67</v>
+        <v>29</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>11</v>
@@ -3949,18 +3913,18 @@
         <v>12</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>142</v>
+        <v>1501</v>
       </c>
       <c r="C143" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860753999</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>11</v>
@@ -3977,13 +3941,13 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>143</v>
+        <v>1502</v>
       </c>
       <c r="C144" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045860753999</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>11</v>
@@ -3995,18 +3959,18 @@
         <v>12</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>144</v>
+        <v>1503</v>
       </c>
       <c r="C145" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045944417405</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>11</v>
@@ -4018,18 +3982,18 @@
         <v>12</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>145</v>
+        <v>1504</v>
       </c>
       <c r="C146" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045944473924</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>11</v>
@@ -4041,18 +4005,18 @@
         <v>12</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>146</v>
+        <v>1505</v>
       </c>
       <c r="C147" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>11</v>
@@ -4064,18 +4028,18 @@
         <v>12</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>147</v>
+        <v>1506</v>
       </c>
       <c r="C148" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>11</v>
@@ -4087,18 +4051,18 @@
         <v>12</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>148</v>
+        <v>1507</v>
       </c>
       <c r="C149" s="2">
-        <v>45807.956109483632</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>11</v>
@@ -4110,18 +4074,18 @@
         <v>12</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>149</v>
+        <v>1508</v>
       </c>
       <c r="C150" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>11</v>
@@ -4133,18 +4097,18 @@
         <v>12</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>150</v>
+        <v>1509</v>
       </c>
       <c r="C151" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>11</v>
@@ -4161,13 +4125,13 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>151</v>
+        <v>1510</v>
       </c>
       <c r="C152" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>11</v>
@@ -4179,18 +4143,18 @@
         <v>12</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>152</v>
+        <v>1511</v>
       </c>
       <c r="C153" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>11</v>
@@ -4202,18 +4166,18 @@
         <v>12</v>
       </c>
       <c r="I153" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>153</v>
+        <v>1512</v>
       </c>
       <c r="C154" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>11</v>
@@ -4225,18 +4189,18 @@
         <v>12</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>154</v>
+        <v>1513</v>
       </c>
       <c r="C155" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>11</v>
@@ -4253,13 +4217,13 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>155</v>
+        <v>1514</v>
       </c>
       <c r="C156" s="2">
-        <v>45807.956109540151</v>
+        <v>45808.045944530437</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>11</v>
@@ -4276,13 +4240,13 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>156</v>
+        <v>1515</v>
       </c>
       <c r="C157" s="2">
-        <v>45807.956109596664</v>
+        <v>45808.045944586956</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>11</v>
@@ -4299,13 +4263,13 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>157</v>
+        <v>1516</v>
       </c>
       <c r="C158" s="2">
-        <v>45807.956117350346</v>
+        <v>45808.045944586956</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>11</v>
@@ -4317,18 +4281,18 @@
         <v>12</v>
       </c>
       <c r="I158" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>158</v>
+        <v>1517</v>
       </c>
       <c r="C159" s="2">
-        <v>45807.956117350346</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>11</v>
@@ -4340,18 +4304,18 @@
         <v>12</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>159</v>
+        <v>1518</v>
       </c>
       <c r="C160" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>11</v>
@@ -4363,18 +4327,18 @@
         <v>12</v>
       </c>
       <c r="I160" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>160</v>
+        <v>1519</v>
       </c>
       <c r="C161" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>11</v>
@@ -4386,18 +4350,18 @@
         <v>12</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>161</v>
+        <v>1520</v>
       </c>
       <c r="C162" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>11</v>
@@ -4409,18 +4373,18 @@
         <v>12</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>162</v>
+        <v>1521</v>
       </c>
       <c r="C163" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>11</v>
@@ -4432,18 +4396,18 @@
         <v>12</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>163</v>
+        <v>1522</v>
       </c>
       <c r="C164" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>11</v>
@@ -4455,18 +4419,18 @@
         <v>12</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>164</v>
+        <v>1523</v>
       </c>
       <c r="C165" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>11</v>
@@ -4478,18 +4442,18 @@
         <v>12</v>
       </c>
       <c r="I165" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>165</v>
+        <v>1524</v>
       </c>
       <c r="C166" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>11</v>
@@ -4501,18 +4465,18 @@
         <v>12</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>166</v>
+        <v>1525</v>
       </c>
       <c r="C167" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944643462</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>11</v>
@@ -4524,15 +4488,15 @@
         <v>12</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>167</v>
+        <v>1526</v>
       </c>
       <c r="C168" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944699981</v>
       </c>
       <c r="D168" s="3" t="s">
         <v>47</v>
@@ -4547,18 +4511,18 @@
         <v>12</v>
       </c>
       <c r="I168" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>168</v>
+        <v>1527</v>
       </c>
       <c r="C169" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944699981</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>11</v>
@@ -4570,18 +4534,18 @@
         <v>12</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>169</v>
+        <v>1528</v>
       </c>
       <c r="C170" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944699981</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>11</v>
@@ -4593,18 +4557,18 @@
         <v>12</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>170</v>
+        <v>1529</v>
       </c>
       <c r="C171" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045944824313</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>11</v>
@@ -4616,18 +4580,18 @@
         <v>12</v>
       </c>
       <c r="I171" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>171</v>
+        <v>1530</v>
       </c>
       <c r="C172" s="2">
-        <v>45807.956117418158</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>11</v>
@@ -4639,18 +4603,18 @@
         <v>12</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>172</v>
+        <v>1531</v>
       </c>
       <c r="C173" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>11</v>
@@ -4667,13 +4631,13 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>173</v>
+        <v>1532</v>
       </c>
       <c r="C174" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>11</v>
@@ -4690,13 +4654,13 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>174</v>
+        <v>1533</v>
       </c>
       <c r="C175" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>11</v>
@@ -4708,18 +4672,18 @@
         <v>12</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>175</v>
+        <v>1534</v>
       </c>
       <c r="C176" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>11</v>
@@ -4731,18 +4695,18 @@
         <v>12</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>176</v>
+        <v>1535</v>
       </c>
       <c r="C177" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>11</v>
@@ -4754,18 +4718,18 @@
         <v>12</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>177</v>
+        <v>1536</v>
       </c>
       <c r="C178" s="2">
-        <v>45807.956117474678</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>11</v>
@@ -4777,18 +4741,18 @@
         <v>12</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>178</v>
+        <v>1537</v>
       </c>
       <c r="C179" s="2">
-        <v>45807.956117531183</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>11</v>
@@ -4805,13 +4769,13 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>179</v>
+        <v>1538</v>
       </c>
       <c r="C180" s="2">
-        <v>45807.956117870279</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>11</v>
@@ -4828,13 +4792,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>180</v>
+        <v>1539</v>
       </c>
       <c r="C181" s="2">
-        <v>45807.956117870279</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>11</v>
@@ -4851,13 +4815,13 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>181</v>
+        <v>1540</v>
       </c>
       <c r="C182" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>11</v>
@@ -4869,18 +4833,18 @@
         <v>12</v>
       </c>
       <c r="I182" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>182</v>
+        <v>1541</v>
       </c>
       <c r="C183" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>11</v>
@@ -4897,13 +4861,13 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>183</v>
+        <v>1542</v>
       </c>
       <c r="C184" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>11</v>
@@ -4915,18 +4879,18 @@
         <v>12</v>
       </c>
       <c r="I184" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>184</v>
+        <v>1543</v>
       </c>
       <c r="C185" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>11</v>
@@ -4938,18 +4902,18 @@
         <v>12</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>185</v>
+        <v>1544</v>
       </c>
       <c r="C186" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>11</v>
@@ -4961,18 +4925,18 @@
         <v>12</v>
       </c>
       <c r="I186" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A187" s="1">
-        <v>186</v>
+        <v>1545</v>
       </c>
       <c r="C187" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>11</v>
@@ -4984,18 +4948,18 @@
         <v>12</v>
       </c>
       <c r="I187" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A188" s="1">
-        <v>187</v>
+        <v>1546</v>
       </c>
       <c r="C188" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945457277</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>11</v>
@@ -5012,13 +4976,13 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A189" s="1">
-        <v>188</v>
+        <v>1547</v>
       </c>
       <c r="C189" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945513797</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>11</v>
@@ -5030,18 +4994,18 @@
         <v>12</v>
       </c>
       <c r="I189" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A190" s="1">
-        <v>189</v>
+        <v>1548</v>
       </c>
       <c r="C190" s="2">
-        <v>45807.956176407519</v>
+        <v>45808.045945513797</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>11</v>
@@ -5053,15 +5017,15 @@
         <v>12</v>
       </c>
       <c r="I190" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A191" s="1">
-        <v>190</v>
+        <v>1549</v>
       </c>
       <c r="C191" s="2">
-        <v>45807.956176464038</v>
+        <v>45808.045945513797</v>
       </c>
       <c r="D191" s="3" t="s">
         <v>39</v>
@@ -5076,18 +5040,18 @@
         <v>12</v>
       </c>
       <c r="I191" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A192" s="1">
-        <v>191</v>
+        <v>1550</v>
       </c>
       <c r="C192" s="2">
-        <v>45807.956176464038</v>
+        <v>45808.045945570302</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>11</v>
@@ -5104,13 +5068,13 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A193" s="1">
-        <v>192</v>
+        <v>1551</v>
       </c>
       <c r="C193" s="2">
-        <v>45807.956261506406</v>
+        <v>45808.045945570302</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>11</v>
@@ -5122,18 +5086,18 @@
         <v>12</v>
       </c>
       <c r="I193" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A194" s="1">
-        <v>193</v>
+        <v>1552</v>
       </c>
       <c r="C194" s="2">
-        <v>45807.956261506406</v>
+        <v>45808.045945570302</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>11</v>
@@ -5145,18 +5109,18 @@
         <v>12</v>
       </c>
       <c r="I194" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A195" s="1">
-        <v>194</v>
+        <v>1553</v>
       </c>
       <c r="C195" s="2">
-        <v>45807.956261562918</v>
+        <v>45808.045945570302</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>11</v>
@@ -5168,18 +5132,18 @@
         <v>12</v>
       </c>
       <c r="I195" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A196" s="1">
-        <v>195</v>
+        <v>1554</v>
       </c>
       <c r="C196" s="2">
-        <v>45807.956261687104</v>
+        <v>45808.045945626822</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>11</v>
@@ -5196,13 +5160,13 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A197" s="1">
-        <v>196</v>
+        <v>1555</v>
       </c>
       <c r="C197" s="2">
-        <v>45807.956262489613</v>
+        <v>45808.045945626822</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>11</v>
@@ -5219,13 +5183,13 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A198" s="1">
-        <v>197</v>
+        <v>1556</v>
       </c>
       <c r="C198" s="2">
-        <v>45807.956262489613</v>
+        <v>45808.045945626822</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>11</v>
@@ -5242,13 +5206,13 @@
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A199" s="1">
-        <v>198</v>
+        <v>1557</v>
       </c>
       <c r="C199" s="2">
-        <v>45807.956320506928</v>
+        <v>45808.045945626822</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>11</v>
@@ -5265,13 +5229,13 @@
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A200" s="1">
-        <v>199</v>
+        <v>1558</v>
       </c>
       <c r="C200" s="2">
-        <v>45807.956320506928</v>
+        <v>45808.045945626822</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>11</v>
@@ -5288,13 +5252,13 @@
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A201" s="1">
-        <v>200</v>
+        <v>1559</v>
       </c>
       <c r="C201" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945683334</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>11</v>
@@ -5306,18 +5270,18 @@
         <v>12</v>
       </c>
       <c r="I201" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A202" s="1">
-        <v>201</v>
+        <v>1560</v>
       </c>
       <c r="C202" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945683334</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>11</v>
@@ -5329,18 +5293,18 @@
         <v>12</v>
       </c>
       <c r="I202" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A203" s="1">
-        <v>202</v>
+        <v>1561</v>
       </c>
       <c r="C203" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945683334</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>11</v>
@@ -5352,18 +5316,18 @@
         <v>12</v>
       </c>
       <c r="I203" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A204" s="1">
-        <v>203</v>
+        <v>1562</v>
       </c>
       <c r="C204" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945683334</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>11</v>
@@ -5375,18 +5339,18 @@
         <v>12</v>
       </c>
       <c r="I204" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A205" s="1">
-        <v>204</v>
+        <v>1563</v>
       </c>
       <c r="C205" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945683334</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>11</v>
@@ -5403,13 +5367,13 @@
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A206" s="1">
-        <v>205</v>
+        <v>1564</v>
       </c>
       <c r="C206" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945751161</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>11</v>
@@ -5426,13 +5390,13 @@
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A207" s="1">
-        <v>206</v>
+        <v>1565</v>
       </c>
       <c r="C207" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945920705</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>11</v>
@@ -5444,18 +5408,18 @@
         <v>12</v>
       </c>
       <c r="I207" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A208" s="1">
-        <v>207</v>
+        <v>1566</v>
       </c>
       <c r="C208" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945920705</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>11</v>
@@ -5472,13 +5436,13 @@
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A209" s="1">
-        <v>208</v>
+        <v>1567</v>
       </c>
       <c r="C209" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945920705</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>61</v>
+        <v>42</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>11</v>
@@ -5495,13 +5459,13 @@
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A210" s="1">
-        <v>209</v>
+        <v>1568</v>
       </c>
       <c r="C210" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045945920705</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>11</v>
@@ -5518,13 +5482,13 @@
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A211" s="1">
-        <v>210</v>
+        <v>1569</v>
       </c>
       <c r="C211" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.04594597721</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>11</v>
@@ -5541,13 +5505,13 @@
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A212" s="1">
-        <v>211</v>
+        <v>1570</v>
       </c>
       <c r="C212" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045957212205</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>11</v>
@@ -5559,18 +5523,18 @@
         <v>12</v>
       </c>
       <c r="I212" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A213" s="1">
-        <v>212</v>
+        <v>1571</v>
       </c>
       <c r="C213" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045957212205</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>11</v>
@@ -5582,18 +5546,18 @@
         <v>12</v>
       </c>
       <c r="I213" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A214" s="1">
-        <v>213</v>
+        <v>1572</v>
       </c>
       <c r="C214" s="2">
-        <v>45807.956320789497</v>
+        <v>45808.045957212205</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>11</v>
@@ -5605,18 +5569,18 @@
         <v>12</v>
       </c>
       <c r="I214" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A215" s="1">
-        <v>214</v>
+        <v>1573</v>
       </c>
       <c r="C215" s="2">
-        <v>45807.956320846009</v>
+        <v>45808.04595726871</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>11</v>
@@ -5628,18 +5592,18 @@
         <v>12</v>
       </c>
       <c r="I215" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A216" s="1">
-        <v>215</v>
+        <v>1574</v>
       </c>
       <c r="C216" s="2">
-        <v>45807.956320846009</v>
+        <v>45808.04595726871</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>55</v>
+        <v>25</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>11</v>
@@ -5651,18 +5615,18 @@
         <v>12</v>
       </c>
       <c r="I216" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A217" s="1">
-        <v>216</v>
+        <v>1575</v>
       </c>
       <c r="C217" s="2">
-        <v>45807.956320846009</v>
+        <v>45808.04595726871</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>11</v>
@@ -5674,18 +5638,18 @@
         <v>12</v>
       </c>
       <c r="I217" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A218" s="1">
-        <v>217</v>
+        <v>1576</v>
       </c>
       <c r="C218" s="2">
-        <v>45807.956320846009</v>
+        <v>45808.04595726871</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>11</v>
@@ -5697,18 +5661,18 @@
         <v>12</v>
       </c>
       <c r="I218" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A219" s="1">
-        <v>218</v>
+        <v>1577</v>
       </c>
       <c r="C219" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.04595726871</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>11</v>
@@ -5720,18 +5684,18 @@
         <v>12</v>
       </c>
       <c r="I219" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A220" s="1">
-        <v>219</v>
+        <v>1578</v>
       </c>
       <c r="C220" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.04595732523</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>11</v>
@@ -5743,18 +5707,18 @@
         <v>12</v>
       </c>
       <c r="I220" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A221" s="1">
-        <v>220</v>
+        <v>1579</v>
       </c>
       <c r="C221" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.04595732523</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>11</v>
@@ -5766,18 +5730,18 @@
         <v>12</v>
       </c>
       <c r="I221" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A222" s="1">
-        <v>221</v>
+        <v>1580</v>
       </c>
       <c r="C222" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.046017354463</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>11</v>
@@ -5789,18 +5753,18 @@
         <v>12</v>
       </c>
       <c r="I222" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A223" s="1">
-        <v>222</v>
+        <v>1581</v>
       </c>
       <c r="C223" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.046017354463</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>11</v>
@@ -5812,18 +5776,18 @@
         <v>12</v>
       </c>
       <c r="I223" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A224" s="1">
-        <v>223</v>
+        <v>1582</v>
       </c>
       <c r="C224" s="2">
-        <v>45807.956320913821</v>
+        <v>45808.046017354463</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>11</v>
@@ -5840,13 +5804,13 @@
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A225" s="1">
-        <v>224</v>
+        <v>1583</v>
       </c>
       <c r="C225" s="2">
-        <v>45807.956320970341</v>
+        <v>45808.046017422275</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>11</v>
@@ -5858,18 +5822,18 @@
         <v>12</v>
       </c>
       <c r="I225" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A226" s="1">
-        <v>225</v>
+        <v>1584</v>
       </c>
       <c r="C226" s="2">
-        <v>45807.956320970341</v>
+        <v>45808.046017422275</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>11</v>
@@ -5881,18 +5845,18 @@
         <v>12</v>
       </c>
       <c r="I226" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A227" s="1">
-        <v>226</v>
+        <v>1585</v>
       </c>
       <c r="C227" s="2">
-        <v>45807.956320970341</v>
+        <v>45808.046017422275</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>11</v>
@@ -5904,18 +5868,18 @@
         <v>12</v>
       </c>
       <c r="I227" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A228" s="1">
-        <v>227</v>
+        <v>1586</v>
       </c>
       <c r="C228" s="2">
-        <v>45807.956320970341</v>
+        <v>45808.046017422275</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>11</v>
@@ -5927,18 +5891,18 @@
         <v>12</v>
       </c>
       <c r="I228" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A229" s="1">
-        <v>228</v>
+        <v>1587</v>
       </c>
       <c r="C229" s="2">
-        <v>45807.956320970341</v>
+        <v>45808.046017478795</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>11</v>
@@ -5950,18 +5914,18 @@
         <v>12</v>
       </c>
       <c r="I229" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A230" s="1">
-        <v>229</v>
+        <v>1588</v>
       </c>
       <c r="C230" s="2">
-        <v>45807.956321026861</v>
+        <v>45808.046029109391</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>11</v>
@@ -5973,18 +5937,18 @@
         <v>12</v>
       </c>
       <c r="I230" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A231" s="1">
-        <v>230</v>
+        <v>1589</v>
       </c>
       <c r="C231" s="2">
-        <v>45807.956321083373</v>
+        <v>45808.046029109391</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>11</v>
@@ -5996,18 +5960,18 @@
         <v>12</v>
       </c>
       <c r="I231" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A232" s="1">
-        <v>231</v>
+        <v>1590</v>
       </c>
       <c r="C232" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029109391</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>11</v>
@@ -6019,18 +5983,18 @@
         <v>12</v>
       </c>
       <c r="I232" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A233" s="1">
-        <v>232</v>
+        <v>1591</v>
       </c>
       <c r="C233" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029165896</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>11</v>
@@ -6042,18 +6006,18 @@
         <v>12</v>
       </c>
       <c r="I233" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A234" s="1">
-        <v>233</v>
+        <v>1592</v>
       </c>
       <c r="C234" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029165896</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>11</v>
@@ -6065,18 +6029,18 @@
         <v>12</v>
       </c>
       <c r="I234" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A235" s="1">
-        <v>234</v>
+        <v>1593</v>
       </c>
       <c r="C235" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029165896</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>11</v>
@@ -6088,18 +6052,18 @@
         <v>12</v>
       </c>
       <c r="I235" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A236" s="1">
-        <v>235</v>
+        <v>1594</v>
       </c>
       <c r="C236" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029165896</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>11</v>
@@ -6111,18 +6075,18 @@
         <v>12</v>
       </c>
       <c r="I236" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A237" s="1">
-        <v>236</v>
+        <v>1595</v>
       </c>
       <c r="C237" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029165896</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>11</v>
@@ -6134,18 +6098,18 @@
         <v>12</v>
       </c>
       <c r="I237" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A238" s="1">
-        <v>237</v>
+        <v>1596</v>
       </c>
       <c r="C238" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029233716</v>
       </c>
       <c r="D238" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>11</v>
@@ -6162,13 +6126,13 @@
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A239" s="1">
-        <v>238</v>
+        <v>1597</v>
       </c>
       <c r="C239" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046029233716</v>
       </c>
       <c r="D239" s="3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F239" s="3" t="s">
         <v>11</v>
@@ -6180,18 +6144,18 @@
         <v>12</v>
       </c>
       <c r="I239" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A240" s="1">
-        <v>239</v>
+        <v>1598</v>
       </c>
       <c r="C240" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089500167</v>
       </c>
       <c r="D240" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>11</v>
@@ -6208,13 +6172,13 @@
     </row>
     <row r="241" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A241" s="1">
-        <v>240</v>
+        <v>1599</v>
       </c>
       <c r="C241" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089500167</v>
       </c>
       <c r="D241" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F241" s="3" t="s">
         <v>11</v>
@@ -6226,18 +6190,18 @@
         <v>12</v>
       </c>
       <c r="I241" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A242" s="1">
-        <v>241</v>
+        <v>1600</v>
       </c>
       <c r="C242" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089500167</v>
       </c>
       <c r="D242" s="3" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>11</v>
@@ -6254,13 +6218,13 @@
     </row>
     <row r="243" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A243" s="1">
-        <v>242</v>
+        <v>1601</v>
       </c>
       <c r="C243" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089556679</v>
       </c>
       <c r="D243" s="3" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F243" s="3" t="s">
         <v>11</v>
@@ -6272,18 +6236,18 @@
         <v>12</v>
       </c>
       <c r="I243" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="244" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A244" s="1">
-        <v>243</v>
+        <v>1602</v>
       </c>
       <c r="C244" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089556679</v>
       </c>
       <c r="D244" s="3" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>11</v>
@@ -6295,18 +6259,18 @@
         <v>12</v>
       </c>
       <c r="I244" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="245" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A245" s="1">
-        <v>244</v>
+        <v>1603</v>
       </c>
       <c r="C245" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089556679</v>
       </c>
       <c r="D245" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F245" s="3" t="s">
         <v>11</v>
@@ -6318,18 +6282,18 @@
         <v>12</v>
       </c>
       <c r="I245" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A246" s="1">
-        <v>245</v>
+        <v>1604</v>
       </c>
       <c r="C246" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089556679</v>
       </c>
       <c r="D246" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>11</v>
@@ -6341,18 +6305,18 @@
         <v>12</v>
       </c>
       <c r="I246" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="247" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A247" s="1">
-        <v>246</v>
+        <v>1605</v>
       </c>
       <c r="C247" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046089613192</v>
       </c>
       <c r="D247" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F247" s="3" t="s">
         <v>11</v>
@@ -6364,18 +6328,18 @@
         <v>12</v>
       </c>
       <c r="I247" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="248" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A248" s="1">
-        <v>247</v>
+        <v>1606</v>
       </c>
       <c r="C248" s="2">
-        <v>45807.956326294036</v>
+        <v>45808.046101187269</v>
       </c>
       <c r="D248" s="3" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>11</v>
@@ -6387,18 +6351,18 @@
         <v>12</v>
       </c>
       <c r="I248" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="249" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A249" s="1">
-        <v>248</v>
+        <v>1607</v>
       </c>
       <c r="C249" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101187269</v>
       </c>
       <c r="D249" s="3" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F249" s="3" t="s">
         <v>11</v>
@@ -6410,18 +6374,18 @@
         <v>12</v>
       </c>
       <c r="I249" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="250" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A250" s="1">
-        <v>249</v>
+        <v>1608</v>
       </c>
       <c r="C250" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101187269</v>
       </c>
       <c r="D250" s="3" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>11</v>
@@ -6433,18 +6397,18 @@
         <v>12</v>
       </c>
       <c r="I250" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="251" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A251" s="1">
-        <v>250</v>
+        <v>1609</v>
       </c>
       <c r="C251" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101243781</v>
       </c>
       <c r="D251" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F251" s="3" t="s">
         <v>11</v>
@@ -6456,18 +6420,18 @@
         <v>12</v>
       </c>
       <c r="I251" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="252" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A252" s="1">
-        <v>251</v>
+        <v>1610</v>
       </c>
       <c r="C252" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101243781</v>
       </c>
       <c r="D252" s="3" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>11</v>
@@ -6479,18 +6443,18 @@
         <v>12</v>
       </c>
       <c r="I252" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="253" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A253" s="1">
-        <v>252</v>
+        <v>1611</v>
       </c>
       <c r="C253" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101243781</v>
       </c>
       <c r="D253" s="3" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="F253" s="3" t="s">
         <v>11</v>
@@ -6502,18 +6466,18 @@
         <v>12</v>
       </c>
       <c r="I253" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="254" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A254" s="1">
-        <v>253</v>
+        <v>1612</v>
       </c>
       <c r="C254" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101243781</v>
       </c>
       <c r="D254" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>11</v>
@@ -6525,18 +6489,18 @@
         <v>12</v>
       </c>
       <c r="I254" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="255" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A255" s="1">
-        <v>254</v>
+        <v>1613</v>
       </c>
       <c r="C255" s="2">
-        <v>45807.956326350548</v>
+        <v>45808.046101243781</v>
       </c>
       <c r="D255" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F255" s="3" t="s">
         <v>11</v>
@@ -6548,18 +6512,18 @@
         <v>12</v>
       </c>
       <c r="I255" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="256" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A256" s="1">
-        <v>255</v>
+        <v>1614</v>
       </c>
       <c r="C256" s="2">
-        <v>45807.956326407068</v>
+        <v>45808.046101300293</v>
       </c>
       <c r="D256" s="3" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>11</v>
@@ -6576,13 +6540,13 @@
     </row>
     <row r="257" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A257" s="1">
-        <v>256</v>
+        <v>1615</v>
       </c>
       <c r="C257" s="2">
-        <v>45807.956407063888</v>
+        <v>45808.046101300293</v>
       </c>
       <c r="D257" s="3" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F257" s="3" t="s">
         <v>11</v>
@@ -6594,18 +6558,18 @@
         <v>12</v>
       </c>
       <c r="I257" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="258" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A258" s="1">
-        <v>257</v>
+        <v>1616</v>
       </c>
       <c r="C258" s="2">
-        <v>45807.956407063888</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D258" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>11</v>
@@ -6617,18 +6581,18 @@
         <v>12</v>
       </c>
       <c r="I258" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="259" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A259" s="1">
-        <v>258</v>
+        <v>1617</v>
       </c>
       <c r="C259" s="2">
-        <v>45807.95640717692</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="F259" s="3" t="s">
         <v>11</v>
@@ -6640,18 +6604,18 @@
         <v>12</v>
       </c>
       <c r="I259" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="260" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A260" s="1">
-        <v>259</v>
+        <v>1618</v>
       </c>
       <c r="C260" s="2">
-        <v>45807.956407233425</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>11</v>
@@ -6663,18 +6627,18 @@
         <v>12</v>
       </c>
       <c r="I260" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="261" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A261" s="1">
-        <v>260</v>
+        <v>1619</v>
       </c>
       <c r="C261" s="2">
-        <v>45807.956407459489</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D261" s="3" t="s">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="F261" s="3" t="s">
         <v>11</v>
@@ -6691,13 +6655,13 @@
     </row>
     <row r="262" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A262" s="1">
-        <v>261</v>
+        <v>1620</v>
       </c>
       <c r="C262" s="2">
-        <v>45807.956407459489</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D262" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>11</v>
@@ -6709,18 +6673,18 @@
         <v>12</v>
       </c>
       <c r="I262" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A263" s="1">
-        <v>262</v>
+        <v>1621</v>
       </c>
       <c r="C263" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D263" s="3" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="F263" s="3" t="s">
         <v>11</v>
@@ -6732,18 +6696,18 @@
         <v>12</v>
       </c>
       <c r="I263" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="264" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A264" s="1">
-        <v>263</v>
+        <v>1622</v>
       </c>
       <c r="C264" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>11</v>
@@ -6755,18 +6719,18 @@
         <v>12</v>
       </c>
       <c r="I264" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="265" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A265" s="1">
-        <v>264</v>
+        <v>1623</v>
       </c>
       <c r="C265" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D265" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F265" s="3" t="s">
         <v>11</v>
@@ -6778,18 +6742,18 @@
         <v>12</v>
       </c>
       <c r="I265" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="266" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A266" s="1">
-        <v>265</v>
+        <v>1624</v>
       </c>
       <c r="C266" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D266" s="3" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>11</v>
@@ -6801,18 +6765,18 @@
         <v>12</v>
       </c>
       <c r="I266" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="267" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A267" s="1">
-        <v>266</v>
+        <v>1625</v>
       </c>
       <c r="C267" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.04614854604</v>
       </c>
       <c r="D267" s="3" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F267" s="3" t="s">
         <v>11</v>
@@ -6824,18 +6788,18 @@
         <v>12</v>
       </c>
       <c r="I267" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="268" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A268" s="1">
-        <v>267</v>
+        <v>1626</v>
       </c>
       <c r="C268" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D268" s="3" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>11</v>
@@ -6852,13 +6816,13 @@
     </row>
     <row r="269" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A269" s="1">
-        <v>268</v>
+        <v>1627</v>
       </c>
       <c r="C269" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F269" s="3" t="s">
         <v>11</v>
@@ -6870,18 +6834,18 @@
         <v>12</v>
       </c>
       <c r="I269" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A270" s="1">
-        <v>269</v>
+        <v>1628</v>
       </c>
       <c r="C270" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D270" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>11</v>
@@ -6893,18 +6857,18 @@
         <v>12</v>
       </c>
       <c r="I270" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="271" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A271" s="1">
-        <v>270</v>
+        <v>1629</v>
       </c>
       <c r="C271" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D271" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F271" s="3" t="s">
         <v>11</v>
@@ -6921,13 +6885,13 @@
     </row>
     <row r="272" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A272" s="1">
-        <v>271</v>
+        <v>1630</v>
       </c>
       <c r="C272" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D272" s="3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>11</v>
@@ -6944,13 +6908,13 @@
     </row>
     <row r="273" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A273" s="1">
-        <v>272</v>
+        <v>1631</v>
       </c>
       <c r="C273" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148613859</v>
       </c>
       <c r="D273" s="3" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="F273" s="3" t="s">
         <v>11</v>
@@ -6967,13 +6931,13 @@
     </row>
     <row r="274" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A274" s="1">
-        <v>273</v>
+        <v>1632</v>
       </c>
       <c r="C274" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046148670372</v>
       </c>
       <c r="D274" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>11</v>
@@ -6990,13 +6954,13 @@
     </row>
     <row r="275" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A275" s="1">
-        <v>274</v>
+        <v>1633</v>
       </c>
       <c r="C275" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046221155317</v>
       </c>
       <c r="D275" s="3" t="s">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="F275" s="3" t="s">
         <v>11</v>
@@ -7008,18 +6972,18 @@
         <v>12</v>
       </c>
       <c r="I275" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="276" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A276" s="1">
-        <v>275</v>
+        <v>1634</v>
       </c>
       <c r="C276" s="2">
-        <v>45807.956466166281</v>
+        <v>45808.046221155317</v>
       </c>
       <c r="D276" s="3" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>11</v>
@@ -7031,18 +6995,18 @@
         <v>12</v>
       </c>
       <c r="I276" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="277" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A277" s="1">
-        <v>276</v>
+        <v>1635</v>
       </c>
       <c r="C277" s="2">
-        <v>45807.956466222793</v>
+        <v>45808.046221437886</v>
       </c>
       <c r="D277" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F277" s="3" t="s">
         <v>11</v>
@@ -7054,18 +7018,18 @@
         <v>12</v>
       </c>
       <c r="I277" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="278" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A278" s="1">
-        <v>277</v>
+        <v>1636</v>
       </c>
       <c r="C278" s="2">
-        <v>45807.956466222793</v>
+        <v>45808.046221437886</v>
       </c>
       <c r="D278" s="3" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>11</v>
@@ -7077,18 +7041,18 @@
         <v>12</v>
       </c>
       <c r="I278" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="279" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A279" s="1">
-        <v>278</v>
+        <v>1637</v>
       </c>
       <c r="C279" s="2">
-        <v>45807.956466222793</v>
+        <v>45808.046221437886</v>
       </c>
       <c r="D279" s="3" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F279" s="3" t="s">
         <v>11</v>
@@ -7100,18 +7064,18 @@
         <v>12</v>
       </c>
       <c r="I279" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="280" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A280" s="1">
-        <v>279</v>
+        <v>1638</v>
       </c>
       <c r="C280" s="2">
-        <v>45807.956466222793</v>
+        <v>45808.046226942279</v>
       </c>
       <c r="D280" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>11</v>
@@ -7123,18 +7087,18 @@
         <v>12</v>
       </c>
       <c r="I280" s="3" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
     </row>
     <row r="281" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A281" s="1">
-        <v>280</v>
+        <v>1639</v>
       </c>
       <c r="C281" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046226942279</v>
       </c>
       <c r="D281" s="3" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="F281" s="3" t="s">
         <v>11</v>
@@ -7146,18 +7110,18 @@
         <v>12</v>
       </c>
       <c r="I281" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="282" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A282" s="1">
-        <v>281</v>
+        <v>1640</v>
       </c>
       <c r="C282" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046226942279</v>
       </c>
       <c r="D282" s="3" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>11</v>
@@ -7169,18 +7133,18 @@
         <v>12</v>
       </c>
       <c r="I282" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="283" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A283" s="1">
-        <v>282</v>
+        <v>1641</v>
       </c>
       <c r="C283" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046420593368</v>
       </c>
       <c r="D283" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F283" s="3" t="s">
         <v>11</v>
@@ -7192,18 +7156,18 @@
         <v>12</v>
       </c>
       <c r="I283" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="284" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A284" s="1">
-        <v>283</v>
+        <v>1642</v>
       </c>
       <c r="C284" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046420649887</v>
       </c>
       <c r="D284" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>11</v>
@@ -7215,18 +7179,18 @@
         <v>12</v>
       </c>
       <c r="I284" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="285" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A285" s="1">
-        <v>284</v>
+        <v>1643</v>
       </c>
       <c r="C285" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046467319175</v>
       </c>
       <c r="D285" s="3" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="F285" s="3" t="s">
         <v>11</v>
@@ -7238,15 +7202,15 @@
         <v>12</v>
       </c>
       <c r="I285" s="3" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="286" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A286" s="1">
-        <v>285</v>
+        <v>1644</v>
       </c>
       <c r="C286" s="2">
-        <v>45807.956466279305</v>
+        <v>45808.046467319175</v>
       </c>
       <c r="D286" s="3" t="s">
         <v>15</v>
@@ -7266,13 +7230,13 @@
     </row>
     <row r="287" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A287" s="1">
-        <v>286</v>
+        <v>1645</v>
       </c>
       <c r="C287" s="2">
-        <v>45807.956466347132</v>
+        <v>45808.046473106137</v>
       </c>
       <c r="D287" s="3" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="F287" s="3" t="s">
         <v>11</v>
@@ -7284,978 +7248,12 @@
         <v>12</v>
       </c>
       <c r="I287" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A288" s="1">
-        <v>287</v>
-      </c>
-      <c r="C288" s="2">
-        <v>45807.956466347132</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G288" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H288" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I288" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A289" s="1">
-        <v>288</v>
-      </c>
-      <c r="C289" s="2">
-        <v>45807.956466347132</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G289" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H289" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I289" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A290" s="1">
-        <v>289</v>
-      </c>
-      <c r="C290" s="2">
-        <v>45807.956466347132</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G290" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H290" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I290" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A291" s="1">
-        <v>290</v>
-      </c>
-      <c r="C291" s="2">
-        <v>45807.956466347132</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F291" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G291" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H291" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I291" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A292" s="1">
-        <v>291</v>
-      </c>
-      <c r="C292" s="2">
-        <v>45807.956466403637</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G292" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H292" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I292" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A293" s="1">
-        <v>292</v>
-      </c>
-      <c r="C293" s="2">
-        <v>45807.956466460157</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G293" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H293" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I293" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A294" s="1">
-        <v>293</v>
-      </c>
-      <c r="C294" s="2">
-        <v>45807.956540154359</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G294" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H294" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I294" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="1">
-        <v>294</v>
-      </c>
-      <c r="C295" s="2">
-        <v>45807.956540154359</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F295" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G295" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H295" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I295" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A296" s="1">
-        <v>295</v>
-      </c>
-      <c r="C296" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F296" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G296" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H296" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I296" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="1">
-        <v>296</v>
-      </c>
-      <c r="C297" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F297" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G297" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H297" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I297" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A298" s="1">
-        <v>297</v>
-      </c>
-      <c r="C298" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D298" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F298" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G298" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H298" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I298" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A299" s="1">
-        <v>298</v>
-      </c>
-      <c r="C299" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D299" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G299" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H299" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I299" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A300" s="1">
-        <v>299</v>
-      </c>
-      <c r="C300" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G300" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H300" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I300" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="1">
-        <v>300</v>
-      </c>
-      <c r="C301" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G301" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H301" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I301" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A302" s="1">
-        <v>301</v>
-      </c>
-      <c r="C302" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G302" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H302" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I302" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="1">
-        <v>302</v>
-      </c>
-      <c r="C303" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G303" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H303" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I303" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A304" s="1">
-        <v>303</v>
-      </c>
-      <c r="C304" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F304" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G304" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H304" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I304" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A305" s="1">
-        <v>304</v>
-      </c>
-      <c r="C305" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D305" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F305" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G305" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H305" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I305" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A306" s="1">
-        <v>305</v>
-      </c>
-      <c r="C306" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F306" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G306" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H306" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I306" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A307" s="1">
-        <v>306</v>
-      </c>
-      <c r="C307" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D307" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F307" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G307" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H307" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I307" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A308" s="1">
-        <v>307</v>
-      </c>
-      <c r="C308" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D308" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F308" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G308" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H308" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I308" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A309" s="1">
-        <v>308</v>
-      </c>
-      <c r="C309" s="2">
-        <v>45807.956540267391</v>
-      </c>
-      <c r="D309" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F309" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G309" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H309" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I309" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A310" s="1">
-        <v>309</v>
-      </c>
-      <c r="C310" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D310" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F310" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G310" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H310" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I310" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A311" s="1">
-        <v>310</v>
-      </c>
-      <c r="C311" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D311" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F311" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G311" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H311" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I311" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A312" s="1">
-        <v>311</v>
-      </c>
-      <c r="C312" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D312" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F312" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G312" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H312" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I312" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A313" s="1">
-        <v>312</v>
-      </c>
-      <c r="C313" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D313" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F313" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G313" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H313" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I313" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A314" s="1">
-        <v>313</v>
-      </c>
-      <c r="C314" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D314" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F314" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G314" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H314" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I314" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A315" s="1">
-        <v>314</v>
-      </c>
-      <c r="C315" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D315" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F315" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G315" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H315" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I315" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A316" s="1">
-        <v>315</v>
-      </c>
-      <c r="C316" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D316" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F316" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G316" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H316" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I316" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A317" s="1">
-        <v>316</v>
-      </c>
-      <c r="C317" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D317" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F317" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G317" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H317" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I317" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A318" s="1">
-        <v>317</v>
-      </c>
-      <c r="C318" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D318" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F318" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G318" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H318" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I318" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A319" s="1">
-        <v>318</v>
-      </c>
-      <c r="C319" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D319" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F319" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G319" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H319" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I319" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A320" s="1">
-        <v>319</v>
-      </c>
-      <c r="C320" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D320" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F320" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G320" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H320" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I320" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A321" s="1">
-        <v>320</v>
-      </c>
-      <c r="C321" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D321" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F321" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G321" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H321" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I321" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A322" s="1">
-        <v>321</v>
-      </c>
-      <c r="C322" s="2">
-        <v>45807.956540335203</v>
-      </c>
-      <c r="D322" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F322" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G322" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H322" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I322" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A323" s="1">
-        <v>322</v>
-      </c>
-      <c r="C323" s="2">
-        <v>45807.956540391722</v>
-      </c>
-      <c r="D323" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F323" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G323" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H323" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I323" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A324" s="1">
-        <v>323</v>
-      </c>
-      <c r="C324" s="2">
-        <v>45807.956540391722</v>
-      </c>
-      <c r="D324" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F324" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G324" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H324" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I324" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A325" s="1">
-        <v>324</v>
-      </c>
-      <c r="C325" s="2">
-        <v>45807.956540391722</v>
-      </c>
-      <c r="D325" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F325" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G325" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H325" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I325" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A326" s="1">
-        <v>325</v>
-      </c>
-      <c r="C326" s="2">
-        <v>45807.956540391722</v>
-      </c>
-      <c r="D326" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F326" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G326" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H326" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I326" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A327" s="1">
-        <v>326</v>
-      </c>
-      <c r="C327" s="2">
-        <v>45807.956540448242</v>
-      </c>
-      <c r="D327" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F327" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G327" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H327" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I327" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="328" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A328" s="1">
-        <v>327</v>
-      </c>
-      <c r="C328" s="2">
-        <v>45807.956543115732</v>
-      </c>
-      <c r="D328" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F328" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G328" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H328" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I328" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="329" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A329" s="1">
-        <v>328</v>
-      </c>
-      <c r="C329" s="2">
-        <v>45807.956543115732</v>
-      </c>
-      <c r="D329" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F329" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G329" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H329" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I329" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J329">
-    <sortCondition ref="A2:A329"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J287">
+    <sortCondition ref="A2:A287"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ  ЛО\pmi_lodzt\lonn1_modes\Журнал событий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ЛО\pmi_lodzt\lonn2_modes\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0207E54-E3A5-4326-8855-5F271F84930B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF2FAE22-6300-4359-97C5-492B5A907AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40785" yWindow="4035" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="935" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1305" uniqueCount="64">
   <si>
     <t>№</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Ед. изм.</t>
   </si>
   <si>
-    <t>Виртуальный ключ-51_Опер. вывод</t>
+    <t>Слот M3.Реле1. Статус</t>
   </si>
   <si>
     <t>Хорошее [0]</t>
@@ -66,7 +66,61 @@
     <t>System</t>
   </si>
   <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле3. Статус</t>
+  </si>
+  <si>
     <t>0</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле7. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле8. Статус</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО НН1 / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО НН1 / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО НН1 / ЗАПВ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО НН1 / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО НН2 / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО НН2 / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО НН2 / ЗАПВ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО НН2 / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-51_Опер. вывод</t>
   </si>
   <si>
     <t>Внеш.откл. от СО</t>
@@ -82,15 +136,6 @@
   </si>
   <si>
     <t>Слот M4.Реле2. Статус</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>ЛО Т / ЛО: Срабатывание</t>
@@ -114,61 +159,28 @@
     <t>ПС / ПС: Пуск (имп)</t>
   </si>
   <si>
-    <t>Слот M3.Реле1. Статус</t>
-  </si>
-  <si>
     <t>Слот M3.Реле2. Статус</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
   </si>
   <si>
     <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
   </si>
   <si>
-    <t>Слот M3.Реле3. Статус</t>
-  </si>
-  <si>
     <t>Слот M3.Реле5. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле7. Статус</t>
-  </si>
-  <si>
-    <t>ЛО НН1 / ЛО: Ввод</t>
   </si>
   <si>
     <t>ЛО НН1 / ЛО: Отключение</t>
   </si>
   <si>
-    <t>ЛО НН1 / ЗАПВ: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО НН2 / ЛО: Ввод</t>
-  </si>
-  <si>
     <t>ЛО НН2 / ЛО: Отключение</t>
   </si>
   <si>
-    <t>ЛО НН2 / ЗАПВ: Ввод</t>
+    <t>Виртуальный ключ-58_Опер. вывод</t>
   </si>
   <si>
-    <t>Слот M3.Реле8. Статус</t>
+    <t>ЛО НН1 / ЗАПВ: Запрет АПВ</t>
   </si>
   <si>
-    <t>ЛО НН1 / ЗАПВ: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-55_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ЛО НН2 / ЗАПВ: Запрет АПВ</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ЛО НН1 / ЗАПВ</t>
+    <t>ДВ: ОВ ЛО НН2 / ЗАПВ</t>
   </si>
   <si>
     <t>Слот M8. ДВ4. Статус</t>
@@ -177,46 +189,34 @@
     <t>Слот M3.Реле6. Статус</t>
   </si>
   <si>
-    <t>ЛО НН1 / ЛО: Отключить аварийно</t>
+    <t>ЛО НН2 / ЛО: Отключить аварийно</t>
   </si>
   <si>
-    <t>Слот M3.Реле4. Статус</t>
-  </si>
-  <si>
-    <t>ЛО НН1 / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-54_Опер. вывод</t>
+    <t>Виртуальный ключ-57_Опер. вывод</t>
   </si>
   <si>
     <t>Слот M4.Реле1. Статус</t>
   </si>
   <si>
-    <t>ЛО НН1 / ЗАПВ: Запрет АПВ</t>
+    <t>ЛО НН2 / ЗАПВ: Запрет АПВ</t>
   </si>
   <si>
-    <t>ДВ: ОВ ЛО НН1 / ЛО</t>
+    <t>ДВ: ОВ ЛО НН2 / ЛО</t>
   </si>
   <si>
     <t>Слот M8. ДВ3. Статус</t>
   </si>
   <si>
-    <t>Виртуальный ключ-53_Опер. вывод</t>
+    <t>Виртуальный ключ-56_Опер. вывод</t>
   </si>
   <si>
-    <t>ДВ: ОВ ЛО НН1</t>
+    <t>ДВ: ОВ ЛО НН2</t>
   </si>
   <si>
     <t>Слот M8. ДВ2. Статус</t>
   </si>
   <si>
-    <t>ЛО НН2 / ЛО: Отключить аварийно</t>
-  </si>
-  <si>
-    <t>ЛО НН2 / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ЛО НН2 / ЗАПВ: Оперативный вывод</t>
+    <t>ЛО НН1 / ЛО: Отключить аварийно</t>
   </si>
 </sst>
 </file>
@@ -618,7 +618,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J186"/>
+  <dimension ref="A1:J260"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -666,13 +666,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>4519</v>
+        <v>4923</v>
       </c>
       <c r="C2" s="2">
-        <v>45812.82290883387</v>
+        <v>45812.86431501613</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -684,18 +684,18 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>4520</v>
+        <v>4924</v>
       </c>
       <c r="C3" s="2">
-        <v>45812.82290883387</v>
+        <v>45812.86431501613</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -707,18 +707,18 @@
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>4521</v>
+        <v>4925</v>
       </c>
       <c r="C4" s="2">
-        <v>45812.82290883387</v>
+        <v>45812.864320803092</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -730,18 +730,18 @@
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>4522</v>
+        <v>4926</v>
       </c>
       <c r="C5" s="2">
-        <v>45812.82290883387</v>
+        <v>45812.864320859604</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -758,10 +758,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>4523</v>
+        <v>4927</v>
       </c>
       <c r="C6" s="2">
-        <v>45812.82290889039</v>
+        <v>45812.864320859604</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>22</v>
@@ -776,18 +776,18 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>4524</v>
+        <v>4928</v>
       </c>
       <c r="C7" s="2">
-        <v>45812.82290889039</v>
+        <v>45812.864320859604</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -804,13 +804,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>4525</v>
+        <v>4929</v>
       </c>
       <c r="C8" s="2">
-        <v>45812.822908946895</v>
+        <v>45812.864320916124</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -827,13 +827,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>4526</v>
+        <v>4930</v>
       </c>
       <c r="C9" s="2">
-        <v>45812.822908946895</v>
+        <v>45812.864320916124</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -850,13 +850,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>4527</v>
+        <v>4931</v>
       </c>
       <c r="C10" s="2">
-        <v>45812.822908946895</v>
+        <v>45812.864320916124</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -868,18 +868,18 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>4528</v>
+        <v>4932</v>
       </c>
       <c r="C11" s="2">
-        <v>45812.822909003415</v>
+        <v>45812.864320916124</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -896,13 +896,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>4529</v>
+        <v>4933</v>
       </c>
       <c r="C12" s="2">
-        <v>45812.822909003415</v>
+        <v>45812.864320972629</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>56</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -919,13 +919,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>4530</v>
+        <v>4934</v>
       </c>
       <c r="C13" s="2">
-        <v>45812.822914620985</v>
+        <v>45812.864387467009</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -937,18 +937,18 @@
         <v>12</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>4531</v>
+        <v>4935</v>
       </c>
       <c r="C14" s="2">
-        <v>45812.822914677497</v>
+        <v>45812.864387467009</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -960,18 +960,18 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>4532</v>
+        <v>4936</v>
       </c>
       <c r="C15" s="2">
-        <v>45812.822914677497</v>
+        <v>45812.864387523521</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -983,18 +983,18 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>4533</v>
+        <v>4937</v>
       </c>
       <c r="C16" s="2">
-        <v>45812.82291473401</v>
+        <v>45812.864387523521</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -1006,18 +1006,18 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>4534</v>
+        <v>4938</v>
       </c>
       <c r="C17" s="2">
-        <v>45812.8230109547</v>
+        <v>45812.864387523521</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -1029,18 +1029,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>4535</v>
+        <v>4939</v>
       </c>
       <c r="C18" s="2">
-        <v>45812.8230109547</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -1052,18 +1052,18 @@
         <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>4536</v>
+        <v>4940</v>
       </c>
       <c r="C19" s="2">
-        <v>45812.823011011213</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1075,18 +1075,18 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>4537</v>
+        <v>4941</v>
       </c>
       <c r="C20" s="2">
-        <v>45812.823011011213</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1098,18 +1098,18 @@
         <v>12</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>4538</v>
+        <v>4942</v>
       </c>
       <c r="C21" s="2">
-        <v>45812.823011011213</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1121,15 +1121,15 @@
         <v>12</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>4539</v>
+        <v>4943</v>
       </c>
       <c r="C22" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>38</v>
@@ -1144,18 +1144,18 @@
         <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>4540</v>
+        <v>4944</v>
       </c>
       <c r="C23" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864387580034</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1167,18 +1167,18 @@
         <v>12</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>4541</v>
+        <v>4945</v>
       </c>
       <c r="C24" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864387636553</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -1190,18 +1190,18 @@
         <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>4542</v>
+        <v>4946</v>
       </c>
       <c r="C25" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864387636553</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1213,18 +1213,18 @@
         <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>4543</v>
+        <v>4947</v>
       </c>
       <c r="C26" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864387636553</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1236,18 +1236,18 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>4544</v>
+        <v>4948</v>
       </c>
       <c r="C27" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864533533269</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1259,18 +1259,18 @@
         <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>4545</v>
+        <v>4949</v>
       </c>
       <c r="C28" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864533533269</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1282,18 +1282,18 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>4546</v>
+        <v>4950</v>
       </c>
       <c r="C29" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864533589789</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1305,18 +1305,18 @@
         <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>4547</v>
+        <v>4951</v>
       </c>
       <c r="C30" s="2">
-        <v>45812.823011067732</v>
+        <v>45812.864533589789</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1328,18 +1328,18 @@
         <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>4548</v>
+        <v>4952</v>
       </c>
       <c r="C31" s="2">
-        <v>45812.823011124237</v>
+        <v>45812.864533589789</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1356,13 +1356,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>4549</v>
+        <v>4953</v>
       </c>
       <c r="C32" s="2">
-        <v>45812.823011124237</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1374,18 +1374,18 @@
         <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>4550</v>
+        <v>4954</v>
       </c>
       <c r="C33" s="2">
-        <v>45812.823011124237</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>49</v>
+        <v>63</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1397,18 +1397,18 @@
         <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>4551</v>
+        <v>4955</v>
       </c>
       <c r="C34" s="2">
-        <v>45812.823011124237</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1420,18 +1420,18 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>4552</v>
+        <v>4956</v>
       </c>
       <c r="C35" s="2">
-        <v>45812.823011124237</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1443,18 +1443,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>4553</v>
+        <v>4957</v>
       </c>
       <c r="C36" s="2">
-        <v>45812.823022641809</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1471,13 +1471,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>4554</v>
+        <v>4958</v>
       </c>
       <c r="C37" s="2">
-        <v>45812.823022641809</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1494,13 +1494,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>4555</v>
+        <v>4959</v>
       </c>
       <c r="C38" s="2">
-        <v>45812.823022698314</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1517,13 +1517,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>4556</v>
+        <v>4960</v>
       </c>
       <c r="C39" s="2">
-        <v>45812.823082682342</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1535,18 +1535,18 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>4557</v>
+        <v>4961</v>
       </c>
       <c r="C40" s="2">
-        <v>45812.823082682342</v>
+        <v>45812.864533646294</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1558,18 +1558,18 @@
         <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>4558</v>
+        <v>4962</v>
       </c>
       <c r="C41" s="2">
-        <v>45812.823082682342</v>
+        <v>45812.864533702814</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1581,18 +1581,18 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>4559</v>
+        <v>4963</v>
       </c>
       <c r="C42" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864533702814</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1609,13 +1609,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>4560</v>
+        <v>4964</v>
       </c>
       <c r="C43" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864533702814</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1627,18 +1627,18 @@
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>4561</v>
+        <v>4965</v>
       </c>
       <c r="C44" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864533702814</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1655,13 +1655,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>4562</v>
+        <v>4966</v>
       </c>
       <c r="C45" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864533702814</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1678,13 +1678,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>4563</v>
+        <v>4967</v>
       </c>
       <c r="C46" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864545220371</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1696,18 +1696,18 @@
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>4564</v>
+        <v>4968</v>
       </c>
       <c r="C47" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864545220371</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1719,18 +1719,18 @@
         <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>4565</v>
+        <v>4969</v>
       </c>
       <c r="C48" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864545276891</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>37</v>
+        <v>53</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1742,18 +1742,18 @@
         <v>12</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>4566</v>
+        <v>4970</v>
       </c>
       <c r="C49" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864679994993</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>52</v>
+        <v>32</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1765,18 +1765,18 @@
         <v>12</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>4567</v>
+        <v>4971</v>
       </c>
       <c r="C50" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864679994993</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1788,18 +1788,18 @@
         <v>12</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>4568</v>
+        <v>4972</v>
       </c>
       <c r="C51" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680062805</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1811,18 +1811,18 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>4569</v>
+        <v>4973</v>
       </c>
       <c r="C52" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680062805</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -1834,18 +1834,18 @@
         <v>12</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>4570</v>
+        <v>4974</v>
       </c>
       <c r="C53" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680062805</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1857,18 +1857,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>4571</v>
+        <v>4975</v>
       </c>
       <c r="C54" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1880,18 +1880,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>4572</v>
+        <v>4976</v>
       </c>
       <c r="C55" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1903,18 +1903,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>4573</v>
+        <v>4977</v>
       </c>
       <c r="C56" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1926,18 +1926,18 @@
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>4574</v>
+        <v>4978</v>
       </c>
       <c r="C57" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1949,18 +1949,18 @@
         <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>4575</v>
+        <v>4979</v>
       </c>
       <c r="C58" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -1972,18 +1972,18 @@
         <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>4576</v>
+        <v>4980</v>
       </c>
       <c r="C59" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680119324</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -1995,18 +1995,18 @@
         <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>4577</v>
+        <v>4981</v>
       </c>
       <c r="C60" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680175837</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -2018,18 +2018,18 @@
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>4578</v>
+        <v>4982</v>
       </c>
       <c r="C61" s="2">
-        <v>45812.823082738862</v>
+        <v>45812.864680175837</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -2041,18 +2041,18 @@
         <v>12</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>4579</v>
+        <v>4983</v>
       </c>
       <c r="C62" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.864680175837</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -2064,18 +2064,18 @@
         <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>4580</v>
+        <v>4984</v>
       </c>
       <c r="C63" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786076436</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -2092,13 +2092,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>4581</v>
+        <v>4985</v>
       </c>
       <c r="C64" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786076436</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -2115,13 +2115,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>4582</v>
+        <v>4986</v>
       </c>
       <c r="C65" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786132941</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -2133,18 +2133,18 @@
         <v>12</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>4583</v>
+        <v>4987</v>
       </c>
       <c r="C66" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786132941</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -2161,13 +2161,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>4584</v>
+        <v>4988</v>
       </c>
       <c r="C67" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786132941</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -2184,13 +2184,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>4585</v>
+        <v>4989</v>
       </c>
       <c r="C68" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -2202,18 +2202,18 @@
         <v>12</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>4586</v>
+        <v>4990</v>
       </c>
       <c r="C69" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -2230,13 +2230,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>4587</v>
+        <v>4991</v>
       </c>
       <c r="C70" s="2">
-        <v>45812.823082795374</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -2253,13 +2253,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>4588</v>
+        <v>4992</v>
       </c>
       <c r="C71" s="2">
-        <v>45812.823155393344</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -2276,13 +2276,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>4589</v>
+        <v>4993</v>
       </c>
       <c r="C72" s="2">
-        <v>45812.823155393344</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -2299,13 +2299,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>4590</v>
+        <v>4994</v>
       </c>
       <c r="C73" s="2">
-        <v>45812.823155687212</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -2317,18 +2317,18 @@
         <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>4591</v>
+        <v>4995</v>
       </c>
       <c r="C74" s="2">
-        <v>45812.823155687212</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -2340,18 +2340,18 @@
         <v>12</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>4592</v>
+        <v>4996</v>
       </c>
       <c r="C75" s="2">
-        <v>45812.823155687212</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -2363,18 +2363,18 @@
         <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>4593</v>
+        <v>4997</v>
       </c>
       <c r="C76" s="2">
-        <v>45812.823161180306</v>
+        <v>45812.865786189461</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -2391,13 +2391,13 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>4594</v>
+        <v>4998</v>
       </c>
       <c r="C77" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.86578624598</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -2409,18 +2409,18 @@
         <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>4595</v>
+        <v>4999</v>
       </c>
       <c r="C78" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.86578624598</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -2437,13 +2437,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>4596</v>
+        <v>5000</v>
       </c>
       <c r="C79" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.86578624598</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -2455,18 +2455,18 @@
         <v>12</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>4597</v>
+        <v>5001</v>
       </c>
       <c r="C80" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.86578624598</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>11</v>
@@ -2478,18 +2478,18 @@
         <v>12</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>4598</v>
+        <v>5002</v>
       </c>
       <c r="C81" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.86578624598</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>11</v>
@@ -2506,13 +2506,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>4599</v>
+        <v>5003</v>
       </c>
       <c r="C82" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865797763538</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>11</v>
@@ -2524,18 +2524,18 @@
         <v>12</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>4600</v>
+        <v>5004</v>
       </c>
       <c r="C83" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865797763538</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -2547,18 +2547,18 @@
         <v>12</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>4601</v>
+        <v>5005</v>
       </c>
       <c r="C84" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865797820057</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>11</v>
@@ -2570,18 +2570,18 @@
         <v>12</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>4602</v>
+        <v>5006</v>
       </c>
       <c r="C85" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865859115067</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -2593,18 +2593,18 @@
         <v>12</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>4603</v>
+        <v>5007</v>
       </c>
       <c r="C86" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865859115067</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>11</v>
@@ -2621,13 +2621,13 @@
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>4604</v>
+        <v>5008</v>
       </c>
       <c r="C87" s="2">
-        <v>45812.823161236818</v>
+        <v>45812.865859115067</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>11</v>
@@ -2639,18 +2639,18 @@
         <v>12</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>4605</v>
+        <v>5009</v>
       </c>
       <c r="C88" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -2662,18 +2662,18 @@
         <v>12</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>4606</v>
+        <v>5010</v>
       </c>
       <c r="C89" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>61</v>
+        <v>20</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -2685,18 +2685,18 @@
         <v>12</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>4607</v>
+        <v>5011</v>
       </c>
       <c r="C90" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -2708,18 +2708,18 @@
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>4608</v>
+        <v>5012</v>
       </c>
       <c r="C91" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -2731,18 +2731,18 @@
         <v>12</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>4609</v>
+        <v>5013</v>
       </c>
       <c r="C92" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -2754,18 +2754,18 @@
         <v>12</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>4610</v>
+        <v>5014</v>
       </c>
       <c r="C93" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>11</v>
@@ -2777,18 +2777,18 @@
         <v>12</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>4611</v>
+        <v>5015</v>
       </c>
       <c r="C94" s="2">
-        <v>45812.82316129333</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>11</v>
@@ -2800,18 +2800,18 @@
         <v>12</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>4612</v>
+        <v>5016</v>
       </c>
       <c r="C95" s="2">
-        <v>45812.82316134985</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>11</v>
@@ -2828,13 +2828,13 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>4613</v>
+        <v>5017</v>
       </c>
       <c r="C96" s="2">
-        <v>45812.82316134985</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -2846,18 +2846,18 @@
         <v>12</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>4614</v>
+        <v>5018</v>
       </c>
       <c r="C97" s="2">
-        <v>45812.823172878714</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>11</v>
@@ -2869,18 +2869,18 @@
         <v>12</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>4615</v>
+        <v>5019</v>
       </c>
       <c r="C98" s="2">
-        <v>45812.823227584398</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>11</v>
@@ -2897,13 +2897,13 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>4616</v>
+        <v>5020</v>
       </c>
       <c r="C99" s="2">
-        <v>45812.823227584398</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>11</v>
@@ -2915,18 +2915,18 @@
         <v>12</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>4617</v>
+        <v>5021</v>
       </c>
       <c r="C100" s="2">
-        <v>45812.823227821762</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>11</v>
@@ -2938,18 +2938,18 @@
         <v>12</v>
       </c>
       <c r="I100" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>4618</v>
+        <v>5022</v>
       </c>
       <c r="C101" s="2">
-        <v>45812.823227821762</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>11</v>
@@ -2961,18 +2961,18 @@
         <v>12</v>
       </c>
       <c r="I101" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>4619</v>
+        <v>5023</v>
       </c>
       <c r="C102" s="2">
-        <v>45812.823227821762</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -2984,18 +2984,18 @@
         <v>12</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>4620</v>
+        <v>5024</v>
       </c>
       <c r="C103" s="2">
-        <v>45812.823233382667</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>58</v>
+        <v>29</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>11</v>
@@ -3007,18 +3007,18 @@
         <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>4621</v>
+        <v>5025</v>
       </c>
       <c r="C104" s="2">
-        <v>45812.823233439187</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -3030,18 +3030,18 @@
         <v>12</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>4622</v>
+        <v>5026</v>
       </c>
       <c r="C105" s="2">
-        <v>45812.823233439187</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>11</v>
@@ -3053,18 +3053,18 @@
         <v>12</v>
       </c>
       <c r="I105" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>4623</v>
+        <v>5027</v>
       </c>
       <c r="C106" s="2">
-        <v>45812.823233439187</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>11</v>
@@ -3076,18 +3076,18 @@
         <v>12</v>
       </c>
       <c r="I106" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>4624</v>
+        <v>5028</v>
       </c>
       <c r="C107" s="2">
-        <v>45812.823233495692</v>
+        <v>45812.865859171587</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>11</v>
@@ -3099,18 +3099,18 @@
         <v>12</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>4625</v>
+        <v>5029</v>
       </c>
       <c r="C108" s="2">
-        <v>45812.823233495692</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>11</v>
@@ -3127,13 +3127,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>4626</v>
+        <v>5030</v>
       </c>
       <c r="C109" s="2">
-        <v>45812.823233495692</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>11</v>
@@ -3145,18 +3145,18 @@
         <v>12</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>4627</v>
+        <v>5031</v>
       </c>
       <c r="C110" s="2">
-        <v>45812.82329966229</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>56</v>
+        <v>14</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>11</v>
@@ -3168,18 +3168,18 @@
         <v>12</v>
       </c>
       <c r="I110" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>4628</v>
+        <v>5032</v>
       </c>
       <c r="C111" s="2">
-        <v>45812.82329966229</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>11</v>
@@ -3196,13 +3196,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>4629</v>
+        <v>5033</v>
       </c>
       <c r="C112" s="2">
-        <v>45812.823299956166</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -3214,18 +3214,18 @@
         <v>12</v>
       </c>
       <c r="I112" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>4630</v>
+        <v>5034</v>
       </c>
       <c r="C113" s="2">
-        <v>45812.823299956166</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>11</v>
@@ -3237,18 +3237,18 @@
         <v>12</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>4631</v>
+        <v>5035</v>
       </c>
       <c r="C114" s="2">
-        <v>45812.823299956166</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>11</v>
@@ -3260,18 +3260,18 @@
         <v>12</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>4632</v>
+        <v>5036</v>
       </c>
       <c r="C115" s="2">
-        <v>45812.823300012678</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>11</v>
@@ -3283,18 +3283,18 @@
         <v>12</v>
       </c>
       <c r="I115" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>4633</v>
+        <v>5037</v>
       </c>
       <c r="C116" s="2">
-        <v>45812.823300012678</v>
+        <v>45812.865859228099</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>11</v>
@@ -3306,18 +3306,18 @@
         <v>12</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>4634</v>
+        <v>5038</v>
       </c>
       <c r="C117" s="2">
-        <v>45812.823300012678</v>
+        <v>45812.865931679131</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>11</v>
@@ -3329,18 +3329,18 @@
         <v>12</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>4635</v>
+        <v>5039</v>
       </c>
       <c r="C118" s="2">
-        <v>45812.823300069198</v>
+        <v>45812.865931679131</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>11</v>
@@ -3352,18 +3352,18 @@
         <v>12</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>4636</v>
+        <v>5040</v>
       </c>
       <c r="C119" s="2">
-        <v>45812.823300069198</v>
+        <v>45812.865931973</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>11</v>
@@ -3375,18 +3375,18 @@
         <v>12</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>4637</v>
+        <v>5041</v>
       </c>
       <c r="C120" s="2">
-        <v>45812.823300069198</v>
+        <v>45812.865931973</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>11</v>
@@ -3403,13 +3403,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>4638</v>
+        <v>5042</v>
       </c>
       <c r="C121" s="2">
-        <v>45812.823305449398</v>
+        <v>45812.865931973</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>11</v>
@@ -3426,13 +3426,13 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>4639</v>
+        <v>5043</v>
       </c>
       <c r="C122" s="2">
-        <v>45812.82330550591</v>
+        <v>45812.865937466238</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -3444,18 +3444,18 @@
         <v>12</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>4640</v>
+        <v>5044</v>
       </c>
       <c r="C123" s="2">
-        <v>45812.82330550591</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>52</v>
+        <v>19</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -3472,13 +3472,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>4641</v>
+        <v>5045</v>
       </c>
       <c r="C124" s="2">
-        <v>45812.82330550591</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>11</v>
@@ -3490,18 +3490,18 @@
         <v>12</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>4642</v>
+        <v>5046</v>
       </c>
       <c r="C125" s="2">
-        <v>45812.82330550591</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>11</v>
@@ -3513,18 +3513,18 @@
         <v>12</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>4643</v>
+        <v>5047</v>
       </c>
       <c r="C126" s="2">
-        <v>45812.823305562422</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>11</v>
@@ -3536,18 +3536,18 @@
         <v>12</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>4644</v>
+        <v>5048</v>
       </c>
       <c r="C127" s="2">
-        <v>45812.823305562422</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>11</v>
@@ -3559,18 +3559,18 @@
         <v>12</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>4645</v>
+        <v>5049</v>
       </c>
       <c r="C128" s="2">
-        <v>45812.823305562422</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>11</v>
@@ -3582,18 +3582,18 @@
         <v>12</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>4646</v>
+        <v>5050</v>
       </c>
       <c r="C129" s="2">
-        <v>45812.823305562422</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>11</v>
@@ -3605,18 +3605,18 @@
         <v>12</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>4647</v>
+        <v>5051</v>
       </c>
       <c r="C130" s="2">
-        <v>45812.823317091286</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>11</v>
@@ -3628,18 +3628,18 @@
         <v>12</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>4648</v>
+        <v>5052</v>
       </c>
       <c r="C131" s="2">
-        <v>45812.823317147806</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>11</v>
@@ -3656,13 +3656,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>4649</v>
+        <v>5053</v>
       </c>
       <c r="C132" s="2">
-        <v>45812.823372497609</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>11</v>
@@ -3674,18 +3674,18 @@
         <v>12</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>4650</v>
+        <v>5054</v>
       </c>
       <c r="C133" s="2">
-        <v>45812.823372497609</v>
+        <v>45812.865937522605</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>11</v>
@@ -3702,13 +3702,13 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>4651</v>
+        <v>5055</v>
       </c>
       <c r="C134" s="2">
-        <v>45812.823372667161</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>11</v>
@@ -3720,18 +3720,18 @@
         <v>12</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>4652</v>
+        <v>5056</v>
       </c>
       <c r="C135" s="2">
-        <v>45812.823372667161</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D135" s="3" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>11</v>
@@ -3743,18 +3743,18 @@
         <v>12</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>4653</v>
+        <v>5057</v>
       </c>
       <c r="C136" s="2">
-        <v>45812.823372667161</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>17</v>
+        <v>50</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>11</v>
@@ -3766,18 +3766,18 @@
         <v>12</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>4654</v>
+        <v>5058</v>
       </c>
       <c r="C137" s="2">
-        <v>45812.823372723673</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>11</v>
@@ -3794,13 +3794,13 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>4655</v>
+        <v>5059</v>
       </c>
       <c r="C138" s="2">
-        <v>45812.823372723673</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>11</v>
@@ -3812,18 +3812,18 @@
         <v>12</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>4656</v>
+        <v>5060</v>
       </c>
       <c r="C139" s="2">
-        <v>45812.823372723673</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>11</v>
@@ -3835,18 +3835,18 @@
         <v>12</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>4657</v>
+        <v>5061</v>
       </c>
       <c r="C140" s="2">
-        <v>45812.823372780185</v>
+        <v>45812.865937579118</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>11</v>
@@ -3863,13 +3863,13 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>4658</v>
+        <v>5062</v>
       </c>
       <c r="C141" s="2">
-        <v>45812.823372780185</v>
+        <v>45812.865937635637</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>11</v>
@@ -3881,18 +3881,18 @@
         <v>12</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>4659</v>
+        <v>5063</v>
       </c>
       <c r="C142" s="2">
-        <v>45812.823372780185</v>
+        <v>45812.865937635637</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>11</v>
@@ -3909,13 +3909,13 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>4660</v>
+        <v>5064</v>
       </c>
       <c r="C143" s="2">
-        <v>45812.823378284724</v>
+        <v>45812.865949153194</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>11</v>
@@ -3927,18 +3927,18 @@
         <v>12</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>4661</v>
+        <v>5065</v>
       </c>
       <c r="C144" s="2">
-        <v>45812.823378341243</v>
+        <v>45812.866004130155</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>11</v>
@@ -3950,18 +3950,18 @@
         <v>12</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>4662</v>
+        <v>5066</v>
       </c>
       <c r="C145" s="2">
-        <v>45812.823378341243</v>
+        <v>45812.866004130155</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>11</v>
@@ -3973,18 +3973,18 @@
         <v>12</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>4663</v>
+        <v>5067</v>
       </c>
       <c r="C146" s="2">
-        <v>45812.823378397756</v>
+        <v>45812.866004424039</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>36</v>
+        <v>58</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>11</v>
@@ -3996,18 +3996,18 @@
         <v>12</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>4664</v>
+        <v>5068</v>
       </c>
       <c r="C147" s="2">
-        <v>45812.823378397756</v>
+        <v>45812.866004424039</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>11</v>
@@ -4024,13 +4024,13 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>4665</v>
+        <v>5069</v>
       </c>
       <c r="C148" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866004424039</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>11</v>
@@ -4042,18 +4042,18 @@
         <v>12</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>4666</v>
+        <v>5070</v>
       </c>
       <c r="C149" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866009917117</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>11</v>
@@ -4065,18 +4065,18 @@
         <v>12</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>4667</v>
+        <v>5071</v>
       </c>
       <c r="C150" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866009973637</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>11</v>
@@ -4088,18 +4088,18 @@
         <v>12</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>4668</v>
+        <v>5072</v>
       </c>
       <c r="C151" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866009973637</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>11</v>
@@ -4111,18 +4111,18 @@
         <v>12</v>
       </c>
       <c r="I151" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>4669</v>
+        <v>5073</v>
       </c>
       <c r="C152" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866009973637</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>11</v>
@@ -4139,13 +4139,13 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>4670</v>
+        <v>5074</v>
       </c>
       <c r="C153" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866010030149</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>11</v>
@@ -4162,13 +4162,13 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>4671</v>
+        <v>5075</v>
       </c>
       <c r="C154" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866010030149</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>11</v>
@@ -4180,18 +4180,18 @@
         <v>12</v>
       </c>
       <c r="I154" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>4672</v>
+        <v>5076</v>
       </c>
       <c r="C155" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.866010030149</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>11</v>
@@ -4208,13 +4208,13 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>4673</v>
+        <v>5077</v>
       </c>
       <c r="C156" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.86607641149</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>11</v>
@@ -4226,18 +4226,18 @@
         <v>12</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>4674</v>
+        <v>5078</v>
       </c>
       <c r="C157" s="2">
-        <v>45812.823631309337</v>
+        <v>45812.86607641149</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>23</v>
+        <v>59</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>11</v>
@@ -4249,18 +4249,18 @@
         <v>12</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>4675</v>
+        <v>5079</v>
       </c>
       <c r="C158" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076705373</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>11</v>
@@ -4277,13 +4277,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>4676</v>
+        <v>5080</v>
       </c>
       <c r="C159" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076705373</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>11</v>
@@ -4295,18 +4295,18 @@
         <v>12</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>4677</v>
+        <v>5081</v>
       </c>
       <c r="C160" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076705373</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>11</v>
@@ -4323,13 +4323,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>4678</v>
+        <v>5082</v>
       </c>
       <c r="C161" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076761886</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>11</v>
@@ -4341,18 +4341,18 @@
         <v>12</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>4679</v>
+        <v>5083</v>
       </c>
       <c r="C162" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076761886</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>11</v>
@@ -4364,18 +4364,18 @@
         <v>12</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>4680</v>
+        <v>5084</v>
       </c>
       <c r="C163" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076761886</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>11</v>
@@ -4387,18 +4387,18 @@
         <v>12</v>
       </c>
       <c r="I163" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>4681</v>
+        <v>5085</v>
       </c>
       <c r="C164" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076818398</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>11</v>
@@ -4410,18 +4410,18 @@
         <v>12</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>4682</v>
+        <v>5086</v>
       </c>
       <c r="C165" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076818398</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>11</v>
@@ -4438,13 +4438,13 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>4683</v>
+        <v>5087</v>
       </c>
       <c r="C166" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866076818398</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>11</v>
@@ -4456,18 +4456,18 @@
         <v>12</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>4684</v>
+        <v>5088</v>
       </c>
       <c r="C167" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866082198605</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>11</v>
@@ -4479,18 +4479,18 @@
         <v>12</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>4685</v>
+        <v>5089</v>
       </c>
       <c r="C168" s="2">
-        <v>45812.823631365849</v>
+        <v>45812.866082255117</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>11</v>
@@ -4507,10 +4507,10 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>4686</v>
+        <v>5090</v>
       </c>
       <c r="C169" s="2">
-        <v>45812.823631433668</v>
+        <v>45812.866082255117</v>
       </c>
       <c r="D169" s="3" t="s">
         <v>28</v>
@@ -4525,18 +4525,18 @@
         <v>12</v>
       </c>
       <c r="I169" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>4687</v>
+        <v>5091</v>
       </c>
       <c r="C170" s="2">
-        <v>45812.823631433668</v>
+        <v>45812.866082255117</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>11</v>
@@ -4548,18 +4548,18 @@
         <v>12</v>
       </c>
       <c r="I170" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>4688</v>
+        <v>5092</v>
       </c>
       <c r="C171" s="2">
-        <v>45812.823631433668</v>
+        <v>45812.866082255117</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>11</v>
@@ -4576,13 +4576,13 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>4689</v>
+        <v>5093</v>
       </c>
       <c r="C172" s="2">
-        <v>45812.823631433668</v>
+        <v>45812.866082311637</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>11</v>
@@ -4594,18 +4594,18 @@
         <v>12</v>
       </c>
       <c r="I172" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>4690</v>
+        <v>5094</v>
       </c>
       <c r="C173" s="2">
-        <v>45812.823672349761</v>
+        <v>45812.866082311637</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>11</v>
@@ -4617,18 +4617,18 @@
         <v>12</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>4691</v>
+        <v>5095</v>
       </c>
       <c r="C174" s="2">
-        <v>45812.823672349761</v>
+        <v>45812.866082311637</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>11</v>
@@ -4640,18 +4640,18 @@
         <v>12</v>
       </c>
       <c r="I174" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>4692</v>
+        <v>5096</v>
       </c>
       <c r="C175" s="2">
-        <v>45812.823672349761</v>
+        <v>45812.866082311637</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>11</v>
@@ -4663,18 +4663,18 @@
         <v>12</v>
       </c>
       <c r="I175" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>4693</v>
+        <v>5097</v>
       </c>
       <c r="C176" s="2">
-        <v>45812.823672406281</v>
+        <v>45812.866093829194</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>11</v>
@@ -4686,18 +4686,18 @@
         <v>12</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>4694</v>
+        <v>5098</v>
       </c>
       <c r="C177" s="2">
-        <v>45812.823672406281</v>
+        <v>45812.866093885714</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>11</v>
@@ -4709,18 +4709,18 @@
         <v>12</v>
       </c>
       <c r="I177" s="3" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>4695</v>
+        <v>5099</v>
       </c>
       <c r="C178" s="2">
-        <v>45812.823672406281</v>
+        <v>45812.866150026734</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>11</v>
@@ -4732,18 +4732,18 @@
         <v>12</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A179" s="1">
-        <v>4696</v>
+        <v>5100</v>
       </c>
       <c r="C179" s="2">
-        <v>45812.823672406281</v>
+        <v>45812.866150026734</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>11</v>
@@ -4755,18 +4755,18 @@
         <v>12</v>
       </c>
       <c r="I179" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A180" s="1">
-        <v>4697</v>
+        <v>5101</v>
       </c>
       <c r="C180" s="2">
-        <v>45812.823672406281</v>
+        <v>45812.866150196271</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>11</v>
@@ -4783,13 +4783,13 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A181" s="1">
-        <v>4698</v>
+        <v>5102</v>
       </c>
       <c r="C181" s="2">
-        <v>45812.823672462786</v>
+        <v>45812.866150196271</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>11</v>
@@ -4806,13 +4806,13 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
-        <v>4699</v>
+        <v>5103</v>
       </c>
       <c r="C182" s="2">
-        <v>45812.823672643637</v>
+        <v>45812.866150196271</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>11</v>
@@ -4829,13 +4829,13 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
-        <v>4700</v>
+        <v>5104</v>
       </c>
       <c r="C183" s="2">
-        <v>45812.823672643637</v>
+        <v>45812.86615025279</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>11</v>
@@ -4847,18 +4847,18 @@
         <v>12</v>
       </c>
       <c r="I183" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
-        <v>4701</v>
+        <v>5105</v>
       </c>
       <c r="C184" s="2">
-        <v>45812.823672700149</v>
+        <v>45812.86615025279</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>11</v>
@@ -4875,13 +4875,13 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
-        <v>4702</v>
+        <v>5106</v>
       </c>
       <c r="C185" s="2">
-        <v>45812.823672700149</v>
+        <v>45812.86615025279</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>11</v>
@@ -4893,35 +4893,1737 @@
         <v>12</v>
       </c>
       <c r="I185" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
-        <v>4703</v>
+        <v>5107</v>
       </c>
       <c r="C186" s="2">
-        <v>45812.823678430752</v>
+        <v>45812.866150309303</v>
       </c>
       <c r="D186" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>5108</v>
+      </c>
+      <c r="C187" s="2">
+        <v>45812.866150309303</v>
+      </c>
+      <c r="D187" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F186" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H186" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I186" s="3" t="s">
+      <c r="F187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>5109</v>
+      </c>
+      <c r="C188" s="2">
+        <v>45812.866150309303</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>5110</v>
+      </c>
+      <c r="C189" s="2">
+        <v>45812.866155813841</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>5111</v>
+      </c>
+      <c r="C190" s="2">
+        <v>45812.866155870353</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>5112</v>
+      </c>
+      <c r="C191" s="2">
+        <v>45812.866155870353</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>5113</v>
+      </c>
+      <c r="C192" s="2">
+        <v>45812.866155926873</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>5114</v>
+      </c>
+      <c r="C193" s="2">
+        <v>45812.866155926873</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>5115</v>
+      </c>
+      <c r="C194" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>5116</v>
+      </c>
+      <c r="C195" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>5117</v>
+      </c>
+      <c r="C196" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>5118</v>
+      </c>
+      <c r="C197" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>5119</v>
+      </c>
+      <c r="C198" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>5120</v>
+      </c>
+      <c r="C199" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>5121</v>
+      </c>
+      <c r="C200" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>5122</v>
+      </c>
+      <c r="C201" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>5123</v>
+      </c>
+      <c r="C202" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>5124</v>
+      </c>
+      <c r="C203" s="2">
+        <v>45812.866427917535</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>5125</v>
+      </c>
+      <c r="C204" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>5126</v>
+      </c>
+      <c r="C205" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>5127</v>
+      </c>
+      <c r="C206" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>5128</v>
+      </c>
+      <c r="C207" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>5129</v>
+      </c>
+      <c r="C208" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>5130</v>
+      </c>
+      <c r="C209" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>5131</v>
+      </c>
+      <c r="C210" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>5132</v>
+      </c>
+      <c r="C211" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>5133</v>
+      </c>
+      <c r="C212" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>5134</v>
+      </c>
+      <c r="C213" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>5135</v>
+      </c>
+      <c r="C214" s="2">
+        <v>45812.866427974048</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>5136</v>
+      </c>
+      <c r="C215" s="2">
+        <v>45812.866428030567</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>5137</v>
+      </c>
+      <c r="C216" s="2">
+        <v>45812.866428030567</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>5138</v>
+      </c>
+      <c r="C217" s="2">
+        <v>45812.866428030567</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>5139</v>
+      </c>
+      <c r="C218" s="2">
+        <v>45812.866428030567</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>5140</v>
+      </c>
+      <c r="C219" s="2">
+        <v>45812.866450658781</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>5141</v>
+      </c>
+      <c r="C220" s="2">
+        <v>45812.866450658781</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>5142</v>
+      </c>
+      <c r="C221" s="2">
+        <v>45812.866450658781</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>5143</v>
+      </c>
+      <c r="C222" s="2">
+        <v>45812.866450715293</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>5144</v>
+      </c>
+      <c r="C223" s="2">
+        <v>45812.866450715293</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>5145</v>
+      </c>
+      <c r="C224" s="2">
+        <v>45812.866450715293</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>5146</v>
+      </c>
+      <c r="C225" s="2">
+        <v>45812.866450715293</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>5147</v>
+      </c>
+      <c r="C226" s="2">
+        <v>45812.866450715293</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>5148</v>
+      </c>
+      <c r="C227" s="2">
+        <v>45812.866450771806</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>5149</v>
+      </c>
+      <c r="C228" s="2">
+        <v>45812.866450896137</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>5150</v>
+      </c>
+      <c r="C229" s="2">
+        <v>45812.866450896137</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>5151</v>
+      </c>
+      <c r="C230" s="2">
+        <v>45812.866450952657</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>5152</v>
+      </c>
+      <c r="C231" s="2">
+        <v>45812.866450952657</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>5153</v>
+      </c>
+      <c r="C232" s="2">
+        <v>45812.866456683252</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>5154</v>
+      </c>
+      <c r="C233" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>5155</v>
+      </c>
+      <c r="C234" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>5156</v>
+      </c>
+      <c r="C235" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>5157</v>
+      </c>
+      <c r="C236" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>5158</v>
+      </c>
+      <c r="C237" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>5159</v>
+      </c>
+      <c r="C238" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>5160</v>
+      </c>
+      <c r="C239" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>5161</v>
+      </c>
+      <c r="C240" s="2">
+        <v>45812.86660690885</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>5162</v>
+      </c>
+      <c r="C241" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>5163</v>
+      </c>
+      <c r="C242" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>5164</v>
+      </c>
+      <c r="C243" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>5165</v>
+      </c>
+      <c r="C244" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>5166</v>
+      </c>
+      <c r="C245" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>5167</v>
+      </c>
+      <c r="C246" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>5168</v>
+      </c>
+      <c r="C247" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>5169</v>
+      </c>
+      <c r="C248" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>5170</v>
+      </c>
+      <c r="C249" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>5171</v>
+      </c>
+      <c r="C250" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>5172</v>
+      </c>
+      <c r="C251" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>5173</v>
+      </c>
+      <c r="C252" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>5174</v>
+      </c>
+      <c r="C253" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>5175</v>
+      </c>
+      <c r="C254" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>5176</v>
+      </c>
+      <c r="C255" s="2">
+        <v>45812.86660696537</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>5177</v>
+      </c>
+      <c r="C256" s="2">
+        <v>45812.866607021882</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>5178</v>
+      </c>
+      <c r="C257" s="2">
+        <v>45812.866607021882</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>5179</v>
+      </c>
+      <c r="C258" s="2">
+        <v>45812.866607021882</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>5180</v>
+      </c>
+      <c r="C259" s="2">
+        <v>45812.866607021882</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>5181</v>
+      </c>
+      <c r="C260" s="2">
+        <v>45812.866607021882</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I260" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J186">
-    <sortCondition ref="A2:A186"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J260">
+    <sortCondition ref="A2:A260"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ЛО\pmi_lodzt\ss2_mode\Журнал событий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ЛО\pmi_lodzt\urov_mode\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8228ED2-2363-4054-AF72-53DA08E56B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB9E91D-1688-4CE5-B83B-534DC6066CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="60">
   <si>
     <t>№</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Ед. изм.</t>
   </si>
   <si>
-    <t>Слот M3.Реле7. Статус</t>
+    <t>Слот M3.Реле1. Статус</t>
   </si>
   <si>
     <t>Хорошее [0]</t>
@@ -69,49 +69,82 @@
     <t>0</t>
   </si>
   <si>
-    <t>Сигнал внешний 4</t>
-  </si>
-  <si>
-    <t>СС / СС: Общ. внеш. сигнал</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ4. Статус</t>
-  </si>
-  <si>
-    <t>ПС / ПС: Пуск (имп)</t>
+    <t>Слот M3.Реле2. Статус</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>Сигнал внешний 3</t>
+    <t>Слот M3.Реле7. Статус</t>
   </si>
   <si>
-    <t>Слот M8. ДВ3. Статус</t>
+    <t>Слот M4.Реле2. Статус</t>
   </si>
   <si>
-    <t>Сигнал внешний 2</t>
+    <t>Слот M4.Реле3. Статус</t>
   </si>
   <si>
-    <t>Слот M8. ДВ2. Статус</t>
+    <t>УРОВ ВН / УРОВ: Ввод</t>
   </si>
   <si>
-    <t>Сигнал внешний 1</t>
+    <t>УРОВ ВН / УРОВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Срабатывание</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
+  </si>
+  <si>
+    <t>ЛО ВН / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО ВН / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>СС / СС: Внеш. откл</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле8. Статус</t>
+  </si>
+  <si>
+    <t>Слот M4.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>ЛО ВН / ЛО: Отключение</t>
+  </si>
+  <si>
+    <t>ПС / ПС: Пуск</t>
+  </si>
+  <si>
+    <t>ДВ: Вывод терминала</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-1_Опер. вывод</t>
   </si>
   <si>
     <t>Слот M8. ДВ1. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле8. Статус</t>
+    <t>Слот M4.Реле1. Статус</t>
   </si>
   <si>
-    <t>ПС / ПС: Пуск</t>
+    <t>ЛО ВН / ЛО: Отключить аварийно</t>
   </si>
   <si>
-    <t>Слот M3.Реле1. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле2. Статус</t>
+    <t>ПС / ПС: Пуск (имп)</t>
   </si>
   <si>
     <t>Слот M3.Реле3. Статус</t>
@@ -123,25 +156,49 @@
     <t>Слот M3.Реле5. Статус</t>
   </si>
   <si>
+    <t>УРОВ ВН / УРОВ: ИО Iмакс</t>
+  </si>
+  <si>
+    <t>УРОВ ВН / УРОВ: Пуск</t>
+  </si>
+  <si>
+    <t>УРОВ ВН / УРОВ: Срабатывание</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-52_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ ЛО ВН</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ3. Статус</t>
+  </si>
+  <si>
+    <t>Внеш.откл. от СО</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ4. Статус</t>
+  </si>
+  <si>
     <t>Слот M3.Реле6. Статус</t>
   </si>
   <si>
-    <t>СС / СС: Вых.цепи разобраны</t>
+    <t>Пуск УРОВ внешний</t>
   </si>
   <si>
-    <t>СС / СС: БИ выведены</t>
+    <t>УРОВ ВН / УРОВ: Сраб "на себя"</t>
   </si>
   <si>
-    <t>СС / СС: ОТ сигн</t>
+    <t>Слот M8. ДВ5. Статус</t>
   </si>
   <si>
-    <t>СС / СС: Неисп. ОТ ГЗ</t>
+    <t>Виртуальный ключ-59_Опер. вывод</t>
   </si>
   <si>
-    <t>СС / СС: Неисп. ОТ ТЗ,ТС</t>
+    <t>ДВ: ОВ УРОВ</t>
   </si>
   <si>
-    <t>СС / СС: ОТ НН сигн</t>
+    <t>Слот M8. ДВ2. Статус</t>
   </si>
   <si>
     <t>Наличие внешнего питания (общий)</t>
@@ -549,7 +606,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J307"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -597,13 +654,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9502</v>
+        <v>9604</v>
       </c>
       <c r="C2" s="2">
-        <v>46178.754527350553</v>
+        <v>46181.594941282056</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -615,18 +672,18 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>9503</v>
+        <v>9605</v>
       </c>
       <c r="C3" s="2">
-        <v>46178.754527350553</v>
+        <v>46181.594941282056</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -638,18 +695,18 @@
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>9504</v>
+        <v>9606</v>
       </c>
       <c r="C4" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950211242</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -661,18 +718,18 @@
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>9505</v>
+        <v>9607</v>
       </c>
       <c r="C5" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950211242</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -684,18 +741,18 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>9506</v>
+        <v>9608</v>
       </c>
       <c r="C6" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950211242</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -707,18 +764,18 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>9507</v>
+        <v>9609</v>
       </c>
       <c r="C7" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950211242</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -730,18 +787,18 @@
         <v>12</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>9508</v>
+        <v>9610</v>
       </c>
       <c r="C8" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950267761</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -753,18 +810,18 @@
         <v>12</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>9509</v>
+        <v>9611</v>
       </c>
       <c r="C9" s="2">
-        <v>46178.754536042528</v>
+        <v>46181.594950267761</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -776,18 +833,18 @@
         <v>12</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9510</v>
+        <v>9612</v>
       </c>
       <c r="C10" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595579167122</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -799,18 +856,18 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9511</v>
+        <v>9613</v>
       </c>
       <c r="C11" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595579234941</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -822,18 +879,18 @@
         <v>12</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>9512</v>
+        <v>9614</v>
       </c>
       <c r="C12" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638326027</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -845,18 +902,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>9513</v>
+        <v>9615</v>
       </c>
       <c r="C13" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638326027</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -868,18 +925,18 @@
         <v>12</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>9514</v>
+        <v>9616</v>
       </c>
       <c r="C14" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638382547</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -891,18 +948,18 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>9515</v>
+        <v>9617</v>
       </c>
       <c r="C15" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638382547</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -914,18 +971,18 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>9516</v>
+        <v>9618</v>
       </c>
       <c r="C16" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638382547</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -937,18 +994,18 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>9517</v>
+        <v>9619</v>
       </c>
       <c r="C17" s="2">
-        <v>46178.754536099033</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -960,18 +1017,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>9518</v>
+        <v>9620</v>
       </c>
       <c r="C18" s="2">
-        <v>46178.754536155553</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -983,18 +1040,18 @@
         <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>9519</v>
+        <v>9621</v>
       </c>
       <c r="C19" s="2">
-        <v>46178.754536155553</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1006,18 +1063,18 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>9520</v>
+        <v>9622</v>
       </c>
       <c r="C20" s="2">
-        <v>46178.7552606428</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1029,18 +1086,18 @@
         <v>12</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>9521</v>
+        <v>9623</v>
       </c>
       <c r="C21" s="2">
-        <v>46178.7552606428</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1052,18 +1109,18 @@
         <v>12</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>9522</v>
+        <v>9624</v>
       </c>
       <c r="C22" s="2">
-        <v>46178.7552606428</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -1075,18 +1132,18 @@
         <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>9523</v>
+        <v>9625</v>
       </c>
       <c r="C23" s="2">
-        <v>46178.755260699312</v>
+        <v>46181.595638439052</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1098,18 +1155,18 @@
         <v>12</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>9524</v>
+        <v>9626</v>
       </c>
       <c r="C24" s="2">
-        <v>46178.755260699312</v>
+        <v>46181.595638495572</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -1121,18 +1178,18 @@
         <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>9525</v>
+        <v>9627</v>
       </c>
       <c r="C25" s="2">
-        <v>46178.755260767131</v>
+        <v>46181.595638495572</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1144,18 +1201,18 @@
         <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>9526</v>
+        <v>9628</v>
       </c>
       <c r="C26" s="2">
-        <v>46178.75533318425</v>
+        <v>46181.595638495572</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1167,18 +1224,18 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>9527</v>
+        <v>9629</v>
       </c>
       <c r="C27" s="2">
-        <v>46178.75533318425</v>
+        <v>46181.595638495572</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1190,18 +1247,18 @@
         <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>9528</v>
+        <v>9630</v>
       </c>
       <c r="C28" s="2">
-        <v>46178.75533318425</v>
+        <v>46181.595638495572</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1213,18 +1270,18 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>9529</v>
+        <v>9631</v>
       </c>
       <c r="C29" s="2">
-        <v>46178.75533324077</v>
+        <v>46181.595650013129</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1236,18 +1293,18 @@
         <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>9530</v>
+        <v>9632</v>
       </c>
       <c r="C30" s="2">
-        <v>46178.755333534646</v>
+        <v>46181.595650013129</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1259,18 +1316,18 @@
         <v>12</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>9531</v>
+        <v>9633</v>
       </c>
       <c r="C31" s="2">
-        <v>46178.755333534646</v>
+        <v>46181.595650069648</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1282,18 +1339,18 @@
         <v>12</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>9532</v>
+        <v>9634</v>
       </c>
       <c r="C32" s="2">
-        <v>46178.755333534646</v>
+        <v>46181.595650069648</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1305,18 +1362,18 @@
         <v>12</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>9533</v>
+        <v>9635</v>
       </c>
       <c r="C33" s="2">
-        <v>46178.755333591158</v>
+        <v>46181.595650069648</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1328,18 +1385,18 @@
         <v>12</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>9534</v>
+        <v>9636</v>
       </c>
       <c r="C34" s="2">
-        <v>46178.755333591158</v>
+        <v>46181.595650126168</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1351,18 +1408,18 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>9535</v>
+        <v>9637</v>
       </c>
       <c r="C35" s="2">
-        <v>46178.755333647678</v>
+        <v>46181.595709861518</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>17</v>
+        <v>56</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1374,18 +1431,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>9536</v>
+        <v>9638</v>
       </c>
       <c r="C36" s="2">
-        <v>46178.755405262142</v>
+        <v>46181.595709861518</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>21</v>
+        <v>55</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1397,18 +1454,18 @@
         <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>9537</v>
+        <v>9639</v>
       </c>
       <c r="C37" s="2">
-        <v>46178.755405262142</v>
+        <v>46181.595709861518</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1420,18 +1477,18 @@
         <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>9538</v>
+        <v>9640</v>
       </c>
       <c r="C38" s="2">
-        <v>46178.755405262142</v>
+        <v>46181.595709918038</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1448,13 +1505,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>9539</v>
+        <v>9641</v>
       </c>
       <c r="C39" s="2">
-        <v>46178.755405318647</v>
+        <v>46181.595709918038</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1466,18 +1523,18 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>9540</v>
+        <v>9642</v>
       </c>
       <c r="C40" s="2">
-        <v>46178.75540555601</v>
+        <v>46181.595709918038</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1489,18 +1546,18 @@
         <v>12</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>9541</v>
+        <v>9643</v>
       </c>
       <c r="C41" s="2">
-        <v>46178.75540555601</v>
+        <v>46181.595709918038</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1512,18 +1569,18 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>9542</v>
+        <v>9644</v>
       </c>
       <c r="C42" s="2">
-        <v>46178.75540555601</v>
+        <v>46181.595709974557</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1535,18 +1592,18 @@
         <v>12</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>9543</v>
+        <v>9645</v>
       </c>
       <c r="C43" s="2">
-        <v>46178.75540561253</v>
+        <v>46181.595709974557</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1558,18 +1615,18 @@
         <v>12</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>9544</v>
+        <v>9646</v>
       </c>
       <c r="C44" s="2">
-        <v>46178.75540561253</v>
+        <v>46181.595709974557</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1581,18 +1638,18 @@
         <v>12</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>9545</v>
+        <v>9647</v>
       </c>
       <c r="C45" s="2">
-        <v>46178.755405680342</v>
+        <v>46181.595709974557</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1609,13 +1666,13 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>9546</v>
+        <v>9648</v>
       </c>
       <c r="C46" s="2">
-        <v>46178.75547722714</v>
+        <v>46181.595782493401</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1632,13 +1689,13 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>9547</v>
+        <v>9649</v>
       </c>
       <c r="C47" s="2">
-        <v>46178.75547722714</v>
+        <v>46181.595782493401</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1655,13 +1712,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>9548</v>
+        <v>9650</v>
       </c>
       <c r="C48" s="2">
-        <v>46178.75547722714</v>
+        <v>46181.595782674238</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1673,18 +1730,18 @@
         <v>12</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>9549</v>
+        <v>9651</v>
       </c>
       <c r="C49" s="2">
-        <v>46178.755477294952</v>
+        <v>46181.595782674238</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1696,18 +1753,18 @@
         <v>12</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>9550</v>
+        <v>9652</v>
       </c>
       <c r="C50" s="2">
-        <v>46178.755477521016</v>
+        <v>46181.595782674238</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1719,18 +1776,18 @@
         <v>12</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>9551</v>
+        <v>9653</v>
       </c>
       <c r="C51" s="2">
-        <v>46178.755477521016</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1742,18 +1799,18 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>9552</v>
+        <v>9654</v>
       </c>
       <c r="C52" s="2">
-        <v>46178.755477521016</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -1765,18 +1822,18 @@
         <v>12</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>9553</v>
+        <v>9655</v>
       </c>
       <c r="C53" s="2">
-        <v>46178.755477577528</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1788,18 +1845,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>9554</v>
+        <v>9656</v>
       </c>
       <c r="C54" s="2">
-        <v>46178.755477577528</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1811,18 +1868,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>9555</v>
+        <v>9657</v>
       </c>
       <c r="C55" s="2">
-        <v>46178.755477634048</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1834,18 +1891,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>9556</v>
+        <v>9658</v>
       </c>
       <c r="C56" s="2">
-        <v>46178.755549429501</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1862,13 +1919,13 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>9557</v>
+        <v>9659</v>
       </c>
       <c r="C57" s="2">
-        <v>46178.755549429501</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1885,13 +1942,13 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>9558</v>
+        <v>9660</v>
       </c>
       <c r="C58" s="2">
-        <v>46178.755549429501</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -1903,35 +1960,5739 @@
         <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>9559</v>
+        <v>9661</v>
       </c>
       <c r="C59" s="2">
-        <v>46178.755549486021</v>
+        <v>46181.595782730757</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="1">
+        <v>9662</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46181.595782730757</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="1">
+        <v>9663</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46181.595782730757</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="1">
+        <v>9664</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46181.595782787277</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="1">
+        <v>9665</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46181.595782787277</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G63" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I63" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="1">
+        <v>9666</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46181.595782787277</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A65" s="1">
+        <v>9667</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46181.595782787277</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G65" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I65" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A66" s="1">
+        <v>9668</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46181.595782787277</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I66" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A67" s="1">
+        <v>9669</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46181.595788280363</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G67" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I67" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A68" s="1">
+        <v>9670</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46181.595855735635</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G68" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I68" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A69" s="1">
+        <v>9671</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46181.595855735635</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G69" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I69" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A70" s="1">
+        <v>9672</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46181.59586152259</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A71" s="1">
+        <v>9673</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I71" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A72" s="1">
+        <v>9674</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A73" s="1">
+        <v>9675</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I73" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A74" s="1">
+        <v>9676</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I74" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A75" s="1">
+        <v>9677</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I75" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A76" s="1">
+        <v>9678</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I76" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A77" s="1">
+        <v>9679</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G77" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H77" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I77" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A78" s="1">
+        <v>9680</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G78" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I78" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A79" s="1">
+        <v>9681</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A80" s="1">
+        <v>9682</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>9683</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46181.59586157911</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>9684</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>9685</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>9686</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>9687</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>9688</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>9689</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I59" s="3" t="s">
+      <c r="F87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>9690</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>9691</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>9692</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>9693</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46181.595861635629</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>9694</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46181.595861692142</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>9695</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46181.595861692142</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>9696</v>
+      </c>
+      <c r="C94" s="2">
+        <v>46181.595861692142</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>9697</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46181.595861692142</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>9698</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46181.595861692142</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>9699</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46181.595873209706</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>9700</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46181.595873209706</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>9701</v>
+      </c>
+      <c r="C99" s="2">
+        <v>46181.595873266211</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>9702</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46181.595873266211</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>9703</v>
+      </c>
+      <c r="C101" s="2">
+        <v>46181.595873266211</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>9704</v>
+      </c>
+      <c r="C102" s="2">
+        <v>46181.595873322731</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>9705</v>
+      </c>
+      <c r="C103" s="2">
+        <v>46181.595927384013</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>9706</v>
+      </c>
+      <c r="C104" s="2">
+        <v>46181.595927384013</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>9707</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46181.595927440518</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>9708</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46181.595927440518</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>9709</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46181.595927440518</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>9710</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46181.595927497037</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>9711</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46181.595927497037</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>9712</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46181.595927497037</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>9713</v>
+      </c>
+      <c r="C111" s="2">
+        <v>46181.595927497037</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>9714</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46181.595927497037</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>9715</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46181.595927553557</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>9716</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46181.595927553557</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>9717</v>
+      </c>
+      <c r="C115" s="2">
+        <v>46181.595927553557</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>9718</v>
+      </c>
+      <c r="C116" s="2">
+        <v>46181.595927553557</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>9719</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46181.595927610062</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>9720</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46181.595999733305</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>9721</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46181.595999733305</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>9722</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46181.595999733305</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>9723</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46181.595999789824</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>9724</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46181.595999789824</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>9725</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46181.595999789824</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>9726</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46181.595999846344</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>9727</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46181.595999846344</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>9728</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46181.596084640049</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>9729</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46181.596084696554</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>9730</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46181.5962658805</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>9731</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46181.5962658805</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>9732</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46181.596265937013</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>9733</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46181.596265937013</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>9734</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46181.596434552368</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>9735</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46181.596434552368</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>9736</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46181.596434552368</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>9737</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46181.59643460888</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>9738</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46181.59643460888</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>9739</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46181.59643460888</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>9740</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46181.59643460888</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>9741</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46181.59643460888</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>9742</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46181.5964346654</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>9743</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46181.5964346654</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>9744</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46181.596446126445</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>9745</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46181.596446182957</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>9746</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46181.596446182957</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>9747</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46181.59644623947</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>9748</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46181.596493473757</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>9749</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46181.596493473757</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>9750</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46181.596493473757</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>9751</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46181.596493530276</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>9752</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46181.596578674369</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>9753</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46181.596578674369</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>9754</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46181.596578674369</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>9755</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46181.596578730889</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>9756</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46181.596578730889</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>9757</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46181.596578730889</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>9758</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46181.596578730889</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>9759</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46181.596578787408</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>9760</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46181.596637765462</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>9761</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46181.596637765462</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>9762</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46181.596637821982</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>9763</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46181.596637821982</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>9764</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46181.596637821982</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>9765</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>9766</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>9767</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>9768</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>9769</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>9770</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46181.596637878494</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>9771</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46181.596637935007</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>9772</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46181.596637935007</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>9773</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46181.596637935007</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>9774</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46181.596637935007</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>9775</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46181.596649452564</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>9776</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46181.596649509083</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>9777</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46181.596722954768</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>9778</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46181.596722954768</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>9779</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46181.596723011287</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>9780</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46181.596723011287</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>9781</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46181.596734528845</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>9782</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46181.596734585364</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>9783</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46181.596734585364</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>9784</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46181.596734641877</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>9785</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46181.596781944128</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>9786</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46181.596781944128</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>9787</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46181.596782000648</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>9788</v>
+      </c>
+      <c r="C186" s="2">
+        <v>46181.596782000648</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>9789</v>
+      </c>
+      <c r="C187" s="2">
+        <v>46181.596782000648</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>9790</v>
+      </c>
+      <c r="C188" s="2">
+        <v>46181.59678206846</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>9791</v>
+      </c>
+      <c r="C189" s="2">
+        <v>46181.59678206846</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>9792</v>
+      </c>
+      <c r="C190" s="2">
+        <v>46181.59678206846</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>9793</v>
+      </c>
+      <c r="C191" s="2">
+        <v>46181.59678212498</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>9794</v>
+      </c>
+      <c r="C192" s="2">
+        <v>46181.596865822146</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>9795</v>
+      </c>
+      <c r="C193" s="2">
+        <v>46181.596865822146</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>9796</v>
+      </c>
+      <c r="C194" s="2">
+        <v>46181.596865822146</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>9797</v>
+      </c>
+      <c r="C195" s="2">
+        <v>46181.596865878666</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>9798</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46181.596865878666</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>9799</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46181.596865878666</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>9800</v>
+      </c>
+      <c r="C198" s="2">
+        <v>46181.596865878666</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>9801</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46181.596865935186</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>9802</v>
+      </c>
+      <c r="C200" s="2">
+        <v>46181.596924913239</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>9803</v>
+      </c>
+      <c r="C201" s="2">
+        <v>46181.596924913239</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>9804</v>
+      </c>
+      <c r="C202" s="2">
+        <v>46181.596924913239</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>9805</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46181.596924969759</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>9806</v>
+      </c>
+      <c r="C204" s="2">
+        <v>46181.596924969759</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>9807</v>
+      </c>
+      <c r="C205" s="2">
+        <v>46181.596925026271</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>9808</v>
+      </c>
+      <c r="C206" s="2">
+        <v>46181.596997567722</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>9809</v>
+      </c>
+      <c r="C207" s="2">
+        <v>46181.596997567722</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>9810</v>
+      </c>
+      <c r="C208" s="2">
+        <v>46181.596997624241</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>9811</v>
+      </c>
+      <c r="C209" s="2">
+        <v>46181.596997624241</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>9812</v>
+      </c>
+      <c r="C210" s="2">
+        <v>46181.596997624241</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>9813</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46181.596997680746</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>9814</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46181.596997680746</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>9815</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46181.596997680746</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>9816</v>
+      </c>
+      <c r="C214" s="2">
+        <v>46181.596997680746</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>9817</v>
+      </c>
+      <c r="C215" s="2">
+        <v>46181.596997748573</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>9818</v>
+      </c>
+      <c r="C216" s="2">
+        <v>46181.596997748573</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>9819</v>
+      </c>
+      <c r="C217" s="2">
+        <v>46181.597011345868</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>9820</v>
+      </c>
+      <c r="C218" s="2">
+        <v>46181.597011402388</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>9821</v>
+      </c>
+      <c r="C219" s="2">
+        <v>46181.597070380441</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>9822</v>
+      </c>
+      <c r="C220" s="2">
+        <v>46181.597070380441</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>9823</v>
+      </c>
+      <c r="C221" s="2">
+        <v>46181.597076167411</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>9824</v>
+      </c>
+      <c r="C222" s="2">
+        <v>46181.597076223923</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>9825</v>
+      </c>
+      <c r="C223" s="2">
+        <v>46181.597076223923</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>9826</v>
+      </c>
+      <c r="C224" s="2">
+        <v>46181.597076223923</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>9827</v>
+      </c>
+      <c r="C225" s="2">
+        <v>46181.597076223923</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>9828</v>
+      </c>
+      <c r="C226" s="2">
+        <v>46181.597076223923</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>9829</v>
+      </c>
+      <c r="C227" s="2">
+        <v>46181.597076280443</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>9830</v>
+      </c>
+      <c r="C228" s="2">
+        <v>46181.597076280443</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>9831</v>
+      </c>
+      <c r="C229" s="2">
+        <v>46181.597076280443</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>9832</v>
+      </c>
+      <c r="C230" s="2">
+        <v>46181.597076280443</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>9833</v>
+      </c>
+      <c r="C231" s="2">
+        <v>46181.597087798</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>9834</v>
+      </c>
+      <c r="C232" s="2">
+        <v>46181.597087798</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>9835</v>
+      </c>
+      <c r="C233" s="2">
+        <v>46181.597087854519</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>9836</v>
+      </c>
+      <c r="C234" s="2">
+        <v>46181.597087854519</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>9837</v>
+      </c>
+      <c r="C235" s="2">
+        <v>46181.597087854519</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>9838</v>
+      </c>
+      <c r="C236" s="2">
+        <v>46181.597087911025</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>9839</v>
+      </c>
+      <c r="C237" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>9840</v>
+      </c>
+      <c r="C238" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>9841</v>
+      </c>
+      <c r="C239" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>9842</v>
+      </c>
+      <c r="C240" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>9843</v>
+      </c>
+      <c r="C241" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>9844</v>
+      </c>
+      <c r="C242" s="2">
+        <v>46181.597235152651</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>9845</v>
+      </c>
+      <c r="C243" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>9846</v>
+      </c>
+      <c r="C244" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>9847</v>
+      </c>
+      <c r="C245" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>9848</v>
+      </c>
+      <c r="C246" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>9849</v>
+      </c>
+      <c r="C247" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>9850</v>
+      </c>
+      <c r="C248" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>9851</v>
+      </c>
+      <c r="C249" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>9852</v>
+      </c>
+      <c r="C250" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>9853</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>9854</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46181.597235209163</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>9855</v>
+      </c>
+      <c r="C253" s="2">
+        <v>46181.597235265675</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>9856</v>
+      </c>
+      <c r="C254" s="2">
+        <v>46181.597235265675</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>9857</v>
+      </c>
+      <c r="C255" s="2">
+        <v>46181.597235265675</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>9858</v>
+      </c>
+      <c r="C256" s="2">
+        <v>46181.597235265675</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>9859</v>
+      </c>
+      <c r="C257" s="2">
+        <v>46181.59724678324</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>9860</v>
+      </c>
+      <c r="C258" s="2">
+        <v>46181.597246839752</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>9861</v>
+      </c>
+      <c r="C259" s="2">
+        <v>46181.597299397887</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>9862</v>
+      </c>
+      <c r="C260" s="2">
+        <v>46181.597299397887</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>9863</v>
+      </c>
+      <c r="C261" s="2">
+        <v>46181.597299397887</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>9864</v>
+      </c>
+      <c r="C262" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>9865</v>
+      </c>
+      <c r="C263" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>9866</v>
+      </c>
+      <c r="C264" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>9867</v>
+      </c>
+      <c r="C265" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>9868</v>
+      </c>
+      <c r="C266" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>9869</v>
+      </c>
+      <c r="C267" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>9870</v>
+      </c>
+      <c r="C268" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>9871</v>
+      </c>
+      <c r="C269" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>9872</v>
+      </c>
+      <c r="C270" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>9873</v>
+      </c>
+      <c r="C271" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>9874</v>
+      </c>
+      <c r="C272" s="2">
+        <v>46181.597299454399</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>9875</v>
+      </c>
+      <c r="C273" s="2">
+        <v>46181.597299510919</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>9876</v>
+      </c>
+      <c r="C274" s="2">
+        <v>46181.597299510919</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>9877</v>
+      </c>
+      <c r="C275" s="2">
+        <v>46181.597299510919</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>9878</v>
+      </c>
+      <c r="C276" s="2">
+        <v>46181.597299510919</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>9879</v>
+      </c>
+      <c r="C277" s="2">
+        <v>46181.597299510919</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H277" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>9880</v>
+      </c>
+      <c r="C278" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H278" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>9881</v>
+      </c>
+      <c r="C279" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>9882</v>
+      </c>
+      <c r="C280" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H280" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>9883</v>
+      </c>
+      <c r="C281" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>9884</v>
+      </c>
+      <c r="C282" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>9885</v>
+      </c>
+      <c r="C283" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H283" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>9886</v>
+      </c>
+      <c r="C284" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>9887</v>
+      </c>
+      <c r="C285" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I285" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>9888</v>
+      </c>
+      <c r="C286" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H286" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I286" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>9889</v>
+      </c>
+      <c r="C287" s="2">
+        <v>46181.597507821636</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H287" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>9890</v>
+      </c>
+      <c r="C288" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H288" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I288" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>9891</v>
+      </c>
+      <c r="C289" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>9892</v>
+      </c>
+      <c r="C290" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H290" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I290" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>9893</v>
+      </c>
+      <c r="C291" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H291" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>9894</v>
+      </c>
+      <c r="C292" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H292" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>9895</v>
+      </c>
+      <c r="C293" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H293" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>9896</v>
+      </c>
+      <c r="C294" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>9897</v>
+      </c>
+      <c r="C295" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H295" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>9898</v>
+      </c>
+      <c r="C296" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>9899</v>
+      </c>
+      <c r="C297" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>9900</v>
+      </c>
+      <c r="C298" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H298" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>9901</v>
+      </c>
+      <c r="C299" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H299" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>9902</v>
+      </c>
+      <c r="C300" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H300" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>9903</v>
+      </c>
+      <c r="C301" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H301" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>9904</v>
+      </c>
+      <c r="C302" s="2">
+        <v>46181.597507878156</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H302" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>9905</v>
+      </c>
+      <c r="C303" s="2">
+        <v>46181.597507934675</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>9906</v>
+      </c>
+      <c r="C304" s="2">
+        <v>46181.597507934675</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>9907</v>
+      </c>
+      <c r="C305" s="2">
+        <v>46181.597507934675</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H305" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>9908</v>
+      </c>
+      <c r="C306" s="2">
+        <v>46181.597507934675</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H306" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>9909</v>
+      </c>
+      <c r="C307" s="2">
+        <v>46181.597507934675</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H307" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I307" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J59">
-    <sortCondition ref="A2:A59"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J307">
+    <sortCondition ref="A2:A307"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ЛО\pmi_lodzt\urov_mode\Журнал событий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ТокЗ\pmi_tokzdzt\rtponn_modes\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEB9E91D-1688-4CE5-B83B-534DC6066CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6934CBD0-7B0F-426E-9FDA-7A160CCACCAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1540" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="52">
   <si>
     <t>№</t>
   </si>
@@ -75,127 +75,103 @@
     <t>1</t>
   </si>
   <si>
+    <t>Слот M3.Реле5. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле6. Статус</t>
+  </si>
+  <si>
+    <t>Слот M4.Реле2. Статус</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО СН (НН1): Ввод</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО СН (НН1): Оперативный вывод</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО НН (НН2): Ввод</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО НН (НН2): Оперативный вывод</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО общ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Ввод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ РТПО НН2</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ4. Статус</t>
+  </si>
+  <si>
+    <t>ДВ: Вывод терминала</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-1_Опер. вывод</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ1. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле3. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле8. Статус</t>
+  </si>
+  <si>
+    <t>Слот M4.Реле1. Статус</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО СН (НН1): ИО Iмакс</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО СН (НН1): Пуск</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО НН (НН2): ИО Iмакс</t>
+  </si>
+  <si>
+    <t>РТПО / РТПО общ: Пуск</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-46_Опер. вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-45_Опер. вывод</t>
+  </si>
+  <si>
     <t>Слот M3.Реле7. Статус</t>
   </si>
   <si>
-    <t>Слот M4.Реле2. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле3. Статус</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: Ввод</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЛО: Срабатывание</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
-  </si>
-  <si>
-    <t>ЛО ВН / ЛО: Ввод</t>
-  </si>
-  <si>
-    <t>ЛО ВН / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
-    <t>СС / СС: Внеш. откл</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле8. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле4. Статус</t>
-  </si>
-  <si>
-    <t>ЛО ВН / ЛО: Отключение</t>
-  </si>
-  <si>
-    <t>ПС / ПС: Пуск</t>
-  </si>
-  <si>
-    <t>ДВ: Вывод терминала</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-1_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ1. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле1. Статус</t>
-  </si>
-  <si>
-    <t>ЛО ВН / ЛО: Отключить аварийно</t>
-  </si>
-  <si>
-    <t>ПС / ПС: Пуск (имп)</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле3. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле4. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле5. Статус</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: ИО Iмакс</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: Пуск</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: Срабатывание</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-52_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ЛО ВН</t>
+    <t>РТПО / РТПО НН (НН2): Пуск</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ РТПО НН1</t>
   </si>
   <si>
     <t>Слот M8. ДВ3. Статус</t>
   </si>
   <si>
-    <t>Внеш.откл. от СО</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ4. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле6. Статус</t>
-  </si>
-  <si>
-    <t>Пуск УРОВ внешний</t>
-  </si>
-  <si>
-    <t>УРОВ ВН / УРОВ: Сраб "на себя"</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ5. Статус</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-59_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ УРОВ</t>
+    <t>Виртуальный ключ-43_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ РТПО</t>
   </si>
   <si>
     <t>Слот M8. ДВ2. Статус</t>
@@ -606,7 +582,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J307"/>
+  <dimension ref="A1:J178"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -654,13 +630,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>9604</v>
+        <v>10569</v>
       </c>
       <c r="C2" s="2">
-        <v>46181.594941282056</v>
+        <v>46182.776274120202</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -677,13 +653,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>9605</v>
+        <v>10570</v>
       </c>
       <c r="C3" s="2">
-        <v>46181.594941282056</v>
+        <v>46182.776274120202</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -700,13 +676,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>9606</v>
+        <v>10571</v>
       </c>
       <c r="C4" s="2">
-        <v>46181.594950211242</v>
+        <v>46182.776274120202</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>19</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -723,13 +699,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>9607</v>
+        <v>10572</v>
       </c>
       <c r="C5" s="2">
-        <v>46181.594950211242</v>
+        <v>46182.776274120202</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -746,13 +722,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>9608</v>
+        <v>10573</v>
       </c>
       <c r="C6" s="2">
-        <v>46181.594950211242</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -769,13 +745,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>9609</v>
+        <v>10574</v>
       </c>
       <c r="C7" s="2">
-        <v>46181.594950211242</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -792,13 +768,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>9610</v>
+        <v>10575</v>
       </c>
       <c r="C8" s="2">
-        <v>46181.594950267761</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -815,13 +791,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>9611</v>
+        <v>10576</v>
       </c>
       <c r="C9" s="2">
-        <v>46181.594950267761</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -838,13 +814,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>9612</v>
+        <v>10577</v>
       </c>
       <c r="C10" s="2">
-        <v>46181.595579167122</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -861,13 +837,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>9613</v>
+        <v>10578</v>
       </c>
       <c r="C11" s="2">
-        <v>46181.595579234941</v>
+        <v>46182.776283151259</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -884,13 +860,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>9614</v>
+        <v>10579</v>
       </c>
       <c r="C12" s="2">
-        <v>46181.595638326027</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -902,18 +878,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>9615</v>
+        <v>10580</v>
       </c>
       <c r="C13" s="2">
-        <v>46181.595638326027</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -930,13 +906,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>9616</v>
+        <v>10581</v>
       </c>
       <c r="C14" s="2">
-        <v>46181.595638382547</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -948,18 +924,18 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>9617</v>
+        <v>10582</v>
       </c>
       <c r="C15" s="2">
-        <v>46181.595638382547</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -976,13 +952,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>9618</v>
+        <v>10583</v>
       </c>
       <c r="C16" s="2">
-        <v>46181.595638382547</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -994,18 +970,18 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>9619</v>
+        <v>10584</v>
       </c>
       <c r="C17" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -1017,18 +993,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>9620</v>
+        <v>10585</v>
       </c>
       <c r="C18" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -1045,13 +1021,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>9621</v>
+        <v>10586</v>
       </c>
       <c r="C19" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1063,18 +1039,18 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>9622</v>
+        <v>10587</v>
       </c>
       <c r="C20" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1091,13 +1067,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>9623</v>
+        <v>10588</v>
       </c>
       <c r="C21" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1114,13 +1090,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>9624</v>
+        <v>10589</v>
       </c>
       <c r="C22" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -1137,10 +1113,10 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>9625</v>
+        <v>10590</v>
       </c>
       <c r="C23" s="2">
-        <v>46181.595638439052</v>
+        <v>46182.776283207779</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>18</v>
@@ -1160,13 +1136,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>9626</v>
+        <v>10591</v>
       </c>
       <c r="C24" s="2">
-        <v>46181.595638495572</v>
+        <v>46182.776283264284</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -1183,13 +1159,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>9627</v>
+        <v>10592</v>
       </c>
       <c r="C25" s="2">
-        <v>46181.595638495572</v>
+        <v>46182.776283264284</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>41</v>
+        <v>14</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1206,13 +1182,13 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>9628</v>
+        <v>10593</v>
       </c>
       <c r="C26" s="2">
-        <v>46181.595638495572</v>
+        <v>46182.776283264284</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1224,18 +1200,18 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>9629</v>
+        <v>10594</v>
       </c>
       <c r="C27" s="2">
-        <v>46181.595638495572</v>
+        <v>46182.776283264284</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1252,13 +1228,13 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>9630</v>
+        <v>10595</v>
       </c>
       <c r="C28" s="2">
-        <v>46181.595638495572</v>
+        <v>46182.776283264284</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1270,18 +1246,18 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>9631</v>
+        <v>10596</v>
       </c>
       <c r="C29" s="2">
-        <v>46181.595650013129</v>
+        <v>46182.780207632706</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1293,18 +1269,18 @@
         <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>9632</v>
+        <v>10597</v>
       </c>
       <c r="C30" s="2">
-        <v>46181.595650013129</v>
+        <v>46182.780207632706</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1321,13 +1297,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>9633</v>
+        <v>10598</v>
       </c>
       <c r="C31" s="2">
-        <v>46181.595650069648</v>
+        <v>46182.780213419661</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1339,18 +1315,18 @@
         <v>12</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>9634</v>
+        <v>10599</v>
       </c>
       <c r="C32" s="2">
-        <v>46181.595650069648</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1367,13 +1343,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>9635</v>
+        <v>10600</v>
       </c>
       <c r="C33" s="2">
-        <v>46181.595650069648</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1390,13 +1366,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>9636</v>
+        <v>10601</v>
       </c>
       <c r="C34" s="2">
-        <v>46181.595650126168</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1408,18 +1384,18 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>9637</v>
+        <v>10602</v>
       </c>
       <c r="C35" s="2">
-        <v>46181.595709861518</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1431,18 +1407,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>9638</v>
+        <v>10603</v>
       </c>
       <c r="C36" s="2">
-        <v>46181.595709861518</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1459,13 +1435,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>9639</v>
+        <v>10604</v>
       </c>
       <c r="C37" s="2">
-        <v>46181.595709861518</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1482,13 +1458,13 @@
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>9640</v>
+        <v>10605</v>
       </c>
       <c r="C38" s="2">
-        <v>46181.595709918038</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1505,13 +1481,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>9641</v>
+        <v>10606</v>
       </c>
       <c r="C39" s="2">
-        <v>46181.595709918038</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1528,13 +1504,13 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>9642</v>
+        <v>10607</v>
       </c>
       <c r="C40" s="2">
-        <v>46181.595709918038</v>
+        <v>46182.780213476173</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1551,13 +1527,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>9643</v>
+        <v>10608</v>
       </c>
       <c r="C41" s="2">
-        <v>46181.595709918038</v>
+        <v>46182.780213532693</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1569,18 +1545,18 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>9644</v>
+        <v>10609</v>
       </c>
       <c r="C42" s="2">
-        <v>46181.595709974557</v>
+        <v>46182.780213532693</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1597,13 +1573,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>9645</v>
+        <v>10610</v>
       </c>
       <c r="C43" s="2">
-        <v>46181.595709974557</v>
+        <v>46182.780213532693</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1620,13 +1596,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>9646</v>
+        <v>10611</v>
       </c>
       <c r="C44" s="2">
-        <v>46181.595709974557</v>
+        <v>46182.780213532693</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1643,13 +1619,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>9647</v>
+        <v>10612</v>
       </c>
       <c r="C45" s="2">
-        <v>46181.595709974557</v>
+        <v>46182.780213532693</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1661,18 +1637,18 @@
         <v>12</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>9648</v>
+        <v>10613</v>
       </c>
       <c r="C46" s="2">
-        <v>46181.595782493401</v>
+        <v>46182.780321689293</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1684,18 +1660,18 @@
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>9649</v>
+        <v>10614</v>
       </c>
       <c r="C47" s="2">
-        <v>46181.595782493401</v>
+        <v>46182.780321689293</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1707,18 +1683,18 @@
         <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>9650</v>
+        <v>10615</v>
       </c>
       <c r="C48" s="2">
-        <v>46181.595782674238</v>
+        <v>46182.780321689293</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1735,13 +1711,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>9651</v>
+        <v>10616</v>
       </c>
       <c r="C49" s="2">
-        <v>46181.595782674238</v>
+        <v>46182.780321689293</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1758,13 +1734,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>9652</v>
+        <v>10617</v>
       </c>
       <c r="C50" s="2">
-        <v>46181.595782674238</v>
+        <v>46182.780321689293</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1781,13 +1757,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>9653</v>
+        <v>10618</v>
       </c>
       <c r="C51" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.78032175712</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1799,18 +1775,18 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>9654</v>
+        <v>10619</v>
       </c>
       <c r="C52" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.78032175712</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -1827,13 +1803,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>9655</v>
+        <v>10620</v>
       </c>
       <c r="C53" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.78032175712</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1845,18 +1821,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>9656</v>
+        <v>10621</v>
       </c>
       <c r="C54" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.78032175712</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1868,18 +1844,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>9657</v>
+        <v>10622</v>
       </c>
       <c r="C55" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.78032175712</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1896,13 +1872,13 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>9658</v>
+        <v>10623</v>
       </c>
       <c r="C56" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520245731</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1914,18 +1890,18 @@
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>9659</v>
+        <v>10624</v>
       </c>
       <c r="C57" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520245731</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1937,18 +1913,18 @@
         <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>9660</v>
+        <v>10625</v>
       </c>
       <c r="C58" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520245731</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -1965,13 +1941,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>9661</v>
+        <v>10626</v>
       </c>
       <c r="C59" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -1988,13 +1964,13 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>9662</v>
+        <v>10627</v>
       </c>
       <c r="C60" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -2006,18 +1982,18 @@
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>9663</v>
+        <v>10628</v>
       </c>
       <c r="C61" s="2">
-        <v>46181.595782730757</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -2034,13 +2010,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>9664</v>
+        <v>10629</v>
       </c>
       <c r="C62" s="2">
-        <v>46181.595782787277</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -2057,13 +2033,13 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>9665</v>
+        <v>10630</v>
       </c>
       <c r="C63" s="2">
-        <v>46181.595782787277</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -2075,18 +2051,18 @@
         <v>12</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>9666</v>
+        <v>10631</v>
       </c>
       <c r="C64" s="2">
-        <v>46181.595782787277</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>17</v>
+        <v>44</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -2103,13 +2079,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>9667</v>
+        <v>10632</v>
       </c>
       <c r="C65" s="2">
-        <v>46181.595782787277</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -2126,13 +2102,13 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>9668</v>
+        <v>10633</v>
       </c>
       <c r="C66" s="2">
-        <v>46181.595782787277</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -2149,13 +2125,13 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>9669</v>
+        <v>10634</v>
       </c>
       <c r="C67" s="2">
-        <v>46181.595788280363</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -2172,13 +2148,13 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>9670</v>
+        <v>10635</v>
       </c>
       <c r="C68" s="2">
-        <v>46181.595855735635</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -2190,18 +2166,18 @@
         <v>12</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>9671</v>
+        <v>10636</v>
       </c>
       <c r="C69" s="2">
-        <v>46181.595855735635</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -2218,13 +2194,13 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>9672</v>
+        <v>10637</v>
       </c>
       <c r="C70" s="2">
-        <v>46181.59586152259</v>
+        <v>46182.780520302244</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -2236,18 +2212,18 @@
         <v>12</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>9673</v>
+        <v>10638</v>
       </c>
       <c r="C71" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -2259,18 +2235,18 @@
         <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>9674</v>
+        <v>10639</v>
       </c>
       <c r="C72" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -2282,18 +2258,18 @@
         <v>12</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>9675</v>
+        <v>10640</v>
       </c>
       <c r="C73" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -2305,18 +2281,18 @@
         <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>9676</v>
+        <v>10641</v>
       </c>
       <c r="C74" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -2333,13 +2309,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>9677</v>
+        <v>10642</v>
       </c>
       <c r="C75" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -2356,13 +2332,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>9678</v>
+        <v>10643</v>
       </c>
       <c r="C76" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -2374,18 +2350,18 @@
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>9679</v>
+        <v>10644</v>
       </c>
       <c r="C77" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -2402,13 +2378,13 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>9680</v>
+        <v>10645</v>
       </c>
       <c r="C78" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780520358756</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -2420,18 +2396,18 @@
         <v>12</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>9681</v>
+        <v>10646</v>
       </c>
       <c r="C79" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780592357522</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -2443,18 +2419,18 @@
         <v>12</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>9682</v>
+        <v>10647</v>
       </c>
       <c r="C80" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.780592357522</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>11</v>
@@ -2471,13 +2447,13 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="1">
-        <v>9683</v>
+        <v>10648</v>
       </c>
       <c r="C81" s="2">
-        <v>46181.59586157911</v>
+        <v>46182.78059269661</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>11</v>
@@ -2494,13 +2470,13 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
-        <v>9684</v>
+        <v>10649</v>
       </c>
       <c r="C82" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.78059269661</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>11</v>
@@ -2517,13 +2493,13 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="1">
-        <v>9685</v>
+        <v>10650</v>
       </c>
       <c r="C83" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.78059269661</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>11</v>
@@ -2540,13 +2516,13 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="1">
-        <v>9686</v>
+        <v>10651</v>
       </c>
       <c r="C84" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780598144629</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>11</v>
@@ -2558,18 +2534,18 @@
         <v>12</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="1">
-        <v>9687</v>
+        <v>10652</v>
       </c>
       <c r="C85" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780598201149</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>11</v>
@@ -2586,13 +2562,13 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
-        <v>9688</v>
+        <v>10653</v>
       </c>
       <c r="C86" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780598201149</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>11</v>
@@ -2604,18 +2580,18 @@
         <v>12</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="1">
-        <v>9689</v>
+        <v>10654</v>
       </c>
       <c r="C87" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780598201149</v>
       </c>
       <c r="D87" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>11</v>
@@ -2632,13 +2608,13 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="1">
-        <v>9690</v>
+        <v>10655</v>
       </c>
       <c r="C88" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780598201149</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>11</v>
@@ -2655,13 +2631,13 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="1">
-        <v>9691</v>
+        <v>10656</v>
       </c>
       <c r="C89" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780662785321</v>
       </c>
       <c r="D89" s="3" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>11</v>
@@ -2673,18 +2649,18 @@
         <v>12</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="1">
-        <v>9692</v>
+        <v>10657</v>
       </c>
       <c r="C90" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780662785321</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>11</v>
@@ -2696,18 +2672,18 @@
         <v>12</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="1">
-        <v>9693</v>
+        <v>10658</v>
       </c>
       <c r="C91" s="2">
-        <v>46181.595861635629</v>
+        <v>46182.780663067897</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>11</v>
@@ -2724,13 +2700,13 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A92" s="1">
-        <v>9694</v>
+        <v>10659</v>
       </c>
       <c r="C92" s="2">
-        <v>46181.595861692142</v>
+        <v>46182.780663067897</v>
       </c>
       <c r="D92" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>11</v>
@@ -2742,18 +2718,18 @@
         <v>12</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A93" s="1">
-        <v>9695</v>
+        <v>10660</v>
       </c>
       <c r="C93" s="2">
-        <v>46181.595861692142</v>
+        <v>46182.780663067897</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>11</v>
@@ -2770,13 +2746,13 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A94" s="1">
-        <v>9696</v>
+        <v>10661</v>
       </c>
       <c r="C94" s="2">
-        <v>46181.595861692142</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>11</v>
@@ -2793,13 +2769,13 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A95" s="1">
-        <v>9697</v>
+        <v>10662</v>
       </c>
       <c r="C95" s="2">
-        <v>46181.595861692142</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>11</v>
@@ -2811,18 +2787,18 @@
         <v>12</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A96" s="1">
-        <v>9698</v>
+        <v>10663</v>
       </c>
       <c r="C96" s="2">
-        <v>46181.595861692142</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>11</v>
@@ -2839,13 +2815,13 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A97" s="1">
-        <v>9699</v>
+        <v>10664</v>
       </c>
       <c r="C97" s="2">
-        <v>46181.595873209706</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>11</v>
@@ -2862,13 +2838,13 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A98" s="1">
-        <v>9700</v>
+        <v>10665</v>
       </c>
       <c r="C98" s="2">
-        <v>46181.595873209706</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>11</v>
@@ -2880,18 +2856,18 @@
         <v>12</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A99" s="1">
-        <v>9701</v>
+        <v>10666</v>
       </c>
       <c r="C99" s="2">
-        <v>46181.595873266211</v>
+        <v>46182.780668572435</v>
       </c>
       <c r="D99" s="3" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>11</v>
@@ -2903,18 +2879,18 @@
         <v>12</v>
       </c>
       <c r="I99" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A100" s="1">
-        <v>9702</v>
+        <v>10667</v>
       </c>
       <c r="C100" s="2">
-        <v>46181.595873266211</v>
+        <v>46182.780668628948</v>
       </c>
       <c r="D100" s="3" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>11</v>
@@ -2931,13 +2907,13 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A101" s="1">
-        <v>9703</v>
+        <v>10668</v>
       </c>
       <c r="C101" s="2">
-        <v>46181.595873266211</v>
+        <v>46182.780668628948</v>
       </c>
       <c r="D101" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>11</v>
@@ -2954,13 +2930,13 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A102" s="1">
-        <v>9704</v>
+        <v>10669</v>
       </c>
       <c r="C102" s="2">
-        <v>46181.595873322731</v>
+        <v>46182.780668628948</v>
       </c>
       <c r="D102" s="3" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>11</v>
@@ -2972,18 +2948,18 @@
         <v>12</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A103" s="1">
-        <v>9705</v>
+        <v>10670</v>
       </c>
       <c r="C103" s="2">
-        <v>46181.595927384013</v>
+        <v>46182.780668628948</v>
       </c>
       <c r="D103" s="3" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>11</v>
@@ -2995,18 +2971,18 @@
         <v>12</v>
       </c>
       <c r="I103" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A104" s="1">
-        <v>9706</v>
+        <v>10671</v>
       </c>
       <c r="C104" s="2">
-        <v>46181.595927384013</v>
+        <v>46182.780668628948</v>
       </c>
       <c r="D104" s="3" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>11</v>
@@ -3018,18 +2994,18 @@
         <v>12</v>
       </c>
       <c r="I104" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A105" s="1">
-        <v>9707</v>
+        <v>10672</v>
       </c>
       <c r="C105" s="2">
-        <v>46181.595927440518</v>
+        <v>46182.780735349377</v>
       </c>
       <c r="D105" s="3" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>11</v>
@@ -3046,13 +3022,13 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A106" s="1">
-        <v>9708</v>
+        <v>10673</v>
       </c>
       <c r="C106" s="2">
-        <v>46181.595927440518</v>
+        <v>46182.780735349377</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>11</v>
@@ -3069,13 +3045,13 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A107" s="1">
-        <v>9709</v>
+        <v>10674</v>
       </c>
       <c r="C107" s="2">
-        <v>46181.595927440518</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D107" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>11</v>
@@ -3087,18 +3063,18 @@
         <v>12</v>
       </c>
       <c r="I107" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A108" s="1">
-        <v>9710</v>
+        <v>10675</v>
       </c>
       <c r="C108" s="2">
-        <v>46181.595927497037</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D108" s="3" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>11</v>
@@ -3115,13 +3091,13 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A109" s="1">
-        <v>9711</v>
+        <v>10676</v>
       </c>
       <c r="C109" s="2">
-        <v>46181.595927497037</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D109" s="3" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>11</v>
@@ -3133,18 +3109,18 @@
         <v>12</v>
       </c>
       <c r="I109" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A110" s="1">
-        <v>9712</v>
+        <v>10677</v>
       </c>
       <c r="C110" s="2">
-        <v>46181.595927497037</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>11</v>
@@ -3161,13 +3137,13 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A111" s="1">
-        <v>9713</v>
+        <v>10678</v>
       </c>
       <c r="C111" s="2">
-        <v>46181.595927497037</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D111" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>11</v>
@@ -3184,13 +3160,13 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A112" s="1">
-        <v>9714</v>
+        <v>10679</v>
       </c>
       <c r="C112" s="2">
-        <v>46181.595927497037</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D112" s="3" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>11</v>
@@ -3207,13 +3183,13 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="1">
-        <v>9715</v>
+        <v>10680</v>
       </c>
       <c r="C113" s="2">
-        <v>46181.595927553557</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D113" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>11</v>
@@ -3225,18 +3201,18 @@
         <v>12</v>
       </c>
       <c r="I113" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="1">
-        <v>9716</v>
+        <v>10681</v>
       </c>
       <c r="C114" s="2">
-        <v>46181.595927553557</v>
+        <v>46182.78073564326</v>
       </c>
       <c r="D114" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>11</v>
@@ -3248,18 +3224,18 @@
         <v>12</v>
       </c>
       <c r="I114" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="1">
-        <v>9717</v>
+        <v>10682</v>
       </c>
       <c r="C115" s="2">
-        <v>46181.595927553557</v>
+        <v>46182.780735699766</v>
       </c>
       <c r="D115" s="3" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>11</v>
@@ -3276,13 +3252,13 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A116" s="1">
-        <v>9718</v>
+        <v>10683</v>
       </c>
       <c r="C116" s="2">
-        <v>46181.595927553557</v>
+        <v>46182.780735699766</v>
       </c>
       <c r="D116" s="3" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>11</v>
@@ -3294,18 +3270,18 @@
         <v>12</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="1">
-        <v>9719</v>
+        <v>10684</v>
       </c>
       <c r="C117" s="2">
-        <v>46181.595927610062</v>
+        <v>46182.780735699766</v>
       </c>
       <c r="D117" s="3" t="s">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>11</v>
@@ -3322,13 +3298,13 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="1">
-        <v>9720</v>
+        <v>10685</v>
       </c>
       <c r="C118" s="2">
-        <v>46181.595999733305</v>
+        <v>46182.780735699766</v>
       </c>
       <c r="D118" s="3" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>11</v>
@@ -3340,18 +3316,18 @@
         <v>12</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="1">
-        <v>9721</v>
+        <v>10686</v>
       </c>
       <c r="C119" s="2">
-        <v>46181.595999733305</v>
+        <v>46182.780735699766</v>
       </c>
       <c r="D119" s="3" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>11</v>
@@ -3363,18 +3339,18 @@
         <v>12</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="1">
-        <v>9722</v>
+        <v>10687</v>
       </c>
       <c r="C120" s="2">
-        <v>46181.595999733305</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>11</v>
@@ -3391,13 +3367,13 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="1">
-        <v>9723</v>
+        <v>10688</v>
       </c>
       <c r="C121" s="2">
-        <v>46181.595999789824</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D121" s="3" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>11</v>
@@ -3409,18 +3385,18 @@
         <v>12</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="1">
-        <v>9724</v>
+        <v>10689</v>
       </c>
       <c r="C122" s="2">
-        <v>46181.595999789824</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D122" s="3" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>11</v>
@@ -3437,13 +3413,13 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="1">
-        <v>9725</v>
+        <v>10690</v>
       </c>
       <c r="C123" s="2">
-        <v>46181.595999789824</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D123" s="3" t="s">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>11</v>
@@ -3460,13 +3436,13 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A124" s="1">
-        <v>9726</v>
+        <v>10691</v>
       </c>
       <c r="C124" s="2">
-        <v>46181.595999846344</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D124" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>11</v>
@@ -3478,18 +3454,18 @@
         <v>12</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A125" s="1">
-        <v>9727</v>
+        <v>10692</v>
       </c>
       <c r="C125" s="2">
-        <v>46181.595999846344</v>
+        <v>46182.780741136339</v>
       </c>
       <c r="D125" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>11</v>
@@ -3501,18 +3477,18 @@
         <v>12</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="1">
-        <v>9728</v>
+        <v>10693</v>
       </c>
       <c r="C126" s="2">
-        <v>46181.596084640049</v>
+        <v>46182.780741192859</v>
       </c>
       <c r="D126" s="3" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>11</v>
@@ -3524,18 +3500,18 @@
         <v>12</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A127" s="1">
-        <v>9729</v>
+        <v>10694</v>
       </c>
       <c r="C127" s="2">
-        <v>46181.596084696554</v>
+        <v>46182.780741192859</v>
       </c>
       <c r="D127" s="3" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>11</v>
@@ -3552,13 +3528,13 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A128" s="1">
-        <v>9730</v>
+        <v>10695</v>
       </c>
       <c r="C128" s="2">
-        <v>46181.5962658805</v>
+        <v>46182.780741192859</v>
       </c>
       <c r="D128" s="3" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>11</v>
@@ -3570,18 +3546,18 @@
         <v>12</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A129" s="1">
-        <v>9731</v>
+        <v>10696</v>
       </c>
       <c r="C129" s="2">
-        <v>46181.5962658805</v>
+        <v>46182.780741192859</v>
       </c>
       <c r="D129" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>11</v>
@@ -3593,18 +3569,18 @@
         <v>12</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A130" s="1">
-        <v>9732</v>
+        <v>10697</v>
       </c>
       <c r="C130" s="2">
-        <v>46181.596265937013</v>
+        <v>46182.780741192859</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>11</v>
@@ -3616,18 +3592,18 @@
         <v>12</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A131" s="1">
-        <v>9733</v>
+        <v>10698</v>
       </c>
       <c r="C131" s="2">
-        <v>46181.596265937013</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D131" s="3" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>11</v>
@@ -3644,13 +3620,13 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A132" s="1">
-        <v>9734</v>
+        <v>10699</v>
       </c>
       <c r="C132" s="2">
-        <v>46181.596434552368</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D132" s="3" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>11</v>
@@ -3662,18 +3638,18 @@
         <v>12</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A133" s="1">
-        <v>9735</v>
+        <v>10700</v>
       </c>
       <c r="C133" s="2">
-        <v>46181.596434552368</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D133" s="3" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>11</v>
@@ -3685,18 +3661,18 @@
         <v>12</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A134" s="1">
-        <v>9736</v>
+        <v>10701</v>
       </c>
       <c r="C134" s="2">
-        <v>46181.596434552368</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D134" s="3" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>11</v>
@@ -3708,15 +3684,15 @@
         <v>12</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A135" s="1">
-        <v>9737</v>
+        <v>10702</v>
       </c>
       <c r="C135" s="2">
-        <v>46181.59643460888</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>39</v>
@@ -3731,18 +3707,18 @@
         <v>12</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A136" s="1">
-        <v>9738</v>
+        <v>10703</v>
       </c>
       <c r="C136" s="2">
-        <v>46181.59643460888</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D136" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>11</v>
@@ -3754,18 +3730,18 @@
         <v>12</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A137" s="1">
-        <v>9739</v>
+        <v>10704</v>
       </c>
       <c r="C137" s="2">
-        <v>46181.59643460888</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D137" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>11</v>
@@ -3777,18 +3753,18 @@
         <v>12</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A138" s="1">
-        <v>9740</v>
+        <v>10705</v>
       </c>
       <c r="C138" s="2">
-        <v>46181.59643460888</v>
+        <v>46182.780923428123</v>
       </c>
       <c r="D138" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>11</v>
@@ -3800,18 +3776,18 @@
         <v>12</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A139" s="1">
-        <v>9741</v>
+        <v>10706</v>
       </c>
       <c r="C139" s="2">
-        <v>46181.59643460888</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>11</v>
@@ -3823,18 +3799,18 @@
         <v>12</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A140" s="1">
-        <v>9742</v>
+        <v>10707</v>
       </c>
       <c r="C140" s="2">
-        <v>46181.5964346654</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D140" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>11</v>
@@ -3851,13 +3827,13 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A141" s="1">
-        <v>9743</v>
+        <v>10708</v>
       </c>
       <c r="C141" s="2">
-        <v>46181.5964346654</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D141" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>11</v>
@@ -3869,18 +3845,18 @@
         <v>12</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A142" s="1">
-        <v>9744</v>
+        <v>10709</v>
       </c>
       <c r="C142" s="2">
-        <v>46181.596446126445</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D142" s="3" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>11</v>
@@ -3892,18 +3868,18 @@
         <v>12</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A143" s="1">
-        <v>9745</v>
+        <v>10710</v>
       </c>
       <c r="C143" s="2">
-        <v>46181.596446182957</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D143" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>11</v>
@@ -3915,18 +3891,18 @@
         <v>12</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A144" s="1">
-        <v>9746</v>
+        <v>10711</v>
       </c>
       <c r="C144" s="2">
-        <v>46181.596446182957</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D144" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>11</v>
@@ -3938,18 +3914,18 @@
         <v>12</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A145" s="1">
-        <v>9747</v>
+        <v>10712</v>
       </c>
       <c r="C145" s="2">
-        <v>46181.59644623947</v>
+        <v>46182.780923484635</v>
       </c>
       <c r="D145" s="3" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>11</v>
@@ -3966,13 +3942,13 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A146" s="1">
-        <v>9748</v>
+        <v>10713</v>
       </c>
       <c r="C146" s="2">
-        <v>46181.596493473757</v>
+        <v>46182.780955720213</v>
       </c>
       <c r="D146" s="3" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>11</v>
@@ -3984,18 +3960,18 @@
         <v>12</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A147" s="1">
-        <v>9749</v>
+        <v>10714</v>
       </c>
       <c r="C147" s="2">
-        <v>46181.596493473757</v>
+        <v>46182.780955720213</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>11</v>
@@ -4007,18 +3983,18 @@
         <v>12</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A148" s="1">
-        <v>9750</v>
+        <v>10715</v>
       </c>
       <c r="C148" s="2">
-        <v>46181.596493473757</v>
+        <v>46182.780955720213</v>
       </c>
       <c r="D148" s="3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>11</v>
@@ -4030,18 +4006,18 @@
         <v>12</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A149" s="1">
-        <v>9751</v>
+        <v>10716</v>
       </c>
       <c r="C149" s="2">
-        <v>46181.596493530276</v>
+        <v>46182.780955776725</v>
       </c>
       <c r="D149" s="3" t="s">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>11</v>
@@ -4058,13 +4034,13 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A150" s="1">
-        <v>9752</v>
+        <v>10717</v>
       </c>
       <c r="C150" s="2">
-        <v>46181.596578674369</v>
+        <v>46182.780955776725</v>
       </c>
       <c r="D150" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>11</v>
@@ -4076,18 +4052,18 @@
         <v>12</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A151" s="1">
-        <v>9753</v>
+        <v>10718</v>
       </c>
       <c r="C151" s="2">
-        <v>46181.596578674369</v>
+        <v>46182.780955776725</v>
       </c>
       <c r="D151" s="3" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>11</v>
@@ -4104,13 +4080,13 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A152" s="1">
-        <v>9754</v>
+        <v>10719</v>
       </c>
       <c r="C152" s="2">
-        <v>46181.596578674369</v>
+        <v>46182.780955776725</v>
       </c>
       <c r="D152" s="3" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>11</v>
@@ -4122,18 +4098,18 @@
         <v>12</v>
       </c>
       <c r="I152" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A153" s="1">
-        <v>9755</v>
+        <v>10720</v>
       </c>
       <c r="C153" s="2">
-        <v>46181.596578730889</v>
+        <v>46182.780956070601</v>
       </c>
       <c r="D153" s="3" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>11</v>
@@ -4150,13 +4126,13 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A154" s="1">
-        <v>9756</v>
+        <v>10721</v>
       </c>
       <c r="C154" s="2">
-        <v>46181.596578730889</v>
+        <v>46182.780956070601</v>
       </c>
       <c r="D154" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>11</v>
@@ -4173,13 +4149,13 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
-        <v>9757</v>
+        <v>10722</v>
       </c>
       <c r="C155" s="2">
-        <v>46181.596578730889</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D155" s="3" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>11</v>
@@ -4191,18 +4167,18 @@
         <v>12</v>
       </c>
       <c r="I155" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
-        <v>9758</v>
+        <v>10723</v>
       </c>
       <c r="C156" s="2">
-        <v>46181.596578730889</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>11</v>
@@ -4214,18 +4190,18 @@
         <v>12</v>
       </c>
       <c r="I156" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
-        <v>9759</v>
+        <v>10724</v>
       </c>
       <c r="C157" s="2">
-        <v>46181.596578787408</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>11</v>
@@ -4237,18 +4213,18 @@
         <v>12</v>
       </c>
       <c r="I157" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
-        <v>9760</v>
+        <v>10725</v>
       </c>
       <c r="C158" s="2">
-        <v>46181.596637765462</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D158" s="3" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>11</v>
@@ -4265,13 +4241,13 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
-        <v>9761</v>
+        <v>10726</v>
       </c>
       <c r="C159" s="2">
-        <v>46181.596637765462</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D159" s="3" t="s">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>11</v>
@@ -4283,18 +4259,18 @@
         <v>12</v>
       </c>
       <c r="I159" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
-        <v>9762</v>
+        <v>10727</v>
       </c>
       <c r="C160" s="2">
-        <v>46181.596637821982</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D160" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>11</v>
@@ -4311,13 +4287,13 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
-        <v>9763</v>
+        <v>10728</v>
       </c>
       <c r="C161" s="2">
-        <v>46181.596637821982</v>
+        <v>46182.781178057747</v>
       </c>
       <c r="D161" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>11</v>
@@ -4329,18 +4305,18 @@
         <v>12</v>
       </c>
       <c r="I161" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
-        <v>9764</v>
+        <v>10729</v>
       </c>
       <c r="C162" s="2">
-        <v>46181.596637821982</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D162" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>11</v>
@@ -4352,18 +4328,18 @@
         <v>12</v>
       </c>
       <c r="I162" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
-        <v>9765</v>
+        <v>10730</v>
       </c>
       <c r="C163" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D163" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>11</v>
@@ -4380,13 +4356,13 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
-        <v>9766</v>
+        <v>10731</v>
       </c>
       <c r="C164" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D164" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>11</v>
@@ -4398,18 +4374,18 @@
         <v>12</v>
       </c>
       <c r="I164" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
-        <v>9767</v>
+        <v>10732</v>
       </c>
       <c r="C165" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D165" s="3" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>11</v>
@@ -4426,13 +4402,13 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
-        <v>9768</v>
+        <v>10733</v>
       </c>
       <c r="C166" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D166" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>11</v>
@@ -4444,18 +4420,18 @@
         <v>12</v>
       </c>
       <c r="I166" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A167" s="1">
-        <v>9769</v>
+        <v>10734</v>
       </c>
       <c r="C167" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D167" s="3" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>11</v>
@@ -4467,18 +4443,18 @@
         <v>12</v>
       </c>
       <c r="I167" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A168" s="1">
-        <v>9770</v>
+        <v>10735</v>
       </c>
       <c r="C168" s="2">
-        <v>46181.596637878494</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D168" s="3" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>11</v>
@@ -4495,13 +4471,13 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A169" s="1">
-        <v>9771</v>
+        <v>10736</v>
       </c>
       <c r="C169" s="2">
-        <v>46181.596637935007</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D169" s="3" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>11</v>
@@ -4518,13 +4494,13 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A170" s="1">
-        <v>9772</v>
+        <v>10737</v>
       </c>
       <c r="C170" s="2">
-        <v>46181.596637935007</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>11</v>
@@ -4541,13 +4517,13 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A171" s="1">
-        <v>9773</v>
+        <v>10738</v>
       </c>
       <c r="C171" s="2">
-        <v>46181.596637935007</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D171" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>11</v>
@@ -4564,13 +4540,13 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A172" s="1">
-        <v>9774</v>
+        <v>10739</v>
       </c>
       <c r="C172" s="2">
-        <v>46181.596637935007</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D172" s="3" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>11</v>
@@ -4587,13 +4563,13 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A173" s="1">
-        <v>9775</v>
+        <v>10740</v>
       </c>
       <c r="C173" s="2">
-        <v>46181.596649452564</v>
+        <v>46182.781178114266</v>
       </c>
       <c r="D173" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>11</v>
@@ -4605,18 +4581,18 @@
         <v>12</v>
       </c>
       <c r="I173" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A174" s="1">
-        <v>9776</v>
+        <v>10741</v>
       </c>
       <c r="C174" s="2">
-        <v>46181.596649509083</v>
+        <v>46182.781178170779</v>
       </c>
       <c r="D174" s="3" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>11</v>
@@ -4633,13 +4609,13 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A175" s="1">
-        <v>9777</v>
+        <v>10742</v>
       </c>
       <c r="C175" s="2">
-        <v>46181.596722954768</v>
+        <v>46182.781178170779</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>11</v>
@@ -4656,13 +4632,13 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A176" s="1">
-        <v>9778</v>
+        <v>10743</v>
       </c>
       <c r="C176" s="2">
-        <v>46181.596722954768</v>
+        <v>46182.781178170779</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>11</v>
@@ -4674,18 +4650,18 @@
         <v>12</v>
       </c>
       <c r="I176" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A177" s="1">
-        <v>9779</v>
+        <v>10744</v>
       </c>
       <c r="C177" s="2">
-        <v>46181.596723011287</v>
+        <v>46182.781178170779</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>11</v>
@@ -4702,13 +4678,13 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A178" s="1">
-        <v>9780</v>
+        <v>10745</v>
       </c>
       <c r="C178" s="2">
-        <v>46181.596723011287</v>
+        <v>46182.781178170779</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>11</v>
@@ -4720,2979 +4696,12 @@
         <v>12</v>
       </c>
       <c r="I178" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A179" s="1">
-        <v>9781</v>
-      </c>
-      <c r="C179" s="2">
-        <v>46181.596734528845</v>
-      </c>
-      <c r="D179" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F179" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G179" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H179" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I179" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A180" s="1">
-        <v>9782</v>
-      </c>
-      <c r="C180" s="2">
-        <v>46181.596734585364</v>
-      </c>
-      <c r="D180" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F180" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G180" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H180" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I180" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A181" s="1">
-        <v>9783</v>
-      </c>
-      <c r="C181" s="2">
-        <v>46181.596734585364</v>
-      </c>
-      <c r="D181" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F181" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G181" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H181" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I181" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A182" s="1">
-        <v>9784</v>
-      </c>
-      <c r="C182" s="2">
-        <v>46181.596734641877</v>
-      </c>
-      <c r="D182" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F182" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G182" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H182" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I182" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A183" s="1">
-        <v>9785</v>
-      </c>
-      <c r="C183" s="2">
-        <v>46181.596781944128</v>
-      </c>
-      <c r="D183" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F183" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G183" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H183" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I183" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A184" s="1">
-        <v>9786</v>
-      </c>
-      <c r="C184" s="2">
-        <v>46181.596781944128</v>
-      </c>
-      <c r="D184" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F184" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G184" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H184" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I184" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A185" s="1">
-        <v>9787</v>
-      </c>
-      <c r="C185" s="2">
-        <v>46181.596782000648</v>
-      </c>
-      <c r="D185" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F185" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G185" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H185" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I185" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A186" s="1">
-        <v>9788</v>
-      </c>
-      <c r="C186" s="2">
-        <v>46181.596782000648</v>
-      </c>
-      <c r="D186" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F186" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G186" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H186" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I186" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A187" s="1">
-        <v>9789</v>
-      </c>
-      <c r="C187" s="2">
-        <v>46181.596782000648</v>
-      </c>
-      <c r="D187" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G187" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H187" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I187" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A188" s="1">
-        <v>9790</v>
-      </c>
-      <c r="C188" s="2">
-        <v>46181.59678206846</v>
-      </c>
-      <c r="D188" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F188" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G188" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H188" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I188" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A189" s="1">
-        <v>9791</v>
-      </c>
-      <c r="C189" s="2">
-        <v>46181.59678206846</v>
-      </c>
-      <c r="D189" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F189" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G189" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H189" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I189" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="1">
-        <v>9792</v>
-      </c>
-      <c r="C190" s="2">
-        <v>46181.59678206846</v>
-      </c>
-      <c r="D190" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F190" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G190" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H190" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I190" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A191" s="1">
-        <v>9793</v>
-      </c>
-      <c r="C191" s="2">
-        <v>46181.59678212498</v>
-      </c>
-      <c r="D191" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F191" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G191" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H191" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I191" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A192" s="1">
-        <v>9794</v>
-      </c>
-      <c r="C192" s="2">
-        <v>46181.596865822146</v>
-      </c>
-      <c r="D192" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F192" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G192" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H192" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I192" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A193" s="1">
-        <v>9795</v>
-      </c>
-      <c r="C193" s="2">
-        <v>46181.596865822146</v>
-      </c>
-      <c r="D193" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F193" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G193" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H193" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I193" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A194" s="1">
-        <v>9796</v>
-      </c>
-      <c r="C194" s="2">
-        <v>46181.596865822146</v>
-      </c>
-      <c r="D194" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F194" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G194" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H194" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I194" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="1">
-        <v>9797</v>
-      </c>
-      <c r="C195" s="2">
-        <v>46181.596865878666</v>
-      </c>
-      <c r="D195" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F195" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G195" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H195" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I195" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="1">
-        <v>9798</v>
-      </c>
-      <c r="C196" s="2">
-        <v>46181.596865878666</v>
-      </c>
-      <c r="D196" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F196" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G196" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H196" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I196" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A197" s="1">
-        <v>9799</v>
-      </c>
-      <c r="C197" s="2">
-        <v>46181.596865878666</v>
-      </c>
-      <c r="D197" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F197" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G197" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H197" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I197" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="1">
-        <v>9800</v>
-      </c>
-      <c r="C198" s="2">
-        <v>46181.596865878666</v>
-      </c>
-      <c r="D198" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F198" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G198" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H198" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I198" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="1">
-        <v>9801</v>
-      </c>
-      <c r="C199" s="2">
-        <v>46181.596865935186</v>
-      </c>
-      <c r="D199" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F199" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G199" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H199" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I199" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="1">
-        <v>9802</v>
-      </c>
-      <c r="C200" s="2">
-        <v>46181.596924913239</v>
-      </c>
-      <c r="D200" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F200" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G200" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H200" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I200" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A201" s="1">
-        <v>9803</v>
-      </c>
-      <c r="C201" s="2">
-        <v>46181.596924913239</v>
-      </c>
-      <c r="D201" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F201" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G201" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H201" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I201" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A202" s="1">
-        <v>9804</v>
-      </c>
-      <c r="C202" s="2">
-        <v>46181.596924913239</v>
-      </c>
-      <c r="D202" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F202" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G202" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H202" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I202" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="1">
-        <v>9805</v>
-      </c>
-      <c r="C203" s="2">
-        <v>46181.596924969759</v>
-      </c>
-      <c r="D203" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F203" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G203" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H203" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I203" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="1">
-        <v>9806</v>
-      </c>
-      <c r="C204" s="2">
-        <v>46181.596924969759</v>
-      </c>
-      <c r="D204" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F204" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G204" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H204" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I204" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A205" s="1">
-        <v>9807</v>
-      </c>
-      <c r="C205" s="2">
-        <v>46181.596925026271</v>
-      </c>
-      <c r="D205" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F205" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G205" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H205" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I205" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="1">
-        <v>9808</v>
-      </c>
-      <c r="C206" s="2">
-        <v>46181.596997567722</v>
-      </c>
-      <c r="D206" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F206" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G206" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H206" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I206" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="1">
-        <v>9809</v>
-      </c>
-      <c r="C207" s="2">
-        <v>46181.596997567722</v>
-      </c>
-      <c r="D207" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="F207" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G207" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H207" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I207" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="1">
-        <v>9810</v>
-      </c>
-      <c r="C208" s="2">
-        <v>46181.596997624241</v>
-      </c>
-      <c r="D208" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F208" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G208" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H208" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I208" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A209" s="1">
-        <v>9811</v>
-      </c>
-      <c r="C209" s="2">
-        <v>46181.596997624241</v>
-      </c>
-      <c r="D209" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F209" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G209" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H209" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I209" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="1">
-        <v>9812</v>
-      </c>
-      <c r="C210" s="2">
-        <v>46181.596997624241</v>
-      </c>
-      <c r="D210" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F210" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G210" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H210" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I210" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A211" s="1">
-        <v>9813</v>
-      </c>
-      <c r="C211" s="2">
-        <v>46181.596997680746</v>
-      </c>
-      <c r="D211" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F211" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G211" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H211" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I211" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A212" s="1">
-        <v>9814</v>
-      </c>
-      <c r="C212" s="2">
-        <v>46181.596997680746</v>
-      </c>
-      <c r="D212" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F212" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G212" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H212" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I212" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="1">
-        <v>9815</v>
-      </c>
-      <c r="C213" s="2">
-        <v>46181.596997680746</v>
-      </c>
-      <c r="D213" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F213" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G213" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H213" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I213" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="1">
-        <v>9816</v>
-      </c>
-      <c r="C214" s="2">
-        <v>46181.596997680746</v>
-      </c>
-      <c r="D214" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F214" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G214" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H214" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I214" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="1">
-        <v>9817</v>
-      </c>
-      <c r="C215" s="2">
-        <v>46181.596997748573</v>
-      </c>
-      <c r="D215" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F215" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G215" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H215" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I215" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="1">
-        <v>9818</v>
-      </c>
-      <c r="C216" s="2">
-        <v>46181.596997748573</v>
-      </c>
-      <c r="D216" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F216" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G216" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H216" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I216" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="1">
-        <v>9819</v>
-      </c>
-      <c r="C217" s="2">
-        <v>46181.597011345868</v>
-      </c>
-      <c r="D217" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F217" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G217" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H217" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I217" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A218" s="1">
-        <v>9820</v>
-      </c>
-      <c r="C218" s="2">
-        <v>46181.597011402388</v>
-      </c>
-      <c r="D218" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F218" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G218" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H218" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I218" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="1">
-        <v>9821</v>
-      </c>
-      <c r="C219" s="2">
-        <v>46181.597070380441</v>
-      </c>
-      <c r="D219" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="F219" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G219" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H219" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I219" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A220" s="1">
-        <v>9822</v>
-      </c>
-      <c r="C220" s="2">
-        <v>46181.597070380441</v>
-      </c>
-      <c r="D220" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F220" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G220" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H220" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I220" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A221" s="1">
-        <v>9823</v>
-      </c>
-      <c r="C221" s="2">
-        <v>46181.597076167411</v>
-      </c>
-      <c r="D221" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F221" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G221" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H221" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I221" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A222" s="1">
-        <v>9824</v>
-      </c>
-      <c r="C222" s="2">
-        <v>46181.597076223923</v>
-      </c>
-      <c r="D222" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F222" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G222" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H222" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I222" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A223" s="1">
-        <v>9825</v>
-      </c>
-      <c r="C223" s="2">
-        <v>46181.597076223923</v>
-      </c>
-      <c r="D223" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F223" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G223" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H223" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I223" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A224" s="1">
-        <v>9826</v>
-      </c>
-      <c r="C224" s="2">
-        <v>46181.597076223923</v>
-      </c>
-      <c r="D224" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F224" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G224" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H224" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I224" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A225" s="1">
-        <v>9827</v>
-      </c>
-      <c r="C225" s="2">
-        <v>46181.597076223923</v>
-      </c>
-      <c r="D225" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F225" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G225" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H225" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I225" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A226" s="1">
-        <v>9828</v>
-      </c>
-      <c r="C226" s="2">
-        <v>46181.597076223923</v>
-      </c>
-      <c r="D226" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F226" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G226" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H226" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I226" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A227" s="1">
-        <v>9829</v>
-      </c>
-      <c r="C227" s="2">
-        <v>46181.597076280443</v>
-      </c>
-      <c r="D227" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F227" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G227" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H227" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I227" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A228" s="1">
-        <v>9830</v>
-      </c>
-      <c r="C228" s="2">
-        <v>46181.597076280443</v>
-      </c>
-      <c r="D228" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F228" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G228" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H228" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I228" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A229" s="1">
-        <v>9831</v>
-      </c>
-      <c r="C229" s="2">
-        <v>46181.597076280443</v>
-      </c>
-      <c r="D229" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F229" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G229" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H229" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I229" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A230" s="1">
-        <v>9832</v>
-      </c>
-      <c r="C230" s="2">
-        <v>46181.597076280443</v>
-      </c>
-      <c r="D230" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F230" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G230" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H230" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I230" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A231" s="1">
-        <v>9833</v>
-      </c>
-      <c r="C231" s="2">
-        <v>46181.597087798</v>
-      </c>
-      <c r="D231" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F231" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G231" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H231" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I231" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A232" s="1">
-        <v>9834</v>
-      </c>
-      <c r="C232" s="2">
-        <v>46181.597087798</v>
-      </c>
-      <c r="D232" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F232" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G232" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H232" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I232" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A233" s="1">
-        <v>9835</v>
-      </c>
-      <c r="C233" s="2">
-        <v>46181.597087854519</v>
-      </c>
-      <c r="D233" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F233" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G233" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H233" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I233" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A234" s="1">
-        <v>9836</v>
-      </c>
-      <c r="C234" s="2">
-        <v>46181.597087854519</v>
-      </c>
-      <c r="D234" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F234" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G234" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H234" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I234" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A235" s="1">
-        <v>9837</v>
-      </c>
-      <c r="C235" s="2">
-        <v>46181.597087854519</v>
-      </c>
-      <c r="D235" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F235" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G235" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H235" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I235" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A236" s="1">
-        <v>9838</v>
-      </c>
-      <c r="C236" s="2">
-        <v>46181.597087911025</v>
-      </c>
-      <c r="D236" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F236" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G236" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H236" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I236" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A237" s="1">
-        <v>9839</v>
-      </c>
-      <c r="C237" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D237" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F237" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G237" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H237" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I237" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A238" s="1">
-        <v>9840</v>
-      </c>
-      <c r="C238" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D238" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="F238" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G238" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H238" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I238" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A239" s="1">
-        <v>9841</v>
-      </c>
-      <c r="C239" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D239" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F239" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G239" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H239" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I239" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A240" s="1">
-        <v>9842</v>
-      </c>
-      <c r="C240" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D240" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="F240" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G240" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H240" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I240" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A241" s="1">
-        <v>9843</v>
-      </c>
-      <c r="C241" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D241" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F241" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G241" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H241" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I241" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A242" s="1">
-        <v>9844</v>
-      </c>
-      <c r="C242" s="2">
-        <v>46181.597235152651</v>
-      </c>
-      <c r="D242" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F242" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G242" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H242" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I242" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A243" s="1">
-        <v>9845</v>
-      </c>
-      <c r="C243" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D243" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F243" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G243" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H243" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I243" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A244" s="1">
-        <v>9846</v>
-      </c>
-      <c r="C244" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D244" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F244" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G244" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H244" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I244" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A245" s="1">
-        <v>9847</v>
-      </c>
-      <c r="C245" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D245" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F245" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G245" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H245" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I245" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A246" s="1">
-        <v>9848</v>
-      </c>
-      <c r="C246" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D246" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F246" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G246" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H246" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I246" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A247" s="1">
-        <v>9849</v>
-      </c>
-      <c r="C247" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D247" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G247" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H247" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I247" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A248" s="1">
-        <v>9850</v>
-      </c>
-      <c r="C248" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D248" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F248" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G248" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H248" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I248" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A249" s="1">
-        <v>9851</v>
-      </c>
-      <c r="C249" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D249" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F249" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G249" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H249" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I249" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A250" s="1">
-        <v>9852</v>
-      </c>
-      <c r="C250" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D250" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F250" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G250" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H250" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I250" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A251" s="1">
-        <v>9853</v>
-      </c>
-      <c r="C251" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D251" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F251" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G251" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H251" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I251" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A252" s="1">
-        <v>9854</v>
-      </c>
-      <c r="C252" s="2">
-        <v>46181.597235209163</v>
-      </c>
-      <c r="D252" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F252" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G252" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H252" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I252" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A253" s="1">
-        <v>9855</v>
-      </c>
-      <c r="C253" s="2">
-        <v>46181.597235265675</v>
-      </c>
-      <c r="D253" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F253" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G253" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H253" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I253" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A254" s="1">
-        <v>9856</v>
-      </c>
-      <c r="C254" s="2">
-        <v>46181.597235265675</v>
-      </c>
-      <c r="D254" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F254" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G254" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H254" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I254" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A255" s="1">
-        <v>9857</v>
-      </c>
-      <c r="C255" s="2">
-        <v>46181.597235265675</v>
-      </c>
-      <c r="D255" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F255" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G255" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H255" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I255" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A256" s="1">
-        <v>9858</v>
-      </c>
-      <c r="C256" s="2">
-        <v>46181.597235265675</v>
-      </c>
-      <c r="D256" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F256" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G256" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H256" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I256" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A257" s="1">
-        <v>9859</v>
-      </c>
-      <c r="C257" s="2">
-        <v>46181.59724678324</v>
-      </c>
-      <c r="D257" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F257" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G257" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H257" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I257" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A258" s="1">
-        <v>9860</v>
-      </c>
-      <c r="C258" s="2">
-        <v>46181.597246839752</v>
-      </c>
-      <c r="D258" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F258" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G258" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H258" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I258" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A259" s="1">
-        <v>9861</v>
-      </c>
-      <c r="C259" s="2">
-        <v>46181.597299397887</v>
-      </c>
-      <c r="D259" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F259" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G259" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H259" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I259" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A260" s="1">
-        <v>9862</v>
-      </c>
-      <c r="C260" s="2">
-        <v>46181.597299397887</v>
-      </c>
-      <c r="D260" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F260" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G260" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H260" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I260" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A261" s="1">
-        <v>9863</v>
-      </c>
-      <c r="C261" s="2">
-        <v>46181.597299397887</v>
-      </c>
-      <c r="D261" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F261" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G261" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H261" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I261" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A262" s="1">
-        <v>9864</v>
-      </c>
-      <c r="C262" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D262" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F262" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G262" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H262" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I262" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A263" s="1">
-        <v>9865</v>
-      </c>
-      <c r="C263" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D263" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F263" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G263" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H263" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I263" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A264" s="1">
-        <v>9866</v>
-      </c>
-      <c r="C264" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D264" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F264" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G264" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H264" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I264" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A265" s="1">
-        <v>9867</v>
-      </c>
-      <c r="C265" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D265" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F265" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G265" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H265" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I265" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A266" s="1">
-        <v>9868</v>
-      </c>
-      <c r="C266" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D266" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F266" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G266" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H266" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I266" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A267" s="1">
-        <v>9869</v>
-      </c>
-      <c r="C267" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D267" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G267" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H267" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I267" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A268" s="1">
-        <v>9870</v>
-      </c>
-      <c r="C268" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D268" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F268" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G268" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H268" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I268" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A269" s="1">
-        <v>9871</v>
-      </c>
-      <c r="C269" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D269" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F269" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G269" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H269" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I269" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A270" s="1">
-        <v>9872</v>
-      </c>
-      <c r="C270" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D270" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F270" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G270" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H270" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I270" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A271" s="1">
-        <v>9873</v>
-      </c>
-      <c r="C271" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D271" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F271" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G271" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H271" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I271" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A272" s="1">
-        <v>9874</v>
-      </c>
-      <c r="C272" s="2">
-        <v>46181.597299454399</v>
-      </c>
-      <c r="D272" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F272" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G272" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H272" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I272" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A273" s="1">
-        <v>9875</v>
-      </c>
-      <c r="C273" s="2">
-        <v>46181.597299510919</v>
-      </c>
-      <c r="D273" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F273" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G273" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H273" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I273" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A274" s="1">
-        <v>9876</v>
-      </c>
-      <c r="C274" s="2">
-        <v>46181.597299510919</v>
-      </c>
-      <c r="D274" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F274" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G274" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H274" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I274" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A275" s="1">
-        <v>9877</v>
-      </c>
-      <c r="C275" s="2">
-        <v>46181.597299510919</v>
-      </c>
-      <c r="D275" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F275" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G275" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H275" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I275" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A276" s="1">
-        <v>9878</v>
-      </c>
-      <c r="C276" s="2">
-        <v>46181.597299510919</v>
-      </c>
-      <c r="D276" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F276" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G276" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H276" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I276" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A277" s="1">
-        <v>9879</v>
-      </c>
-      <c r="C277" s="2">
-        <v>46181.597299510919</v>
-      </c>
-      <c r="D277" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F277" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G277" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H277" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I277" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A278" s="1">
-        <v>9880</v>
-      </c>
-      <c r="C278" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D278" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F278" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G278" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H278" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I278" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A279" s="1">
-        <v>9881</v>
-      </c>
-      <c r="C279" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D279" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F279" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G279" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H279" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I279" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A280" s="1">
-        <v>9882</v>
-      </c>
-      <c r="C280" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D280" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F280" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G280" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H280" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I280" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A281" s="1">
-        <v>9883</v>
-      </c>
-      <c r="C281" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D281" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F281" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G281" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H281" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I281" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A282" s="1">
-        <v>9884</v>
-      </c>
-      <c r="C282" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D282" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F282" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G282" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H282" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I282" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A283" s="1">
-        <v>9885</v>
-      </c>
-      <c r="C283" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D283" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F283" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G283" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H283" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I283" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A284" s="1">
-        <v>9886</v>
-      </c>
-      <c r="C284" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D284" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F284" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G284" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H284" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I284" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A285" s="1">
-        <v>9887</v>
-      </c>
-      <c r="C285" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D285" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F285" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G285" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H285" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I285" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A286" s="1">
-        <v>9888</v>
-      </c>
-      <c r="C286" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D286" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F286" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G286" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H286" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I286" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A287" s="1">
-        <v>9889</v>
-      </c>
-      <c r="C287" s="2">
-        <v>46181.597507821636</v>
-      </c>
-      <c r="D287" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F287" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G287" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H287" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I287" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A288" s="1">
-        <v>9890</v>
-      </c>
-      <c r="C288" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D288" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F288" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G288" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H288" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I288" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A289" s="1">
-        <v>9891</v>
-      </c>
-      <c r="C289" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D289" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F289" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G289" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H289" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I289" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A290" s="1">
-        <v>9892</v>
-      </c>
-      <c r="C290" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D290" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F290" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G290" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H290" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I290" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A291" s="1">
-        <v>9893</v>
-      </c>
-      <c r="C291" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D291" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F291" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G291" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H291" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I291" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A292" s="1">
-        <v>9894</v>
-      </c>
-      <c r="C292" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D292" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F292" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G292" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H292" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I292" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A293" s="1">
-        <v>9895</v>
-      </c>
-      <c r="C293" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D293" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G293" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H293" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I293" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A294" s="1">
-        <v>9896</v>
-      </c>
-      <c r="C294" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D294" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F294" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G294" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H294" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I294" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A295" s="1">
-        <v>9897</v>
-      </c>
-      <c r="C295" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D295" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F295" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G295" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H295" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I295" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A296" s="1">
-        <v>9898</v>
-      </c>
-      <c r="C296" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D296" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F296" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G296" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H296" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I296" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A297" s="1">
-        <v>9899</v>
-      </c>
-      <c r="C297" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D297" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F297" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G297" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H297" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I297" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A298" s="1">
-        <v>9900</v>
-      </c>
-      <c r="C298" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D298" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F298" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G298" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H298" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I298" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A299" s="1">
-        <v>9901</v>
-      </c>
-      <c r="C299" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D299" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F299" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G299" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H299" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I299" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A300" s="1">
-        <v>9902</v>
-      </c>
-      <c r="C300" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D300" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F300" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G300" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H300" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I300" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A301" s="1">
-        <v>9903</v>
-      </c>
-      <c r="C301" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D301" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F301" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G301" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H301" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I301" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A302" s="1">
-        <v>9904</v>
-      </c>
-      <c r="C302" s="2">
-        <v>46181.597507878156</v>
-      </c>
-      <c r="D302" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F302" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G302" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H302" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I302" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A303" s="1">
-        <v>9905</v>
-      </c>
-      <c r="C303" s="2">
-        <v>46181.597507934675</v>
-      </c>
-      <c r="D303" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F303" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G303" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H303" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I303" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A304" s="1">
-        <v>9906</v>
-      </c>
-      <c r="C304" s="2">
-        <v>46181.597507934675</v>
-      </c>
-      <c r="D304" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F304" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G304" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H304" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I304" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A305" s="1">
-        <v>9907</v>
-      </c>
-      <c r="C305" s="2">
-        <v>46181.597507934675</v>
-      </c>
-      <c r="D305" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F305" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G305" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H305" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I305" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A306" s="1">
-        <v>9908</v>
-      </c>
-      <c r="C306" s="2">
-        <v>46181.597507934675</v>
-      </c>
-      <c r="D306" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F306" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G306" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H306" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I306" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A307" s="1">
-        <v>9909</v>
-      </c>
-      <c r="C307" s="2">
-        <v>46181.597507934675</v>
-      </c>
-      <c r="D307" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F307" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G307" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H307" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I307" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J307">
-    <sortCondition ref="A2:A307"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J178">
+    <sortCondition ref="A2:A178"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ТокЗ\pmi_tokzdzt\tozponn_modes\Журнал событий\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89EC581F-44FE-49E7-B0F0-4A575E41C7FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282C5289-DB4B-4A73-942F-F73DAE70AE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="41">
   <si>
     <t>№</t>
   </si>
@@ -57,30 +57,54 @@
     <t>Ед. изм.</t>
   </si>
   <si>
+    <t>Слот M3.Реле1. Статус</t>
+  </si>
+  <si>
+    <t>Хорошее [0]</t>
+  </si>
+  <si>
+    <t>System</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле2. Статус</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле6. Статус</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО ВН: Ввод</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО ВН: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО общ: Ввод</t>
+  </si>
+  <si>
     <t>ЛО Т / ЛО: Ввод</t>
   </si>
   <si>
-    <t>Хорошее [0]</t>
-  </si>
-  <si>
-    <t>System</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
     <t>ЛО Т / ЛО: Оперативный вывод</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>ЛО Т / ЗАПВ: Ввод</t>
   </si>
   <si>
     <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
   </si>
   <si>
+    <t>ДВ: ОВ ТО ЗПО ВН</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ3. Статус</t>
+  </si>
+  <si>
     <t>ДВ: Вывод терминала</t>
   </si>
   <si>
@@ -90,97 +114,40 @@
     <t>Слот M8. ДВ1. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле1. Статус</t>
+    <t>Слот M3.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО ВН: ИО Iмакс</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-35_Опер. вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-34_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ ТО ЗПО</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ2. Статус</t>
   </si>
   <si>
     <t>Слот M3.Реле3. Статус</t>
   </si>
   <si>
-    <t>Слот M3.Реле4. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле6. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле8. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле1. Статус</t>
-  </si>
-  <si>
-    <t>Слот M4.Реле2. Статус</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО СН (НН1): Ввод</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО СН (НН1): ИО Iмакс</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО СН (НН1): Пуск</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО НН (НН2): Оперативный вывод</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО НН (НН2): ИО Iмакс</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО общ: Ввод</t>
+    <t>Слот M3.Реле5. Статус</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО ВН: Пуск</t>
   </si>
   <si>
     <t>ТО ЗПО / ТО ЗПО общ: Пуск</t>
   </si>
   <si>
-    <t>Виртуальный ключ-37_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле2. Статус</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО СН (НН1): Оперативный вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-36_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле5. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле7. Статус</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ТО ЗПО НН2</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО НН (НН2): Ввод</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО НН (НН2): Пуск</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ4. Статус</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ТО ЗПО НН1</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ3. Статус</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-34_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ТО ЗПО</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ2. Статус</t>
+    <t>Наличие внешнего питания (общий)</t>
   </si>
   <si>
     <t>Статус светодиода "Готовность"</t>
-  </si>
-  <si>
-    <t>Наличие внешнего питания (общий)</t>
   </si>
 </sst>
 </file>
@@ -582,7 +549,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J118"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -630,13 +597,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>12563</v>
+        <v>12752</v>
       </c>
       <c r="C2" s="2">
-        <v>46183.813321589863</v>
+        <v>46184.552524154111</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -653,13 +620,13 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>12564</v>
+        <v>12753</v>
       </c>
       <c r="C3" s="2">
-        <v>46183.813321804475</v>
+        <v>46184.552524154111</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -676,13 +643,13 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>12565</v>
+        <v>12754</v>
       </c>
       <c r="C4" s="2">
-        <v>46183.813329513083</v>
+        <v>46184.552533309499</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -699,13 +666,13 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>12566</v>
+        <v>12755</v>
       </c>
       <c r="C5" s="2">
-        <v>46183.813329513083</v>
+        <v>46184.552533309499</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -722,13 +689,13 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>12567</v>
+        <v>12756</v>
       </c>
       <c r="C6" s="2">
-        <v>46183.813329513083</v>
+        <v>46184.552533309499</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -745,13 +712,13 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>12568</v>
+        <v>12757</v>
       </c>
       <c r="C7" s="2">
-        <v>46183.813329513083</v>
+        <v>46184.552533309499</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -768,13 +735,13 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>12569</v>
+        <v>12758</v>
       </c>
       <c r="C8" s="2">
-        <v>46183.813329513083</v>
+        <v>46184.552533366019</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -791,13 +758,13 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>12570</v>
+        <v>12759</v>
       </c>
       <c r="C9" s="2">
-        <v>46183.813329580895</v>
+        <v>46184.552533366019</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -814,13 +781,13 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>12571</v>
+        <v>12760</v>
       </c>
       <c r="C10" s="2">
-        <v>46183.813329580895</v>
+        <v>46184.554472837168</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -837,13 +804,13 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>12572</v>
+        <v>12761</v>
       </c>
       <c r="C11" s="2">
-        <v>46183.813329580895</v>
+        <v>46184.554472837168</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -860,13 +827,13 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>12573</v>
+        <v>12762</v>
       </c>
       <c r="C12" s="2">
-        <v>46183.815193651091</v>
+        <v>46184.554472837168</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -883,13 +850,13 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12574</v>
+        <v>12763</v>
       </c>
       <c r="C13" s="2">
-        <v>46183.815193651091</v>
+        <v>46184.554472893673</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -906,13 +873,13 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12575</v>
+        <v>12764</v>
       </c>
       <c r="C14" s="2">
-        <v>46183.815193651091</v>
+        <v>46184.554472893673</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -929,13 +896,13 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>12576</v>
+        <v>12765</v>
       </c>
       <c r="C15" s="2">
-        <v>46183.815193651091</v>
+        <v>46184.554472893673</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -952,13 +919,13 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>12577</v>
+        <v>12766</v>
       </c>
       <c r="C16" s="2">
-        <v>46183.815193651091</v>
+        <v>46184.554675202686</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -975,13 +942,13 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>12578</v>
+        <v>12767</v>
       </c>
       <c r="C17" s="2">
-        <v>46183.815193707611</v>
+        <v>46184.554675202686</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -998,13 +965,13 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>12579</v>
+        <v>12768</v>
       </c>
       <c r="C18" s="2">
-        <v>46183.815193707611</v>
+        <v>46184.554675202686</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -1021,13 +988,13 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>12580</v>
+        <v>12769</v>
       </c>
       <c r="C19" s="2">
-        <v>46183.815193707611</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1039,18 +1006,18 @@
         <v>12</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>12581</v>
+        <v>12770</v>
       </c>
       <c r="C20" s="2">
-        <v>46183.815193707611</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1067,13 +1034,13 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>12582</v>
+        <v>12771</v>
       </c>
       <c r="C21" s="2">
-        <v>46183.815193707611</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1085,18 +1052,18 @@
         <v>12</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>12583</v>
+        <v>12772</v>
       </c>
       <c r="C22" s="2">
-        <v>46183.815396604223</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -1108,18 +1075,18 @@
         <v>12</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>12584</v>
+        <v>12773</v>
       </c>
       <c r="C23" s="2">
-        <v>46183.815396604223</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1131,15 +1098,15 @@
         <v>12</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>12585</v>
+        <v>12774</v>
       </c>
       <c r="C24" s="2">
-        <v>46183.815396604223</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>20</v>
@@ -1154,18 +1121,18 @@
         <v>12</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>12586</v>
+        <v>12775</v>
       </c>
       <c r="C25" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1177,18 +1144,18 @@
         <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>12587</v>
+        <v>12776</v>
       </c>
       <c r="C26" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1200,18 +1167,18 @@
         <v>12</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>12588</v>
+        <v>12777</v>
       </c>
       <c r="C27" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554675259205</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1223,18 +1190,18 @@
         <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>12589</v>
+        <v>12778</v>
       </c>
       <c r="C28" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.55467531571</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1251,13 +1218,13 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>12590</v>
+        <v>12779</v>
       </c>
       <c r="C29" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.55467531571</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1274,13 +1241,13 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>12591</v>
+        <v>12780</v>
       </c>
       <c r="C30" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.55467531571</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1297,13 +1264,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>12592</v>
+        <v>12781</v>
       </c>
       <c r="C31" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.55467531571</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1320,13 +1287,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>12593</v>
+        <v>12782</v>
       </c>
       <c r="C32" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.55467531571</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1343,13 +1310,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>12594</v>
+        <v>12783</v>
       </c>
       <c r="C33" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554747890928</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1366,13 +1333,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>12595</v>
+        <v>12784</v>
       </c>
       <c r="C34" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554747890928</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1384,18 +1351,18 @@
         <v>12</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>12596</v>
+        <v>12785</v>
       </c>
       <c r="C35" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554748173498</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1407,18 +1374,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>12597</v>
+        <v>12786</v>
       </c>
       <c r="C36" s="2">
-        <v>46183.815396660742</v>
+        <v>46184.554748173498</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1435,13 +1402,13 @@
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>12598</v>
+        <v>12787</v>
       </c>
       <c r="C37" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554748173498</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1453,18 +1420,18 @@
         <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>12599</v>
+        <v>12788</v>
       </c>
       <c r="C38" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554753678036</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1476,18 +1443,18 @@
         <v>12</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>12600</v>
+        <v>12789</v>
       </c>
       <c r="C39" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554753734556</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1499,18 +1466,18 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>12601</v>
+        <v>12790</v>
       </c>
       <c r="C40" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554753734556</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1527,13 +1494,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>12602</v>
+        <v>12791</v>
       </c>
       <c r="C41" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554753734556</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1550,13 +1517,13 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>12603</v>
+        <v>12792</v>
       </c>
       <c r="C42" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554753734556</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1573,13 +1540,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>12604</v>
+        <v>12793</v>
       </c>
       <c r="C43" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554820115896</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1596,13 +1563,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>12605</v>
+        <v>12794</v>
       </c>
       <c r="C44" s="2">
-        <v>46183.815396717247</v>
+        <v>46184.554820115896</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1619,13 +1586,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>12606</v>
+        <v>12795</v>
       </c>
       <c r="C45" s="2">
-        <v>46183.815469055247</v>
+        <v>46184.554820398473</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1637,18 +1604,18 @@
         <v>12</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>12607</v>
+        <v>12796</v>
       </c>
       <c r="C46" s="2">
-        <v>46183.815469055247</v>
+        <v>46184.554820398473</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1660,18 +1627,18 @@
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>12608</v>
+        <v>12797</v>
       </c>
       <c r="C47" s="2">
-        <v>46183.815469349131</v>
+        <v>46184.554820398473</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1688,13 +1655,13 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>12609</v>
+        <v>12798</v>
       </c>
       <c r="C48" s="2">
-        <v>46183.815469349131</v>
+        <v>46184.554825903011</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1706,18 +1673,18 @@
         <v>12</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>12610</v>
+        <v>12799</v>
       </c>
       <c r="C49" s="2">
-        <v>46183.815469349131</v>
+        <v>46184.55498011841</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1729,18 +1696,18 @@
         <v>12</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>12611</v>
+        <v>12800</v>
       </c>
       <c r="C50" s="2">
-        <v>46183.815474842209</v>
+        <v>46184.55498011841</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1757,13 +1724,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>12612</v>
+        <v>12801</v>
       </c>
       <c r="C51" s="2">
-        <v>46183.815474898729</v>
+        <v>46184.55498011841</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1775,15 +1742,15 @@
         <v>12</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>12613</v>
+        <v>12802</v>
       </c>
       <c r="C52" s="2">
-        <v>46183.815474898729</v>
+        <v>46184.554980174915</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>14</v>
@@ -1803,13 +1770,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>12614</v>
+        <v>12803</v>
       </c>
       <c r="C53" s="2">
-        <v>46183.815474898729</v>
+        <v>46184.554980174915</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1821,18 +1788,18 @@
         <v>12</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>12615</v>
+        <v>12804</v>
       </c>
       <c r="C54" s="2">
-        <v>46183.815474898729</v>
+        <v>46184.555002690104</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1844,18 +1811,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>12616</v>
+        <v>12805</v>
       </c>
       <c r="C55" s="2">
-        <v>46183.81554122371</v>
+        <v>46184.555002690104</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1867,18 +1834,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>12617</v>
+        <v>12806</v>
       </c>
       <c r="C56" s="2">
-        <v>46183.81554122371</v>
+        <v>46184.555002690104</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>49</v>
+        <v>28</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1890,18 +1857,18 @@
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>12618</v>
+        <v>12807</v>
       </c>
       <c r="C57" s="2">
-        <v>46183.815541506287</v>
+        <v>46184.555002746623</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1913,18 +1880,18 @@
         <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>12619</v>
+        <v>12808</v>
       </c>
       <c r="C58" s="2">
-        <v>46183.815541506287</v>
+        <v>46184.555002746623</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -1941,13 +1908,13 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>12620</v>
+        <v>12809</v>
       </c>
       <c r="C59" s="2">
-        <v>46183.815541506287</v>
+        <v>46184.555002746623</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -1959,18 +1926,18 @@
         <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>12621</v>
+        <v>12810</v>
       </c>
       <c r="C60" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555002746623</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -1987,13 +1954,13 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>12622</v>
+        <v>12811</v>
       </c>
       <c r="C61" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555003040492</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -2010,13 +1977,13 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>12623</v>
+        <v>12812</v>
       </c>
       <c r="C62" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555003040492</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -2028,18 +1995,18 @@
         <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>12624</v>
+        <v>12813</v>
       </c>
       <c r="C63" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -2056,13 +2023,13 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>12625</v>
+        <v>12814</v>
       </c>
       <c r="C64" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -2079,13 +2046,13 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>12626</v>
+        <v>12815</v>
       </c>
       <c r="C65" s="2">
-        <v>46183.815547010679</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -2097,18 +2064,18 @@
         <v>12</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>12627</v>
+        <v>12816</v>
       </c>
       <c r="C66" s="2">
-        <v>46183.815547067185</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -2120,18 +2087,18 @@
         <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>12628</v>
+        <v>12817</v>
       </c>
       <c r="C67" s="2">
-        <v>46183.815547067185</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -2143,18 +2110,18 @@
         <v>12</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>12629</v>
+        <v>12818</v>
       </c>
       <c r="C68" s="2">
-        <v>46183.815547067185</v>
+        <v>46184.555157843788</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -2166,18 +2133,18 @@
         <v>12</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>12630</v>
+        <v>12819</v>
       </c>
       <c r="C69" s="2">
-        <v>46183.815547067185</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -2189,18 +2156,18 @@
         <v>12</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>12631</v>
+        <v>12820</v>
       </c>
       <c r="C70" s="2">
-        <v>46183.815547067185</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -2217,13 +2184,13 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>12632</v>
+        <v>12821</v>
       </c>
       <c r="C71" s="2">
-        <v>46183.815613267834</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -2240,13 +2207,13 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>12633</v>
+        <v>12822</v>
       </c>
       <c r="C72" s="2">
-        <v>46183.815613267834</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -2263,13 +2230,13 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>12634</v>
+        <v>12823</v>
       </c>
       <c r="C73" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -2286,13 +2253,13 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>12635</v>
+        <v>12824</v>
       </c>
       <c r="C74" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -2309,13 +2276,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>12636</v>
+        <v>12825</v>
       </c>
       <c r="C75" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -2332,13 +2299,13 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>12637</v>
+        <v>12826</v>
       </c>
       <c r="C76" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -2350,18 +2317,18 @@
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>12638</v>
+        <v>12827</v>
       </c>
       <c r="C77" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157900308</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -2373,18 +2340,18 @@
         <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>12639</v>
+        <v>12828</v>
       </c>
       <c r="C78" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157956813</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -2401,13 +2368,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>12640</v>
+        <v>12829</v>
       </c>
       <c r="C79" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157956813</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -2424,13 +2391,13 @@
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>12641</v>
+        <v>12830</v>
       </c>
       <c r="C80" s="2">
-        <v>46183.815613561565</v>
+        <v>46184.555157956813</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>11</v>
@@ -2442,886 +2409,12 @@
         <v>12</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="1">
-        <v>12642</v>
-      </c>
-      <c r="C81" s="2">
-        <v>46183.815613618077</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H81" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="1">
-        <v>12643</v>
-      </c>
-      <c r="C82" s="2">
-        <v>46183.815613618077</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="1">
-        <v>12644</v>
-      </c>
-      <c r="C83" s="2">
-        <v>46183.815613618077</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H83" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="1">
-        <v>12645</v>
-      </c>
-      <c r="C84" s="2">
-        <v>46183.815613618077</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H84" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="1">
-        <v>12646</v>
-      </c>
-      <c r="C85" s="2">
-        <v>46183.815613618077</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H85" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="1">
-        <v>12647</v>
-      </c>
-      <c r="C86" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H86" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="1">
-        <v>12648</v>
-      </c>
-      <c r="C87" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H87" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="1">
-        <v>12649</v>
-      </c>
-      <c r="C88" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H88" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="1">
-        <v>12650</v>
-      </c>
-      <c r="C89" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H89" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="1">
-        <v>12651</v>
-      </c>
-      <c r="C90" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D90" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H90" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I90" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="1">
-        <v>12652</v>
-      </c>
-      <c r="C91" s="2">
-        <v>46183.815619054796</v>
-      </c>
-      <c r="D91" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H91" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="1">
-        <v>12653</v>
-      </c>
-      <c r="C92" s="2">
-        <v>46183.815619111316</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H92" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I92" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="1">
-        <v>12654</v>
-      </c>
-      <c r="C93" s="2">
-        <v>46183.815619111316</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H93" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I93" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="1">
-        <v>12655</v>
-      </c>
-      <c r="C94" s="2">
-        <v>46183.815619111316</v>
-      </c>
-      <c r="D94" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H94" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="1">
-        <v>12656</v>
-      </c>
-      <c r="C95" s="2">
-        <v>46183.815619111316</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G95" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H95" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I95" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="1">
-        <v>12657</v>
-      </c>
-      <c r="C96" s="2">
-        <v>46183.815619111316</v>
-      </c>
-      <c r="D96" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G96" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H96" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="1">
-        <v>12658</v>
-      </c>
-      <c r="C97" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D97" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H97" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I97" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="1">
-        <v>12659</v>
-      </c>
-      <c r="C98" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D98" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H98" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I98" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="1">
-        <v>12660</v>
-      </c>
-      <c r="C99" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G99" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H99" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I99" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="1">
-        <v>12661</v>
-      </c>
-      <c r="C100" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D100" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H100" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="1">
-        <v>12662</v>
-      </c>
-      <c r="C101" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D101" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="1">
-        <v>12663</v>
-      </c>
-      <c r="C102" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D102" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="1">
-        <v>12664</v>
-      </c>
-      <c r="C103" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D103" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G103" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H103" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I103" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="1">
-        <v>12665</v>
-      </c>
-      <c r="C104" s="2">
-        <v>46183.815860900933</v>
-      </c>
-      <c r="D104" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G104" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H104" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I104" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="1">
-        <v>12666</v>
-      </c>
-      <c r="C105" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D105" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G105" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H105" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I105" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="1">
-        <v>12667</v>
-      </c>
-      <c r="C106" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D106" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G106" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H106" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I106" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="1">
-        <v>12668</v>
-      </c>
-      <c r="C107" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D107" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="F107" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G107" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H107" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I107" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="1">
-        <v>12669</v>
-      </c>
-      <c r="C108" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D108" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="F108" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G108" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H108" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I108" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="1">
-        <v>12670</v>
-      </c>
-      <c r="C109" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D109" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G109" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H109" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I109" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="1">
-        <v>12671</v>
-      </c>
-      <c r="C110" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D110" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F110" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G110" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H110" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I110" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="1">
-        <v>12672</v>
-      </c>
-      <c r="C111" s="2">
-        <v>46183.815860957453</v>
-      </c>
-      <c r="D111" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="F111" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G111" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H111" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I111" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="1">
-        <v>12673</v>
-      </c>
-      <c r="C112" s="2">
-        <v>46183.815885145472</v>
-      </c>
-      <c r="D112" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F112" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G112" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H112" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I112" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="1">
-        <v>12674</v>
-      </c>
-      <c r="C113" s="2">
-        <v>46183.815885145472</v>
-      </c>
-      <c r="D113" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F113" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G113" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H113" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I113" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="1">
-        <v>12675</v>
-      </c>
-      <c r="C114" s="2">
-        <v>46183.815885145472</v>
-      </c>
-      <c r="D114" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F114" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G114" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H114" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I114" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="1">
-        <v>12676</v>
-      </c>
-      <c r="C115" s="2">
-        <v>46183.815885201984</v>
-      </c>
-      <c r="D115" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F115" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G115" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H115" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I115" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A116" s="1">
-        <v>12677</v>
-      </c>
-      <c r="C116" s="2">
-        <v>46183.815885201984</v>
-      </c>
-      <c r="D116" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F116" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G116" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H116" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I116" s="3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A117" s="1">
-        <v>12678</v>
-      </c>
-      <c r="C117" s="2">
-        <v>46183.815885201984</v>
-      </c>
-      <c r="D117" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G117" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H117" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I117" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="1">
-        <v>12679</v>
-      </c>
-      <c r="C118" s="2">
-        <v>46183.815885201984</v>
-      </c>
-      <c r="D118" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F118" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G118" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H118" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I118" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J118">
-    <sortCondition ref="A2:A118"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J80">
+    <sortCondition ref="A2:A80"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PMI-DZT2/Журнал событий.xlsx
+++ b/PMI-DZT2/Журнал событий.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d.sharygin\Desktop\pmi_devices\DZT2\PMI-DZT2\PMI-DZT2\ПМИ ТокЗ\pmi_tokzdzt\zpo_modes\Журнал событий\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282C5289-DB4B-4A73-942F-F73DAE70AE61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB6BFD5F-06AB-45EA-A15C-4C5DC6A216E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1615" uniqueCount="58">
   <si>
     <t>№</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Ед. изм.</t>
   </si>
   <si>
-    <t>Слот M3.Реле1. Статус</t>
+    <t>Слот M3.Реле2. Статус</t>
   </si>
   <si>
     <t>Хорошее [0]</t>
@@ -66,22 +66,13 @@
     <t>System</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле2. Статус</t>
-  </si>
-  <si>
     <t>1</t>
   </si>
   <si>
-    <t>Слот M3.Реле6. Статус</t>
+    <t>ЗПО / ЗПО: Ввод</t>
   </si>
   <si>
     <t>ТО ЗПО / ТО ЗПО ВН: Ввод</t>
-  </si>
-  <si>
-    <t>ТО ЗПО / ТО ЗПО ВН: Оперативный вывод</t>
   </si>
   <si>
     <t>ТО ЗПО / ТО ЗПО общ: Ввод</t>
@@ -90,52 +81,22 @@
     <t>ЛО Т / ЛО: Ввод</t>
   </si>
   <si>
-    <t>ЛО Т / ЛО: Оперативный вывод</t>
-  </si>
-  <si>
     <t>ЛО Т / ЗАПВ: Ввод</t>
   </si>
   <si>
-    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
+    <t>Наличие внешнего питания (общий)</t>
   </si>
   <si>
-    <t>ДВ: ОВ ТО ЗПО ВН</t>
+    <t>Статус светодиода "Готовность"</t>
   </si>
   <si>
-    <t>Слот M8. ДВ3. Статус</t>
+    <t>Слот M3.Реле1. Статус</t>
   </si>
   <si>
-    <t>ДВ: Вывод терминала</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-1_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ1. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле4. Статус</t>
+    <t>0</t>
   </si>
   <si>
     <t>ТО ЗПО / ТО ЗПО ВН: ИО Iмакс</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-35_Опер. вывод</t>
-  </si>
-  <si>
-    <t>Виртуальный ключ-34_Опер. вывод</t>
-  </si>
-  <si>
-    <t>ДВ: ОВ ТО ЗПО</t>
-  </si>
-  <si>
-    <t>Слот M8. ДВ2. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле3. Статус</t>
-  </si>
-  <si>
-    <t>Слот M3.Реле5. Статус</t>
   </si>
   <si>
     <t>ТО ЗПО / ТО ЗПО ВН: Пуск</t>
@@ -144,10 +105,100 @@
     <t>ТО ЗПО / ТО ЗПО общ: Пуск</t>
   </si>
   <si>
-    <t>Наличие внешнего питания (общий)</t>
+    <t>СС / СС: ТС сигн</t>
   </si>
   <si>
-    <t>Статус светодиода "Готовность"</t>
+    <t>Отказ сист.охл.</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ4. Статус</t>
+  </si>
+  <si>
+    <t>Слот M4.Реле1. Статус</t>
+  </si>
+  <si>
+    <t>ПС / ПС: Пуск</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле7. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле8. Статус</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Срабатывание</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Запрет АПВ</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле4. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле5. Статус</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле6. Статус</t>
+  </si>
+  <si>
+    <t>ЗПО / ЗПО: Пуск</t>
+  </si>
+  <si>
+    <t>ЗПО / ЗПО: Срабатывание сигн</t>
+  </si>
+  <si>
+    <t>ЗПО / ЗПО: Срабатывание</t>
+  </si>
+  <si>
+    <t>t масла ЗПО</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ5. Статус</t>
+  </si>
+  <si>
+    <t>ПС / ПС: Пуск (имп)</t>
+  </si>
+  <si>
+    <t>Слот M3.Реле3. Статус</t>
+  </si>
+  <si>
+    <t>ЗПО / ЗПО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ТО ЗПО / ТО ЗПО ВН: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЛО: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>ЛО Т / ЗАПВ: Оперативный вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-1_Опер. вывод</t>
+  </si>
+  <si>
+    <t>ДВ: Вывод терминала</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ1. Статус</t>
+  </si>
+  <si>
+    <t>ДВ: ЗПО на сигн</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ3. Статус</t>
+  </si>
+  <si>
+    <t>ДВ: ОВ ЗПО</t>
+  </si>
+  <si>
+    <t>Слот M8. ДВ2. Статус</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-32_Опер. вывод</t>
+  </si>
+  <si>
+    <t>Виртуальный ключ-33_Опер. вывод</t>
   </si>
 </sst>
 </file>
@@ -549,7 +600,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="7.140625" style="1" customWidth="1"/>
@@ -597,13 +648,13 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
-        <v>12752</v>
+        <v>15332</v>
       </c>
       <c r="C2" s="2">
-        <v>46184.552524154111</v>
+        <v>46188.504586260795</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>11</v>
@@ -615,18 +666,18 @@
         <v>12</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>12753</v>
+        <v>15333</v>
       </c>
       <c r="C3" s="2">
-        <v>46184.552524154111</v>
+        <v>46188.504586260795</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>11</v>
@@ -638,18 +689,18 @@
         <v>12</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
-        <v>12754</v>
+        <v>15334</v>
       </c>
       <c r="C4" s="2">
-        <v>46184.552533309499</v>
+        <v>46188.504586317315</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>11</v>
@@ -661,18 +712,18 @@
         <v>12</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
-        <v>12755</v>
+        <v>15335</v>
       </c>
       <c r="C5" s="2">
-        <v>46184.552533309499</v>
+        <v>46188.504586317315</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>11</v>
@@ -684,18 +735,18 @@
         <v>12</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
-        <v>12756</v>
+        <v>15336</v>
       </c>
       <c r="C6" s="2">
-        <v>46184.552533309499</v>
+        <v>46188.504586317315</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>11</v>
@@ -707,18 +758,18 @@
         <v>12</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>12757</v>
+        <v>15337</v>
       </c>
       <c r="C7" s="2">
-        <v>46184.552533309499</v>
+        <v>46188.504586317315</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>11</v>
@@ -730,18 +781,18 @@
         <v>12</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
-        <v>12758</v>
+        <v>15338</v>
       </c>
       <c r="C8" s="2">
-        <v>46184.552533366019</v>
+        <v>46188.504595065649</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>11</v>
@@ -753,18 +804,18 @@
         <v>12</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
-        <v>12759</v>
+        <v>15339</v>
       </c>
       <c r="C9" s="2">
-        <v>46184.552533366019</v>
+        <v>46188.504595065649</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>11</v>
@@ -776,18 +827,18 @@
         <v>12</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
-        <v>12760</v>
+        <v>15340</v>
       </c>
       <c r="C10" s="2">
-        <v>46184.554472837168</v>
+        <v>46188.504595065649</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>11</v>
@@ -799,18 +850,18 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>12761</v>
+        <v>15341</v>
       </c>
       <c r="C11" s="2">
-        <v>46184.554472837168</v>
+        <v>46188.504595065649</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>11</v>
@@ -822,18 +873,18 @@
         <v>12</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
-        <v>12762</v>
+        <v>15342</v>
       </c>
       <c r="C12" s="2">
-        <v>46184.554472837168</v>
+        <v>46188.504595065649</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>11</v>
@@ -845,18 +896,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
-        <v>12763</v>
+        <v>15343</v>
       </c>
       <c r="C13" s="2">
-        <v>46184.554472893673</v>
+        <v>46188.504595122169</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>11</v>
@@ -868,18 +919,18 @@
         <v>12</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
-        <v>12764</v>
+        <v>15344</v>
       </c>
       <c r="C14" s="2">
-        <v>46184.554472893673</v>
+        <v>46188.504595122169</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>11</v>
@@ -891,18 +942,18 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>12765</v>
+        <v>15345</v>
       </c>
       <c r="C15" s="2">
-        <v>46184.554472893673</v>
+        <v>46188.504595122169</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>11</v>
@@ -914,18 +965,18 @@
         <v>12</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
-        <v>12766</v>
+        <v>15346</v>
       </c>
       <c r="C16" s="2">
-        <v>46184.554675202686</v>
+        <v>46188.504595189981</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>11</v>
@@ -937,18 +988,18 @@
         <v>12</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
-        <v>12767</v>
+        <v>15347</v>
       </c>
       <c r="C17" s="2">
-        <v>46184.554675202686</v>
+        <v>46188.504606696239</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -960,18 +1011,18 @@
         <v>12</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <v>12768</v>
+        <v>15348</v>
       </c>
       <c r="C18" s="2">
-        <v>46184.554675202686</v>
+        <v>46188.504606696239</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -983,18 +1034,18 @@
         <v>12</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>12769</v>
+        <v>15349</v>
       </c>
       <c r="C19" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>11</v>
@@ -1011,13 +1062,13 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <v>12770</v>
+        <v>15350</v>
       </c>
       <c r="C20" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>11</v>
@@ -1029,18 +1080,18 @@
         <v>12</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <v>12771</v>
+        <v>15351</v>
       </c>
       <c r="C21" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>11</v>
@@ -1057,13 +1108,13 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <v>12772</v>
+        <v>15352</v>
       </c>
       <c r="C22" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>11</v>
@@ -1080,13 +1131,13 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>12773</v>
+        <v>15353</v>
       </c>
       <c r="C23" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>11</v>
@@ -1103,13 +1154,13 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <v>12774</v>
+        <v>15354</v>
       </c>
       <c r="C24" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606752751</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>11</v>
@@ -1126,13 +1177,13 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <v>12775</v>
+        <v>15355</v>
       </c>
       <c r="C25" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606820577</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>11</v>
@@ -1144,18 +1195,18 @@
         <v>12</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <v>12776</v>
+        <v>15356</v>
       </c>
       <c r="C26" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606820577</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>11</v>
@@ -1172,13 +1223,13 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <v>12777</v>
+        <v>15357</v>
       </c>
       <c r="C27" s="2">
-        <v>46184.554675259205</v>
+        <v>46188.504606820577</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>11</v>
@@ -1190,18 +1241,18 @@
         <v>12</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <v>12778</v>
+        <v>15358</v>
       </c>
       <c r="C28" s="2">
-        <v>46184.55467531571</v>
+        <v>46188.504606877083</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>11</v>
@@ -1213,18 +1264,18 @@
         <v>12</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <v>12779</v>
+        <v>15359</v>
       </c>
       <c r="C29" s="2">
-        <v>46184.55467531571</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>11</v>
@@ -1236,18 +1287,18 @@
         <v>12</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <v>12780</v>
+        <v>15360</v>
       </c>
       <c r="C30" s="2">
-        <v>46184.55467531571</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>11</v>
@@ -1264,13 +1315,13 @@
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <v>12781</v>
+        <v>15361</v>
       </c>
       <c r="C31" s="2">
-        <v>46184.55467531571</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>11</v>
@@ -1287,13 +1338,13 @@
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>12782</v>
+        <v>15362</v>
       </c>
       <c r="C32" s="2">
-        <v>46184.55467531571</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>11</v>
@@ -1310,13 +1361,13 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
-        <v>12783</v>
+        <v>15363</v>
       </c>
       <c r="C33" s="2">
-        <v>46184.554747890928</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>11</v>
@@ -1333,13 +1384,13 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
-        <v>12784</v>
+        <v>15364</v>
       </c>
       <c r="C34" s="2">
-        <v>46184.554747890928</v>
+        <v>46188.505082725256</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>11</v>
@@ -1356,13 +1407,13 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
-        <v>12785</v>
+        <v>15365</v>
       </c>
       <c r="C35" s="2">
-        <v>46184.554748173498</v>
+        <v>46188.505091530256</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>11</v>
@@ -1374,18 +1425,18 @@
         <v>12</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
-        <v>12786</v>
+        <v>15366</v>
       </c>
       <c r="C36" s="2">
-        <v>46184.554748173498</v>
+        <v>46188.505091530256</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>11</v>
@@ -1397,18 +1448,18 @@
         <v>12</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
-        <v>12787</v>
+        <v>15367</v>
       </c>
       <c r="C37" s="2">
-        <v>46184.554748173498</v>
+        <v>46188.505091530256</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>11</v>
@@ -1420,18 +1471,18 @@
         <v>12</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
-        <v>12788</v>
+        <v>15368</v>
       </c>
       <c r="C38" s="2">
-        <v>46184.554753678036</v>
+        <v>46188.505091530256</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>11</v>
@@ -1448,13 +1499,13 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
-        <v>12789</v>
+        <v>15369</v>
       </c>
       <c r="C39" s="2">
-        <v>46184.554753734556</v>
+        <v>46188.505091530256</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>11</v>
@@ -1466,18 +1517,18 @@
         <v>12</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
-        <v>12790</v>
+        <v>15370</v>
       </c>
       <c r="C40" s="2">
-        <v>46184.554753734556</v>
+        <v>46188.505091586776</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>11</v>
@@ -1494,13 +1545,13 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
-        <v>12791</v>
+        <v>15371</v>
       </c>
       <c r="C41" s="2">
-        <v>46184.554753734556</v>
+        <v>46188.505091586776</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>11</v>
@@ -1512,18 +1563,18 @@
         <v>12</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
-        <v>12792</v>
+        <v>15372</v>
       </c>
       <c r="C42" s="2">
-        <v>46184.554753734556</v>
+        <v>46188.505091586776</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>11</v>
@@ -1540,13 +1591,13 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
-        <v>12793</v>
+        <v>15373</v>
       </c>
       <c r="C43" s="2">
-        <v>46184.554820115896</v>
+        <v>46188.505091643296</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>11</v>
@@ -1563,13 +1614,13 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
-        <v>12794</v>
+        <v>15374</v>
       </c>
       <c r="C44" s="2">
-        <v>46184.554820115896</v>
+        <v>46188.505103160853</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>11</v>
@@ -1586,13 +1637,13 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
-        <v>12795</v>
+        <v>15375</v>
       </c>
       <c r="C45" s="2">
-        <v>46184.554820398473</v>
+        <v>46188.505103160853</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>11</v>
@@ -1604,18 +1655,18 @@
         <v>12</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
-        <v>12796</v>
+        <v>15376</v>
       </c>
       <c r="C46" s="2">
-        <v>46184.554820398473</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>11</v>
@@ -1627,18 +1678,18 @@
         <v>12</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
-        <v>12797</v>
+        <v>15377</v>
       </c>
       <c r="C47" s="2">
-        <v>46184.554820398473</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>11</v>
@@ -1650,18 +1701,18 @@
         <v>12</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
-        <v>12798</v>
+        <v>15378</v>
       </c>
       <c r="C48" s="2">
-        <v>46184.554825903011</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>11</v>
@@ -1678,13 +1729,13 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
-        <v>12799</v>
+        <v>15379</v>
       </c>
       <c r="C49" s="2">
-        <v>46184.55498011841</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>11</v>
@@ -1701,13 +1752,13 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
-        <v>12800</v>
+        <v>15380</v>
       </c>
       <c r="C50" s="2">
-        <v>46184.55498011841</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>11</v>
@@ -1724,13 +1775,13 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
-        <v>12801</v>
+        <v>15381</v>
       </c>
       <c r="C51" s="2">
-        <v>46184.55498011841</v>
+        <v>46188.505103217372</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>11</v>
@@ -1747,13 +1798,13 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
-        <v>12802</v>
+        <v>15382</v>
       </c>
       <c r="C52" s="2">
-        <v>46184.554980174915</v>
+        <v>46188.505103273877</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>11</v>
@@ -1770,13 +1821,13 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
-        <v>12803</v>
+        <v>15383</v>
       </c>
       <c r="C53" s="2">
-        <v>46184.554980174915</v>
+        <v>46188.505103273877</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>11</v>
@@ -1793,13 +1844,13 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
-        <v>12804</v>
+        <v>15384</v>
       </c>
       <c r="C54" s="2">
-        <v>46184.555002690104</v>
+        <v>46188.505103273877</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>11</v>
@@ -1811,18 +1862,18 @@
         <v>12</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
-        <v>12805</v>
+        <v>15385</v>
       </c>
       <c r="C55" s="2">
-        <v>46184.555002690104</v>
+        <v>46188.505103330397</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>11</v>
@@ -1834,18 +1885,18 @@
         <v>12</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
-        <v>12806</v>
+        <v>15386</v>
       </c>
       <c r="C56" s="2">
-        <v>46184.555002690104</v>
+        <v>46188.505540771592</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>11</v>
@@ -1857,18 +1908,18 @@
         <v>12</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
-        <v>12807</v>
+        <v>15387</v>
       </c>
       <c r="C57" s="2">
-        <v>46184.555002746623</v>
+        <v>46188.505540771592</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>11</v>
@@ -1880,18 +1931,18 @@
         <v>12</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
-        <v>12808</v>
+        <v>15388</v>
       </c>
       <c r="C58" s="2">
-        <v>46184.555002746623</v>
+        <v>46188.505540828111</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>11</v>
@@ -1903,18 +1954,18 @@
         <v>12</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
-        <v>12809</v>
+        <v>15389</v>
       </c>
       <c r="C59" s="2">
-        <v>46184.555002746623</v>
+        <v>46188.505540828111</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>11</v>
@@ -1926,18 +1977,18 @@
         <v>12</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
-        <v>12810</v>
+        <v>15390</v>
       </c>
       <c r="C60" s="2">
-        <v>46184.555002746623</v>
+        <v>46188.505540828111</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>11</v>
@@ -1949,18 +2000,18 @@
         <v>12</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
-        <v>12811</v>
+        <v>15391</v>
       </c>
       <c r="C61" s="2">
-        <v>46184.555003040492</v>
+        <v>46188.505540828111</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>11</v>
@@ -1972,18 +2023,18 @@
         <v>12</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
-        <v>12812</v>
+        <v>15392</v>
       </c>
       <c r="C62" s="2">
-        <v>46184.555003040492</v>
+        <v>46188.505540895923</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>11</v>
@@ -1995,18 +2046,18 @@
         <v>12</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
-        <v>12813</v>
+        <v>15393</v>
       </c>
       <c r="C63" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540895923</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>11</v>
@@ -2018,18 +2069,18 @@
         <v>12</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="1">
-        <v>12814</v>
+        <v>15394</v>
       </c>
       <c r="C64" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540895923</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>11</v>
@@ -2041,18 +2092,18 @@
         <v>12</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
-        <v>12815</v>
+        <v>15395</v>
       </c>
       <c r="C65" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540895923</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>11</v>
@@ -2064,18 +2115,18 @@
         <v>12</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="1">
-        <v>12816</v>
+        <v>15396</v>
       </c>
       <c r="C66" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540895923</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>11</v>
@@ -2087,18 +2138,18 @@
         <v>12</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="1">
-        <v>12817</v>
+        <v>15397</v>
       </c>
       <c r="C67" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540952436</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>11</v>
@@ -2110,18 +2161,18 @@
         <v>12</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="1">
-        <v>12818</v>
+        <v>15398</v>
       </c>
       <c r="C68" s="2">
-        <v>46184.555157843788</v>
+        <v>46188.505540952436</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>11</v>
@@ -2133,18 +2184,18 @@
         <v>12</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="1">
-        <v>12819</v>
+        <v>15399</v>
       </c>
       <c r="C69" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505540952436</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>11</v>
@@ -2156,18 +2207,18 @@
         <v>12</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="1">
-        <v>12820</v>
+        <v>15400</v>
       </c>
       <c r="C70" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505541008955</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>11</v>
@@ -2179,18 +2230,18 @@
         <v>12</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
-        <v>12821</v>
+        <v>15401</v>
       </c>
       <c r="C71" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505550209411</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>11</v>
@@ -2202,18 +2253,18 @@
         <v>12</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
-        <v>12822</v>
+        <v>15402</v>
       </c>
       <c r="C72" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505550209411</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>11</v>
@@ -2225,18 +2276,18 @@
         <v>12</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
-        <v>12823</v>
+        <v>15403</v>
       </c>
       <c r="C73" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505647255362</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>11</v>
@@ -2248,18 +2299,18 @@
         <v>12</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="1">
-        <v>12824</v>
+        <v>15404</v>
       </c>
       <c r="C74" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505647255362</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>11</v>
@@ -2276,13 +2327,13 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="1">
-        <v>12825</v>
+        <v>15405</v>
       </c>
       <c r="C75" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505647311882</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>11</v>
@@ -2294,18 +2345,18 @@
         <v>12</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="1">
-        <v>12826</v>
+        <v>15406</v>
       </c>
       <c r="C76" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505647311882</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>11</v>
@@ -2317,18 +2368,18 @@
         <v>12</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="1">
-        <v>12827</v>
+        <v>15407</v>
       </c>
       <c r="C77" s="2">
-        <v>46184.555157900308</v>
+        <v>46188.505647368387</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>11</v>
@@ -2340,18 +2391,18 @@
         <v>12</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="1">
-        <v>12828</v>
+        <v>15408</v>
       </c>
       <c r="C78" s="2">
-        <v>46184.555157956813</v>
+        <v>46188.505658885952</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>11</v>
@@ -2368,13 +2419,13 @@
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="1">
-        <v>12829</v>
+        <v>15409</v>
       </c>
       <c r="C79" s="2">
-        <v>46184.555157956813</v>
+        <v>46188.505658885952</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>11</v>
@@ -2386,35 +2437,5601 @@
         <v>12</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
-        <v>12830</v>
+        <v>15410</v>
       </c>
       <c r="C80" s="2">
-        <v>46184.555157956813</v>
+        <v>46188.505658942464</v>
       </c>
       <c r="D80" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="1">
+        <v>15411</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46188.505658942464</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="1">
+        <v>15412</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46188.505658942464</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="1">
+        <v>15413</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46188.505658942464</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="1">
+        <v>15414</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46188.505658942464</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="1">
+        <v>15415</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46188.505658942464</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="1">
+        <v>15416</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46188.50565901029</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="1">
+        <v>15417</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46188.50565901029</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="1">
+        <v>15418</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46188.50565901029</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H88" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="1">
+        <v>15419</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46188.505659066795</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H89" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I89" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="1">
+        <v>15420</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46188.505720056637</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G90" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H90" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I90" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="1">
+        <v>15421</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46188.505720056637</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="1">
+        <v>15422</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46188.505720056637</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H92" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I92" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="1">
+        <v>15423</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46188.505720056637</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I93" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="1">
+        <v>15424</v>
+      </c>
+      <c r="C94" s="2">
+        <v>46188.505720113149</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H94" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I94" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="1">
+        <v>15425</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46188.505720113149</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H95" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I95" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="1">
+        <v>15426</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46188.505720113149</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A97" s="1">
+        <v>15427</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46188.505720169669</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I97" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A98" s="1">
+        <v>15428</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46188.505720169669</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I98" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A99" s="1">
+        <v>15429</v>
+      </c>
+      <c r="C99" s="2">
+        <v>46188.505792858057</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G99" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H99" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I99" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A100" s="1">
+        <v>15430</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46188.505792858057</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I100" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A101" s="1">
+        <v>15431</v>
+      </c>
+      <c r="C101" s="2">
+        <v>46188.505792858057</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A102" s="1">
+        <v>15432</v>
+      </c>
+      <c r="C102" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G102" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H102" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I102" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A103" s="1">
+        <v>15433</v>
+      </c>
+      <c r="C103" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G103" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H103" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I103" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A104" s="1">
+        <v>15434</v>
+      </c>
+      <c r="C104" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G104" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H104" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I104" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A105" s="1">
+        <v>15435</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G105" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H105" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I105" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A106" s="1">
+        <v>15436</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G106" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H106" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I106" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A107" s="1">
+        <v>15437</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G107" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H107" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I107" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A108" s="1">
+        <v>15438</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="H80" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I80" s="3" t="s">
+      <c r="F108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G108" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H108" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I108" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A109" s="1">
+        <v>15439</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G109" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H109" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I109" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A110" s="1">
+        <v>15440</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G110" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H110" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I110" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
+        <v>15441</v>
+      </c>
+      <c r="C111" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D111" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G111" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H111" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I111" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A112" s="1">
+        <v>15442</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D112" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G112" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H112" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I112" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A113" s="1">
+        <v>15443</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D113" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G113" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H113" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I113" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="1">
+        <v>15444</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46188.505792914577</v>
+      </c>
+      <c r="D114" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H114" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I114" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A115" s="1">
+        <v>15445</v>
+      </c>
+      <c r="C115" s="2">
+        <v>46188.505792971082</v>
+      </c>
+      <c r="D115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I115" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A116" s="1">
+        <v>15446</v>
+      </c>
+      <c r="C116" s="2">
+        <v>46188.505792971082</v>
+      </c>
+      <c r="D116" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H116" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I116" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A117" s="1">
+        <v>15447</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46188.505792971082</v>
+      </c>
+      <c r="D117" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G117" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H117" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I117" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A118" s="1">
+        <v>15448</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46188.505792971082</v>
+      </c>
+      <c r="D118" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G118" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H118" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I118" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A119" s="1">
+        <v>15449</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46188.505792971082</v>
+      </c>
+      <c r="D119" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G119" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H119" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I119" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A120" s="1">
+        <v>15450</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46188.505865196057</v>
+      </c>
+      <c r="D120" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G120" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H120" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I120" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A121" s="1">
+        <v>15451</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46188.505865196057</v>
+      </c>
+      <c r="D121" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G121" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H121" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I121" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A122" s="1">
+        <v>15452</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46188.505865433413</v>
+      </c>
+      <c r="D122" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G122" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H122" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I122" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A123" s="1">
+        <v>15453</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46188.505865433413</v>
+      </c>
+      <c r="D123" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G123" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H123" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I123" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="1">
+        <v>15454</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46188.505865433413</v>
+      </c>
+      <c r="D124" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I124" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="1">
+        <v>15455</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46188.505870983019</v>
+      </c>
+      <c r="D125" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G125" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H125" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I125" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A126" s="1">
+        <v>15456</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D126" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G126" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H126" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I126" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="1">
+        <v>15457</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D127" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G127" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H127" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I127" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A128" s="1">
+        <v>15458</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D128" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G128" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H128" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I128" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="129" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A129" s="1">
+        <v>15459</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D129" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G129" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H129" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I129" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="130" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A130" s="1">
+        <v>15460</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D130" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G130" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H130" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I130" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="131" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A131" s="1">
+        <v>15461</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D131" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G131" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H131" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I131" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="132" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A132" s="1">
+        <v>15462</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D132" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G132" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H132" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I132" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="133" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A133" s="1">
+        <v>15463</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46188.505871039539</v>
+      </c>
+      <c r="D133" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F133" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G133" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H133" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I133" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A134" s="1">
+        <v>15464</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46188.506014449602</v>
+      </c>
+      <c r="D134" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G134" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H134" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I134" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="135" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A135" s="1">
+        <v>15465</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46188.506014449602</v>
+      </c>
+      <c r="D135" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F135" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G135" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H135" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I135" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A136" s="1">
+        <v>15466</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46188.506014449602</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A137" s="1">
+        <v>15467</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46188.506014506122</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="138" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A138" s="1">
+        <v>15468</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46188.506202923942</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A139" s="1">
+        <v>15469</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46188.506202923942</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F139" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="140" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A140" s="1">
+        <v>15470</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A141" s="1">
+        <v>15471</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A142" s="1">
+        <v>15472</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A143" s="1">
+        <v>15473</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A144" s="1">
+        <v>15474</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A145" s="1">
+        <v>15475</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46188.506203093493</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A146" s="1">
+        <v>15476</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46188.506212022679</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A147" s="1">
+        <v>15477</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46188.506212022679</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G147" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H147" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I147" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A148" s="1">
+        <v>15478</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46188.506212022679</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G148" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H148" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I148" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A149" s="1">
+        <v>15479</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46188.506212022679</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G149" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H149" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I149" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A150" s="1">
+        <v>15480</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46188.506212079192</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G150" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H150" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I150" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A151" s="1">
+        <v>15481</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46188.506229801926</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G151" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H151" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I151" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A152" s="1">
+        <v>15482</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46188.506229801926</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G152" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H152" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I152" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="153" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A153" s="1">
+        <v>15483</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46188.506230027982</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G153" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H153" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I153" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A154" s="1">
+        <v>15484</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46188.506230027982</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G154" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H154" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I154" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A155" s="1">
+        <v>15485</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46188.506230027982</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G155" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H155" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I155" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A156" s="1">
+        <v>15486</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G156" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H156" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I156" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A157" s="1">
+        <v>15487</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G157" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H157" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I157" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A158" s="1">
+        <v>15488</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G158" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H158" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I158" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A159" s="1">
+        <v>15489</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G159" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H159" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I159" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A160" s="1">
+        <v>15490</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G160" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H160" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I160" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A161" s="1">
+        <v>15491</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G161" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H161" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I161" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A162" s="1">
+        <v>15492</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G162" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H162" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I162" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A163" s="1">
+        <v>15493</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46188.506230095794</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G163" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H163" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I163" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A164" s="1">
+        <v>15494</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46188.506230321858</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G164" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H164" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I164" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A165" s="1">
+        <v>15495</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46188.506230321858</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G165" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H165" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I165" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A166" s="1">
+        <v>15496</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46188.506230378371</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G166" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H166" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I166" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A167" s="1">
+        <v>15497</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46188.506230378371</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G167" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H167" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I167" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A168" s="1">
+        <v>15498</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D168" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G168" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H168" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I168" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A169" s="1">
+        <v>15499</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D169" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G169" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H169" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I169" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A170" s="1">
+        <v>15500</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G170" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H170" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I170" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A171" s="1">
+        <v>15501</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D171" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G171" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H171" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I171" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A172" s="1">
+        <v>15502</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D172" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G172" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H172" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I172" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A173" s="1">
+        <v>15503</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D173" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G173" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H173" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I173" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A174" s="1">
+        <v>15504</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D174" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G174" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H174" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I174" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A175" s="1">
+        <v>15505</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46188.506392370196</v>
+      </c>
+      <c r="D175" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G175" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H175" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I175" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A176" s="1">
+        <v>15506</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D176" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G176" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H176" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I176" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A177" s="1">
+        <v>15507</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D177" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G177" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H177" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I177" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A178" s="1">
+        <v>15508</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G178" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H178" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I178" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A179" s="1">
+        <v>15509</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D179" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G179" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H179" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I179" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A180" s="1">
+        <v>15510</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D180" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G180" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H180" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I180" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A181" s="1">
+        <v>15511</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D181" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G181" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H181" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I181" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A182" s="1">
+        <v>15512</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D182" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G182" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H182" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I182" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A183" s="1">
+        <v>15513</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D183" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G183" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H183" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I183" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A184" s="1">
+        <v>15514</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D184" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G184" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H184" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I184" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A185" s="1">
+        <v>15515</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46188.506392426716</v>
+      </c>
+      <c r="D185" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H185" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I185" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A186" s="1">
+        <v>15516</v>
+      </c>
+      <c r="C186" s="2">
+        <v>46188.506392483221</v>
+      </c>
+      <c r="D186" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G186" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H186" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I186" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A187" s="1">
+        <v>15517</v>
+      </c>
+      <c r="C187" s="2">
+        <v>46188.506392483221</v>
+      </c>
+      <c r="D187" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G187" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H187" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I187" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A188" s="1">
+        <v>15518</v>
+      </c>
+      <c r="C188" s="2">
+        <v>46188.506571248479</v>
+      </c>
+      <c r="D188" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G188" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H188" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I188" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A189" s="1">
+        <v>15519</v>
+      </c>
+      <c r="C189" s="2">
+        <v>46188.506571463244</v>
+      </c>
+      <c r="D189" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G189" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H189" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I189" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A190" s="1">
+        <v>15520</v>
+      </c>
+      <c r="C190" s="2">
+        <v>46188.50657175712</v>
+      </c>
+      <c r="D190" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G190" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H190" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I190" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A191" s="1">
+        <v>15521</v>
+      </c>
+      <c r="C191" s="2">
+        <v>46188.50657175712</v>
+      </c>
+      <c r="D191" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G191" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H191" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I191" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A192" s="1">
+        <v>15522</v>
+      </c>
+      <c r="C192" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D192" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G192" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H192" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I192" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A193" s="1">
+        <v>15523</v>
+      </c>
+      <c r="C193" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D193" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G193" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H193" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I193" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A194" s="1">
+        <v>15524</v>
+      </c>
+      <c r="C194" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D194" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G194" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H194" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I194" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A195" s="1">
+        <v>15525</v>
+      </c>
+      <c r="C195" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D195" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G195" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H195" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I195" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A196" s="1">
+        <v>15526</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D196" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G196" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H196" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I196" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A197" s="1">
+        <v>15527</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46188.506580155066</v>
+      </c>
+      <c r="D197" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G197" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H197" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I197" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A198" s="1">
+        <v>15528</v>
+      </c>
+      <c r="C198" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D198" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G198" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H198" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I198" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A199" s="1">
+        <v>15529</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D199" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G199" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H199" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I199" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A200" s="1">
+        <v>15530</v>
+      </c>
+      <c r="C200" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D200" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G200" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H200" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I200" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A201" s="1">
+        <v>15531</v>
+      </c>
+      <c r="C201" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D201" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G201" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H201" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I201" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A202" s="1">
+        <v>15532</v>
+      </c>
+      <c r="C202" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D202" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G202" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H202" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I202" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A203" s="1">
+        <v>15533</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D203" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G203" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H203" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I203" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A204" s="1">
+        <v>15534</v>
+      </c>
+      <c r="C204" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D204" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G204" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H204" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I204" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A205" s="1">
+        <v>15535</v>
+      </c>
+      <c r="C205" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D205" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G205" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H205" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I205" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A206" s="1">
+        <v>15536</v>
+      </c>
+      <c r="C206" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D206" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G206" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H206" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I206" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A207" s="1">
+        <v>15537</v>
+      </c>
+      <c r="C207" s="2">
+        <v>46188.506580211571</v>
+      </c>
+      <c r="D207" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G207" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H207" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I207" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A208" s="1">
+        <v>15538</v>
+      </c>
+      <c r="C208" s="2">
+        <v>46188.506580279398</v>
+      </c>
+      <c r="D208" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G208" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H208" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I208" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A209" s="1">
+        <v>15539</v>
+      </c>
+      <c r="C209" s="2">
+        <v>46188.506580279398</v>
+      </c>
+      <c r="D209" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G209" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H209" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I209" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A210" s="1">
+        <v>15540</v>
+      </c>
+      <c r="C210" s="2">
+        <v>46188.506616211038</v>
+      </c>
+      <c r="D210" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G210" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H210" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I210" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A211" s="1">
+        <v>15541</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46188.506616211038</v>
+      </c>
+      <c r="D211" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G211" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H211" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I211" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A212" s="1">
+        <v>15542</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46188.506621998</v>
+      </c>
+      <c r="D212" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G212" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H212" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I212" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A213" s="1">
+        <v>15543</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D213" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G213" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H213" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I213" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A214" s="1">
+        <v>15544</v>
+      </c>
+      <c r="C214" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D214" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G214" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H214" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I214" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A215" s="1">
+        <v>15545</v>
+      </c>
+      <c r="C215" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D215" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G215" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H215" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I215" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A216" s="1">
+        <v>15546</v>
+      </c>
+      <c r="C216" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D216" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G216" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H216" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I216" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A217" s="1">
+        <v>15547</v>
+      </c>
+      <c r="C217" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D217" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G217" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H217" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I217" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A218" s="1">
+        <v>15548</v>
+      </c>
+      <c r="C218" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D218" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G218" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H218" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I218" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A219" s="1">
+        <v>15549</v>
+      </c>
+      <c r="C219" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D219" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G219" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H219" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I219" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A220" s="1">
+        <v>15550</v>
+      </c>
+      <c r="C220" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D220" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G220" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H220" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I220" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A221" s="1">
+        <v>15551</v>
+      </c>
+      <c r="C221" s="2">
+        <v>46188.506622054512</v>
+      </c>
+      <c r="D221" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G221" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H221" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I221" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A222" s="1">
+        <v>15552</v>
+      </c>
+      <c r="C222" s="2">
+        <v>46188.506622111025</v>
+      </c>
+      <c r="D222" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G222" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H222" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I222" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A223" s="1">
+        <v>15553</v>
+      </c>
+      <c r="C223" s="2">
+        <v>46188.506622111025</v>
+      </c>
+      <c r="D223" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G223" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H223" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I223" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A224" s="1">
+        <v>15554</v>
+      </c>
+      <c r="C224" s="2">
+        <v>46188.506629525757</v>
+      </c>
+      <c r="D224" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G224" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H224" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I224" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A225" s="1">
+        <v>15555</v>
+      </c>
+      <c r="C225" s="2">
+        <v>46188.506629525757</v>
+      </c>
+      <c r="D225" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G225" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H225" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I225" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A226" s="1">
+        <v>15556</v>
+      </c>
+      <c r="C226" s="2">
+        <v>46188.506629525757</v>
+      </c>
+      <c r="D226" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G226" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H226" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I226" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A227" s="1">
+        <v>15557</v>
+      </c>
+      <c r="C227" s="2">
+        <v>46188.506629582276</v>
+      </c>
+      <c r="D227" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G227" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H227" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I227" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A228" s="1">
+        <v>15558</v>
+      </c>
+      <c r="C228" s="2">
+        <v>46188.506688605543</v>
+      </c>
+      <c r="D228" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G228" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H228" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I228" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A229" s="1">
+        <v>15559</v>
+      </c>
+      <c r="C229" s="2">
+        <v>46188.506688605543</v>
+      </c>
+      <c r="D229" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G229" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H229" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I229" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A230" s="1">
+        <v>15560</v>
+      </c>
+      <c r="C230" s="2">
+        <v>46188.506688662063</v>
+      </c>
+      <c r="D230" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G230" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H230" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I230" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A231" s="1">
+        <v>15561</v>
+      </c>
+      <c r="C231" s="2">
+        <v>46188.506688662063</v>
+      </c>
+      <c r="D231" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G231" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H231" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I231" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A232" s="1">
+        <v>15562</v>
+      </c>
+      <c r="C232" s="2">
+        <v>46188.506688718575</v>
+      </c>
+      <c r="D232" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G232" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H232" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I232" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A233" s="1">
+        <v>15563</v>
+      </c>
+      <c r="C233" s="2">
+        <v>46188.506700236139</v>
+      </c>
+      <c r="D233" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G233" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H233" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I233" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A234" s="1">
+        <v>15564</v>
+      </c>
+      <c r="C234" s="2">
+        <v>46188.506700236139</v>
+      </c>
+      <c r="D234" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G234" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H234" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I234" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A235" s="1">
+        <v>15565</v>
+      </c>
+      <c r="C235" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D235" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G235" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H235" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I235" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A236" s="1">
+        <v>15566</v>
+      </c>
+      <c r="C236" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D236" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G236" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H236" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I236" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A237" s="1">
+        <v>15567</v>
+      </c>
+      <c r="C237" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D237" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G237" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H237" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I237" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A238" s="1">
+        <v>15568</v>
+      </c>
+      <c r="C238" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D238" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G238" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H238" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I238" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A239" s="1">
+        <v>15569</v>
+      </c>
+      <c r="C239" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D239" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G239" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H239" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I239" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A240" s="1">
+        <v>15570</v>
+      </c>
+      <c r="C240" s="2">
+        <v>46188.506700292652</v>
+      </c>
+      <c r="D240" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G240" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H240" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I240" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A241" s="1">
+        <v>15571</v>
+      </c>
+      <c r="C241" s="2">
+        <v>46188.506700349164</v>
+      </c>
+      <c r="D241" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G241" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H241" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I241" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A242" s="1">
+        <v>15572</v>
+      </c>
+      <c r="C242" s="2">
+        <v>46188.506700349164</v>
+      </c>
+      <c r="D242" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G242" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H242" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I242" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A243" s="1">
+        <v>15573</v>
+      </c>
+      <c r="C243" s="2">
+        <v>46188.506700349164</v>
+      </c>
+      <c r="D243" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G243" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H243" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I243" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A244" s="1">
+        <v>15574</v>
+      </c>
+      <c r="C244" s="2">
+        <v>46188.506700416983</v>
+      </c>
+      <c r="D244" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G244" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H244" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I244" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A245" s="1">
+        <v>15575</v>
+      </c>
+      <c r="C245" s="2">
+        <v>46188.506761180761</v>
+      </c>
+      <c r="D245" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G245" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H245" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I245" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A246" s="1">
+        <v>15576</v>
+      </c>
+      <c r="C246" s="2">
+        <v>46188.506761180761</v>
+      </c>
+      <c r="D246" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G246" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H246" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I246" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A247" s="1">
+        <v>15577</v>
+      </c>
+      <c r="C247" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D247" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G247" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H247" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I247" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A248" s="1">
+        <v>15578</v>
+      </c>
+      <c r="C248" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D248" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G248" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H248" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I248" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A249" s="1">
+        <v>15579</v>
+      </c>
+      <c r="C249" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D249" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G249" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H249" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I249" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A250" s="1">
+        <v>15580</v>
+      </c>
+      <c r="C250" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D250" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G250" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H250" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I250" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A251" s="1">
+        <v>15581</v>
+      </c>
+      <c r="C251" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D251" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G251" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H251" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I251" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A252" s="1">
+        <v>15582</v>
+      </c>
+      <c r="C252" s="2">
+        <v>46188.506774653732</v>
+      </c>
+      <c r="D252" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G252" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H252" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I252" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A253" s="1">
+        <v>15583</v>
+      </c>
+      <c r="C253" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D253" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G253" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H253" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I253" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A254" s="1">
+        <v>15584</v>
+      </c>
+      <c r="C254" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D254" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G254" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H254" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I254" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A255" s="1">
+        <v>15585</v>
+      </c>
+      <c r="C255" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D255" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G255" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H255" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I255" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A256" s="1">
+        <v>15586</v>
+      </c>
+      <c r="C256" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D256" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G256" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H256" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I256" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A257" s="1">
+        <v>15587</v>
+      </c>
+      <c r="C257" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D257" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G257" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H257" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I257" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A258" s="1">
+        <v>15588</v>
+      </c>
+      <c r="C258" s="2">
+        <v>46188.506774721543</v>
+      </c>
+      <c r="D258" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G258" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H258" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I258" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A259" s="1">
+        <v>15589</v>
+      </c>
+      <c r="C259" s="2">
+        <v>46188.506774778063</v>
+      </c>
+      <c r="D259" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G259" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H259" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I259" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A260" s="1">
+        <v>15590</v>
+      </c>
+      <c r="C260" s="2">
+        <v>46188.506774778063</v>
+      </c>
+      <c r="D260" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G260" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H260" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I260" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A261" s="1">
+        <v>15591</v>
+      </c>
+      <c r="C261" s="2">
+        <v>46188.506774778063</v>
+      </c>
+      <c r="D261" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G261" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H261" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I261" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A262" s="1">
+        <v>15592</v>
+      </c>
+      <c r="C262" s="2">
+        <v>46188.506774834575</v>
+      </c>
+      <c r="D262" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G262" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H262" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I262" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A263" s="1">
+        <v>15593</v>
+      </c>
+      <c r="C263" s="2">
+        <v>46188.507071160355</v>
+      </c>
+      <c r="D263" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G263" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H263" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I263" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A264" s="1">
+        <v>15594</v>
+      </c>
+      <c r="C264" s="2">
+        <v>46188.507071386404</v>
+      </c>
+      <c r="D264" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G264" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H264" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I264" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A265" s="1">
+        <v>15595</v>
+      </c>
+      <c r="C265" s="2">
+        <v>46188.507071668981</v>
+      </c>
+      <c r="D265" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G265" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H265" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I265" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A266" s="1">
+        <v>15596</v>
+      </c>
+      <c r="C266" s="2">
+        <v>46188.507071668981</v>
+      </c>
+      <c r="D266" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G266" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H266" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I266" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A267" s="1">
+        <v>15597</v>
+      </c>
+      <c r="C267" s="2">
+        <v>46188.507071668981</v>
+      </c>
+      <c r="D267" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G267" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H267" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I267" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A268" s="1">
+        <v>15598</v>
+      </c>
+      <c r="C268" s="2">
+        <v>46188.507071668981</v>
+      </c>
+      <c r="D268" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G268" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H268" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I268" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A269" s="1">
+        <v>15599</v>
+      </c>
+      <c r="C269" s="2">
+        <v>46188.507079784351</v>
+      </c>
+      <c r="D269" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G269" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H269" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I269" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A270" s="1">
+        <v>15600</v>
+      </c>
+      <c r="C270" s="2">
+        <v>46188.507079784351</v>
+      </c>
+      <c r="D270" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G270" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H270" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I270" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A271" s="1">
+        <v>15601</v>
+      </c>
+      <c r="C271" s="2">
+        <v>46188.507079784351</v>
+      </c>
+      <c r="D271" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G271" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H271" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I271" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A272" s="1">
+        <v>15602</v>
+      </c>
+      <c r="C272" s="2">
+        <v>46188.507079784351</v>
+      </c>
+      <c r="D272" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G272" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H272" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I272" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A273" s="1">
+        <v>15603</v>
+      </c>
+      <c r="C273" s="2">
+        <v>46188.507079784351</v>
+      </c>
+      <c r="D273" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G273" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H273" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I273" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A274" s="1">
+        <v>15604</v>
+      </c>
+      <c r="C274" s="2">
+        <v>46188.507079840871</v>
+      </c>
+      <c r="D274" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G274" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H274" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I274" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A275" s="1">
+        <v>15605</v>
+      </c>
+      <c r="C275" s="2">
+        <v>46188.507079840871</v>
+      </c>
+      <c r="D275" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G275" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H275" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I275" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A276" s="1">
+        <v>15606</v>
+      </c>
+      <c r="C276" s="2">
+        <v>46188.507606348139</v>
+      </c>
+      <c r="D276" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G276" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H276" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I276" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A277" s="1">
+        <v>15607</v>
+      </c>
+      <c r="C277" s="2">
+        <v>46188.507606348139</v>
+      </c>
+      <c r="D277" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G277" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H277" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I277" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A278" s="1">
+        <v>15608</v>
+      </c>
+      <c r="C278" s="2">
+        <v>46188.507606348139</v>
+      </c>
+      <c r="D278" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G278" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H278" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I278" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A279" s="1">
+        <v>15609</v>
+      </c>
+      <c r="C279" s="2">
+        <v>46188.507606348139</v>
+      </c>
+      <c r="D279" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G279" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H279" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I279" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A280" s="1">
+        <v>15610</v>
+      </c>
+      <c r="C280" s="2">
+        <v>46188.507606404652</v>
+      </c>
+      <c r="D280" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G280" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H280" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I280" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A281" s="1">
+        <v>15611</v>
+      </c>
+      <c r="C281" s="2">
+        <v>46188.507606404652</v>
+      </c>
+      <c r="D281" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G281" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H281" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I281" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="282" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A282" s="1">
+        <v>15612</v>
+      </c>
+      <c r="C282" s="2">
+        <v>46188.507617922216</v>
+      </c>
+      <c r="D282" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G282" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H282" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I282" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A283" s="1">
+        <v>15613</v>
+      </c>
+      <c r="C283" s="2">
+        <v>46188.507617922216</v>
+      </c>
+      <c r="D283" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G283" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H283" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I283" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="284" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A284" s="1">
+        <v>15614</v>
+      </c>
+      <c r="C284" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D284" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G284" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H284" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I284" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="285" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A285" s="1">
+        <v>15615</v>
+      </c>
+      <c r="C285" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D285" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G285" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H285" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I285" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="286" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A286" s="1">
+        <v>15616</v>
+      </c>
+      <c r="C286" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D286" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G286" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H286" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I286" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="287" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A287" s="1">
+        <v>15617</v>
+      </c>
+      <c r="C287" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D287" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G287" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H287" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I287" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="288" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A288" s="1">
+        <v>15618</v>
+      </c>
+      <c r="C288" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D288" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G288" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H288" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I288" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="289" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A289" s="1">
+        <v>15619</v>
+      </c>
+      <c r="C289" s="2">
+        <v>46188.507617978721</v>
+      </c>
+      <c r="D289" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G289" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H289" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I289" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="290" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A290" s="1">
+        <v>15620</v>
+      </c>
+      <c r="C290" s="2">
+        <v>46188.507618035241</v>
+      </c>
+      <c r="D290" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G290" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H290" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I290" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="291" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A291" s="1">
+        <v>15621</v>
+      </c>
+      <c r="C291" s="2">
+        <v>46188.507618035241</v>
+      </c>
+      <c r="D291" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G291" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H291" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I291" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="292" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A292" s="1">
+        <v>15622</v>
+      </c>
+      <c r="C292" s="2">
+        <v>46188.507618035241</v>
+      </c>
+      <c r="D292" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G292" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H292" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I292" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="293" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A293" s="1">
+        <v>15623</v>
+      </c>
+      <c r="C293" s="2">
+        <v>46188.50761809176</v>
+      </c>
+      <c r="D293" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G293" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H293" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I293" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="294" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A294" s="1">
+        <v>15624</v>
+      </c>
+      <c r="C294" s="2">
+        <v>46188.507665258381</v>
+      </c>
+      <c r="D294" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="F294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G294" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H294" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I294" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="295" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A295" s="1">
+        <v>15625</v>
+      </c>
+      <c r="C295" s="2">
+        <v>46188.507665258381</v>
+      </c>
+      <c r="D295" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G295" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H295" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I295" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="296" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A296" s="1">
+        <v>15626</v>
+      </c>
+      <c r="C296" s="2">
+        <v>46188.507665314886</v>
+      </c>
+      <c r="D296" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G296" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H296" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I296" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="297" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A297" s="1">
+        <v>15627</v>
+      </c>
+      <c r="C297" s="2">
+        <v>46188.507665314886</v>
+      </c>
+      <c r="D297" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G297" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H297" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I297" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="298" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A298" s="1">
+        <v>15628</v>
+      </c>
+      <c r="C298" s="2">
+        <v>46188.507665314886</v>
+      </c>
+      <c r="D298" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G298" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H298" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I298" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="299" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A299" s="1">
+        <v>15629</v>
+      </c>
+      <c r="C299" s="2">
+        <v>46188.507665371406</v>
+      </c>
+      <c r="D299" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G299" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H299" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I299" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="300" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A300" s="1">
+        <v>15630</v>
+      </c>
+      <c r="C300" s="2">
+        <v>46188.507665371406</v>
+      </c>
+      <c r="D300" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G300" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H300" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I300" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="301" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A301" s="1">
+        <v>15631</v>
+      </c>
+      <c r="C301" s="2">
+        <v>46188.507665371406</v>
+      </c>
+      <c r="D301" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G301" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H301" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I301" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="302" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A302" s="1">
+        <v>15632</v>
+      </c>
+      <c r="C302" s="2">
+        <v>46188.507665371406</v>
+      </c>
+      <c r="D302" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="F302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G302" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H302" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I302" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="303" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A303" s="1">
+        <v>15633</v>
+      </c>
+      <c r="C303" s="2">
+        <v>46188.507665371406</v>
+      </c>
+      <c r="D303" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G303" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H303" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I303" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="304" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A304" s="1">
+        <v>15634</v>
+      </c>
+      <c r="C304" s="2">
+        <v>46188.507665427926</v>
+      </c>
+      <c r="D304" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G304" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H304" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I304" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="305" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A305" s="1">
+        <v>15635</v>
+      </c>
+      <c r="C305" s="2">
+        <v>46188.507665427926</v>
+      </c>
+      <c r="D305" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G305" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H305" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I305" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="306" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A306" s="1">
+        <v>15636</v>
+      </c>
+      <c r="C306" s="2">
+        <v>46188.507665427926</v>
+      </c>
+      <c r="D306" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G306" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H306" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I306" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="307" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A307" s="1">
+        <v>15637</v>
+      </c>
+      <c r="C307" s="2">
+        <v>46188.507665495737</v>
+      </c>
+      <c r="D307" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G307" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H307" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I307" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="308" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A308" s="1">
+        <v>15638</v>
+      </c>
+      <c r="C308" s="2">
+        <v>46188.507737765925</v>
+      </c>
+      <c r="D308" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F308" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G308" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H308" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I308" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="309" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A309" s="1">
+        <v>15639</v>
+      </c>
+      <c r="C309" s="2">
+        <v>46188.507737765925</v>
+      </c>
+      <c r="D309" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F309" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G309" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H309" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I309" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="310" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A310" s="1">
+        <v>15640</v>
+      </c>
+      <c r="C310" s="2">
+        <v>46188.507737833737</v>
+      </c>
+      <c r="D310" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G310" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H310" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I310" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="311" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A311" s="1">
+        <v>15641</v>
+      </c>
+      <c r="C311" s="2">
+        <v>46188.507751261503</v>
+      </c>
+      <c r="D311" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F311" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G311" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H311" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I311" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="312" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A312" s="1">
+        <v>15642</v>
+      </c>
+      <c r="C312" s="2">
+        <v>46188.507751261503</v>
+      </c>
+      <c r="D312" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F312" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G312" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H312" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I312" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="313" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A313" s="1">
+        <v>15643</v>
+      </c>
+      <c r="C313" s="2">
+        <v>46188.507751261503</v>
+      </c>
+      <c r="D313" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F313" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G313" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H313" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I313" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="314" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A314" s="1">
+        <v>15644</v>
+      </c>
+      <c r="C314" s="2">
+        <v>46188.507751318008</v>
+      </c>
+      <c r="D314" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F314" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G314" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H314" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I314" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="315" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A315" s="1">
+        <v>15645</v>
+      </c>
+      <c r="C315" s="2">
+        <v>46188.508327512463</v>
+      </c>
+      <c r="D315" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F315" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G315" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H315" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I315" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="316" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A316" s="1">
+        <v>15646</v>
+      </c>
+      <c r="C316" s="2">
+        <v>46188.508327512463</v>
+      </c>
+      <c r="D316" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F316" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G316" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H316" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I316" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="317" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A317" s="1">
+        <v>15647</v>
+      </c>
+      <c r="C317" s="2">
+        <v>46188.508336724219</v>
+      </c>
+      <c r="D317" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G317" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H317" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I317" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="318" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A318" s="1">
+        <v>15648</v>
+      </c>
+      <c r="C318" s="2">
+        <v>46188.508336724219</v>
+      </c>
+      <c r="D318" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G318" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H318" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I318" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="319" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A319" s="1">
+        <v>15649</v>
+      </c>
+      <c r="C319" s="2">
+        <v>46188.508336724219</v>
+      </c>
+      <c r="D319" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F319" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G319" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H319" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I319" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="320" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A320" s="1">
+        <v>15650</v>
+      </c>
+      <c r="C320" s="2">
+        <v>46188.508336724219</v>
+      </c>
+      <c r="D320" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F320" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G320" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H320" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I320" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="321" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A321" s="1">
+        <v>15651</v>
+      </c>
+      <c r="C321" s="2">
+        <v>46188.508336724219</v>
+      </c>
+      <c r="D321" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F321" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G321" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H321" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I321" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A322" s="1">
+        <v>15652</v>
+      </c>
+      <c r="C322" s="2">
+        <v>46188.508336780731</v>
+      </c>
+      <c r="D322" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F322" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G322" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="H322" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I322" s="3" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J80">
-    <sortCondition ref="A2:A80"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J322">
+    <sortCondition ref="A2:A322"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
